--- a/vault-dalarna-university/03 IKS/Analys/Övrigt.xlsx
+++ b/vault-dalarna-university/03 IKS/Analys/Övrigt.xlsx
@@ -3052,7 +3052,7 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>Saknar standardfras om pedagogiskt stöd: Kursen kan tillgodoräknas i Filosofi II.**** Denna kursplan ersätter FI1021. Kursen ingick i huvudområde Materialvetensk…</t>
+          <t>Saknar standardfras om pedagogiskt stöd: Kursen kan tillgodoräknas i Filosofi II. Denna kursplan ersätter FI1021. Kursen ingick i huvudområde Materialvetenskap t…</t>
         </is>
       </c>
       <c r="E97" s="2" t="inlineStr">
@@ -5428,7 +5428,7 @@
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>Saknar standardfras om pedagogiskt stöd: Motsvarar LP1041 delkurs 1 och LP1048. Ersätter LP1062. Denna kurs kan inte användas i en examen tillsammans med kursen_…</t>
+          <t>Saknar standardfras om pedagogiskt stöd: Motsvarar LP1041 delkurs 1 och LP1048. Ersätter LP1062. Denna kurs kan inte användas i en examen tillsammans med kursen …</t>
         </is>
       </c>
       <c r="E185" s="2" t="inlineStr">
@@ -5833,7 +5833,7 @@
       </c>
       <c r="D200" t="inlineStr">
         <is>
-          <t>Saknar standardfras om pedagogiskt stöd: Ersätter GLP29X. Denna kurs kan inte användas i en examen tillsammans med kursen_ Inspelning i studio för Musik- och lju…</t>
+          <t>Saknar standardfras om pedagogiskt stöd: Ersätter GLP29X. Denna kurs kan inte användas i en examen tillsammans med kursen _Inspelning i studio för Musik- och lju…</t>
         </is>
       </c>
       <c r="E200" s="2" t="inlineStr">
@@ -7102,7 +7102,7 @@
       </c>
       <c r="D247" t="inlineStr">
         <is>
-          <t>Saknar standardfras om pedagogiskt stöd: There is a maximum of five resit opportunities to take the exam. **** Replaces NAD 011, NAD 010, NAD 009, NAD 006.…</t>
+          <t>Saknar standardfras om pedagogiskt stöd: There is a maximum of five resit opportunities to take the exam. Replaces NAD 011, NAD 010, NAD 009, NAD 006.…</t>
         </is>
       </c>
       <c r="E247" s="2" t="inlineStr">
@@ -7480,7 +7480,7 @@
       </c>
       <c r="D261" t="inlineStr">
         <is>
-          <t>Saknar standardfras om pedagogiskt stöd: Kursen utgör den andra av tre kurser inom inriktningen _Språk, lek och lärande _och utgör dessutom en valbar yrkesspecia…</t>
+          <t>Saknar standardfras om pedagogiskt stöd: Kursen utgör den andra av tre kurser inom inriktningen _Språk, lek och lärande_ och utgör dessutom en valbar yrkesspecia…</t>
         </is>
       </c>
       <c r="E261" s="2" t="inlineStr">
@@ -11584,7 +11584,7 @@
       </c>
       <c r="D413" t="inlineStr">
         <is>
-          <t>Saknar standardfras om pedagogiskt stöd: Kursen ersätter RV1018.****…</t>
+          <t>Saknar standardfras om pedagogiskt stöd: Kursen ersätter RV1018.…</t>
         </is>
       </c>
       <c r="E413" s="2" t="inlineStr">

--- a/vault-dalarna-university/03 IKS/Analys/Övrigt.xlsx
+++ b/vault-dalarna-university/03 IKS/Analys/Övrigt.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Övrigt" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Övrigt'!$A$1:$E$523</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Övrigt'!$A$1:$E$542</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E523"/>
+  <dimension ref="A1:E542"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -8410,12 +8410,12 @@
     <row r="296">
       <c r="A296" s="2" t="inlineStr">
         <is>
-          <t>GPA2FL</t>
+          <t>FPA0001</t>
         </is>
       </c>
       <c r="B296" t="inlineStr">
         <is>
-          <t>PEE</t>
+          <t>PEDAGARB</t>
         </is>
       </c>
       <c r="C296" t="inlineStr">
@@ -8425,24 +8425,24 @@
       </c>
       <c r="D296" t="inlineStr">
         <is>
-          <t>Saknar standardfras om pedagogiskt stöd: Ersätter PA1044.…</t>
+          <t>Saknar standardfras om pedagogiskt stöd: Kursen är nätbaserad. Undervisningen ges på engelska. Både muntliga och skriftliga examinationer sker på engelska, om in…</t>
         </is>
       </c>
       <c r="E296" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPA2FL</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=FPA0001</t>
         </is>
       </c>
     </row>
     <row r="297">
       <c r="A297" s="2" t="inlineStr">
         <is>
-          <t>GPA2FW</t>
+          <t>FPA0002</t>
         </is>
       </c>
       <c r="B297" t="inlineStr">
         <is>
-          <t>PEE</t>
+          <t>PEDAGARB</t>
         </is>
       </c>
       <c r="C297" t="inlineStr">
@@ -8452,24 +8452,24 @@
       </c>
       <c r="D297" t="inlineStr">
         <is>
-          <t>Saknar standardfras om pedagogiskt stöd: Ersätter PA1046.…</t>
+          <t>Saknar standardfras om pedagogiskt stöd: Maximalt fem examinationstillfällen. Kursen ges på svenska om ej annat anges. Kursen är en campusbaserad kurs om ej anna…</t>
         </is>
       </c>
       <c r="E297" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPA2FW</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=FPA0002</t>
         </is>
       </c>
     </row>
     <row r="298">
       <c r="A298" s="2" t="inlineStr">
         <is>
-          <t>GPA2K3</t>
+          <t>FPA0003</t>
         </is>
       </c>
       <c r="B298" t="inlineStr">
         <is>
-          <t>PEE</t>
+          <t>PEDAGARB</t>
         </is>
       </c>
       <c r="C298" t="inlineStr">
@@ -8479,105 +8479,105 @@
       </c>
       <c r="D298" t="inlineStr">
         <is>
-          <t>Saknar standardfras om pedagogiskt stöd: Ersätter PA1053.…</t>
+          <t>Saknar standardfras om pedagogiskt stöd: Undervisning samt muntliga och skriftliga examinationer sker på engelska, om inteannat meddelas.…</t>
         </is>
       </c>
       <c r="E298" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPA2K3</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=FPA0003</t>
         </is>
       </c>
     </row>
     <row r="299">
       <c r="A299" s="2" t="inlineStr">
         <is>
-          <t>GPA2KU</t>
+          <t>FPA0004</t>
         </is>
       </c>
       <c r="B299" t="inlineStr">
         <is>
-          <t>PEE</t>
+          <t>PEDAGARB</t>
         </is>
       </c>
       <c r="C299" t="inlineStr">
         <is>
-          <t>Saknar standardfras om pedagogiskt stöd</t>
+          <t>Sektion saknas</t>
         </is>
       </c>
       <c r="D299" t="inlineStr">
         <is>
-          <t>Saknar standardfras om pedagogiskt stöd: Kursen ges endast som uppdragsutbildning.…</t>
+          <t>Ingen Övrigt-sektion i kursplanen</t>
         </is>
       </c>
       <c r="E299" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPA2KU</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=FPA0004</t>
         </is>
       </c>
     </row>
     <row r="300">
       <c r="A300" s="2" t="inlineStr">
         <is>
-          <t>GPA2LM</t>
+          <t>FPA0005</t>
         </is>
       </c>
       <c r="B300" t="inlineStr">
         <is>
-          <t>PEE</t>
+          <t>PEDAGARB</t>
         </is>
       </c>
       <c r="C300" t="inlineStr">
         <is>
-          <t>Saknar standardfras om pedagogiskt stöd</t>
+          <t>Sektion saknas</t>
         </is>
       </c>
       <c r="D300" t="inlineStr">
         <is>
-          <t>Saknar standardfras om pedagogiskt stöd: Kursen ersätter GPA2F2.…</t>
+          <t>Ingen Övrigt-sektion i kursplanen</t>
         </is>
       </c>
       <c r="E300" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPA2LM</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=FPA0005</t>
         </is>
       </c>
     </row>
     <row r="301">
       <c r="A301" s="2" t="inlineStr">
         <is>
-          <t>GPA2LN</t>
+          <t>FPA0006</t>
         </is>
       </c>
       <c r="B301" t="inlineStr">
         <is>
-          <t>PEE</t>
+          <t>PEDAGARB</t>
         </is>
       </c>
       <c r="C301" t="inlineStr">
         <is>
-          <t>Saknar standardfras om pedagogiskt stöd</t>
+          <t>Sektion saknas</t>
         </is>
       </c>
       <c r="D301" t="inlineStr">
         <is>
-          <t>Saknar standardfras om pedagogiskt stöd: Kursen ingår i Personal- och arbetslivsprogrammet. Kan ej tillgodoräknas i en examen samtidigt som kursen PA1024, Redovi…</t>
+          <t>Ingen Övrigt-sektion i kursplanen</t>
         </is>
       </c>
       <c r="E301" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPA2LN</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=FPA0006</t>
         </is>
       </c>
     </row>
     <row r="302">
       <c r="A302" s="2" t="inlineStr">
         <is>
-          <t>GPA2NY</t>
+          <t>FPA0007</t>
         </is>
       </c>
       <c r="B302" t="inlineStr">
         <is>
-          <t>PEE</t>
+          <t>PEDAGARB</t>
         </is>
       </c>
       <c r="C302" t="inlineStr">
@@ -8587,24 +8587,24 @@
       </c>
       <c r="D302" t="inlineStr">
         <is>
-          <t>Saknar standardfras om pedagogiskt stöd: Ersätter GPA269.…</t>
+          <t>Saknar standardfras om pedagogiskt stöd: Kursen ges på svenska om ej annat anges. Kursen ges antingen som nätbaserad eller campusförlagd kurs, alternativt med in…</t>
         </is>
       </c>
       <c r="E302" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPA2NY</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=FPA0007</t>
         </is>
       </c>
     </row>
     <row r="303">
       <c r="A303" s="2" t="inlineStr">
         <is>
-          <t>GPA2P7</t>
+          <t>FPA2226</t>
         </is>
       </c>
       <c r="B303" t="inlineStr">
         <is>
-          <t>PEE</t>
+          <t>PEDAGARB</t>
         </is>
       </c>
       <c r="C303" t="inlineStr">
@@ -8614,24 +8614,24 @@
       </c>
       <c r="D303" t="inlineStr">
         <is>
-          <t>Saknar standardfras om pedagogiskt stöd: Ersätter GPA2FN.…</t>
+          <t>Saknar standardfras om pedagogiskt stöd: Undervisning såväl som muntliga och skriftliga examinationer sker på engelska, om inte annat meddelas.…</t>
         </is>
       </c>
       <c r="E303" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPA2P7</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=FPA2226</t>
         </is>
       </c>
     </row>
     <row r="304">
       <c r="A304" s="2" t="inlineStr">
         <is>
-          <t>GPA2R6</t>
+          <t>FPA2227</t>
         </is>
       </c>
       <c r="B304" t="inlineStr">
         <is>
-          <t>PEE</t>
+          <t>PEDAGARB</t>
         </is>
       </c>
       <c r="C304" t="inlineStr">
@@ -8641,24 +8641,24 @@
       </c>
       <c r="D304" t="inlineStr">
         <is>
-          <t>Saknar standardfras om pedagogiskt stöd: Ersätter GPA2JY.…</t>
+          <t>Saknar standardfras om pedagogiskt stöd: Kursen ges på svenska. Kursen är campusbaserad och kommer att inkludera sammankomster i internatform.…</t>
         </is>
       </c>
       <c r="E304" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPA2R6</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=FPA2227</t>
         </is>
       </c>
     </row>
     <row r="305">
       <c r="A305" s="2" t="inlineStr">
         <is>
-          <t>PA2008</t>
+          <t>FPA2228</t>
         </is>
       </c>
       <c r="B305" t="inlineStr">
         <is>
-          <t>PEE</t>
+          <t>PEDAGARB</t>
         </is>
       </c>
       <c r="C305" t="inlineStr">
@@ -8668,78 +8668,78 @@
       </c>
       <c r="D305" t="inlineStr">
         <is>
-          <t>Saknar standardfras om pedagogiskt stöd: Kursen ingår i Personal- och arbetslivsprogrammet.…</t>
+          <t>Saknar standardfras om pedagogiskt stöd: Doktorand som inte är antagen till någon av Högskolan Dalarnas forskarutbildningar antas i mån av plats.…</t>
         </is>
       </c>
       <c r="E305" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PA2008</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=FPA2228</t>
         </is>
       </c>
     </row>
     <row r="306">
       <c r="A306" s="2" t="inlineStr">
         <is>
-          <t>PA2009</t>
+          <t>FPA222A</t>
         </is>
       </c>
       <c r="B306" t="inlineStr">
         <is>
-          <t>PEE</t>
+          <t>PEDAGARB</t>
         </is>
       </c>
       <c r="C306" t="inlineStr">
         <is>
-          <t>Saknar standardfras om pedagogiskt stöd</t>
+          <t>Sektion saknas</t>
         </is>
       </c>
       <c r="D306" t="inlineStr">
         <is>
-          <t>Saknar standardfras om pedagogiskt stöd: Kursen ingår i Personal- och arbetslivsprogrammet.…</t>
+          <t>Ingen Övrigt-sektion i kursplanen</t>
         </is>
       </c>
       <c r="E306" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PA2009</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=FPA222A</t>
         </is>
       </c>
     </row>
     <row r="307">
       <c r="A307" s="2" t="inlineStr">
         <is>
-          <t>PA2010</t>
+          <t>FPA222B</t>
         </is>
       </c>
       <c r="B307" t="inlineStr">
         <is>
-          <t>PEE</t>
+          <t>PEDAGARB</t>
         </is>
       </c>
       <c r="C307" t="inlineStr">
         <is>
-          <t>Saknar standardfras om pedagogiskt stöd</t>
+          <t>Sektion saknas</t>
         </is>
       </c>
       <c r="D307" t="inlineStr">
         <is>
-          <t>Saknar standardfras om pedagogiskt stöd: Kursen ingår i Personal- och arbetslivsprogrammet.…</t>
+          <t>Ingen Övrigt-sektion i kursplanen</t>
         </is>
       </c>
       <c r="E307" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PA2010</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=FPA222B</t>
         </is>
       </c>
     </row>
     <row r="308">
       <c r="A308" s="2" t="inlineStr">
         <is>
-          <t>PA2011</t>
+          <t>FPA222C</t>
         </is>
       </c>
       <c r="B308" t="inlineStr">
         <is>
-          <t>PEE</t>
+          <t>PEDAGARB</t>
         </is>
       </c>
       <c r="C308" t="inlineStr">
@@ -8749,24 +8749,24 @@
       </c>
       <c r="D308" t="inlineStr">
         <is>
-          <t>Saknar standardfras om pedagogiskt stöd: Ersätter PA2006…</t>
+          <t>Saknar standardfras om pedagogiskt stöd: Kursen ges på svenska om ej annat anges. Kursen ges antingen som nätbaserad eller campusförlagd kurs, alternativt med in…</t>
         </is>
       </c>
       <c r="E308" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PA2011</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=FPA222C</t>
         </is>
       </c>
     </row>
     <row r="309">
       <c r="A309" s="2" t="inlineStr">
         <is>
-          <t>APG22X</t>
+          <t>FPA222D</t>
         </is>
       </c>
       <c r="B309" t="inlineStr">
         <is>
-          <t>PGA</t>
+          <t>PEDAGARB</t>
         </is>
       </c>
       <c r="C309" t="inlineStr">
@@ -8776,24 +8776,24 @@
       </c>
       <c r="D309" t="inlineStr">
         <is>
-          <t>Saknar standardfras om pedagogiskt stöd: Kursen ingår i Magisterprogram i pedagogiskt arbete. Kursen motsvarar PG3062.…</t>
+          <t>Saknar standardfras om pedagogiskt stöd: Kursen ges på engelska.…</t>
         </is>
       </c>
       <c r="E309" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG22X</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=FPA222D</t>
         </is>
       </c>
     </row>
     <row r="310">
       <c r="A310" s="2" t="inlineStr">
         <is>
-          <t>APG244</t>
+          <t>FPA222E</t>
         </is>
       </c>
       <c r="B310" t="inlineStr">
         <is>
-          <t>PGA</t>
+          <t>PEDAGARB</t>
         </is>
       </c>
       <c r="C310" t="inlineStr">
@@ -8803,24 +8803,24 @@
       </c>
       <c r="D310" t="inlineStr">
         <is>
-          <t>Saknar standardfras om pedagogiskt stöd: Kursen ingår i Grundlärarprogrammet. Kursen motsvarar PG3026.…</t>
+          <t>Saknar standardfras om pedagogiskt stöd: Kursen ges på svenska. Kursen är campusbaserad.…</t>
         </is>
       </c>
       <c r="E310" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG244</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=FPA222E</t>
         </is>
       </c>
     </row>
     <row r="311">
       <c r="A311" s="2" t="inlineStr">
         <is>
-          <t>APG245</t>
+          <t>FPA222F</t>
         </is>
       </c>
       <c r="B311" t="inlineStr">
         <is>
-          <t>PGA</t>
+          <t>PEDAGARB</t>
         </is>
       </c>
       <c r="C311" t="inlineStr">
@@ -8830,24 +8830,24 @@
       </c>
       <c r="D311" t="inlineStr">
         <is>
-          <t>Saknar standardfras om pedagogiskt stöd: Kursen ingår i Grundlärarprogrammet. Kursen motsvarar PG3027.…</t>
+          <t>Saknar standardfras om pedagogiskt stöd: Undervisning samt muntliga och skriftliga examinationer sker på engelska.…</t>
         </is>
       </c>
       <c r="E311" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG245</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=FPA222F</t>
         </is>
       </c>
     </row>
     <row r="312">
       <c r="A312" s="2" t="inlineStr">
         <is>
-          <t>APG246</t>
+          <t>FPA222G</t>
         </is>
       </c>
       <c r="B312" t="inlineStr">
         <is>
-          <t>PGA</t>
+          <t>PEDAGARB</t>
         </is>
       </c>
       <c r="C312" t="inlineStr">
@@ -8857,24 +8857,24 @@
       </c>
       <c r="D312" t="inlineStr">
         <is>
-          <t>Saknar standardfras om pedagogiskt stöd: Kursen ingår i Grundlärarprogrammet. Kursen motsvarar PG3063. Denna kurs utgör den andra delen av två inom vilka den stu…</t>
+          <t>Saknar standardfras om pedagogiskt stöd: Kursen ges på svenska. Kursen är campusbaserad.…</t>
         </is>
       </c>
       <c r="E312" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG246</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=FPA222G</t>
         </is>
       </c>
     </row>
     <row r="313">
       <c r="A313" s="2" t="inlineStr">
         <is>
-          <t>APG247</t>
+          <t>FPA222J</t>
         </is>
       </c>
       <c r="B313" t="inlineStr">
         <is>
-          <t>PGA</t>
+          <t>PEDAGARB</t>
         </is>
       </c>
       <c r="C313" t="inlineStr">
@@ -8884,51 +8884,51 @@
       </c>
       <c r="D313" t="inlineStr">
         <is>
-          <t>Saknar standardfras om pedagogiskt stöd: Kursen ingår i Grundlärarprogrammet. Kursen motsvarar PG3064. Denna kurs utgör den andra delen av två inom vilka den stu…</t>
+          <t>Saknar standardfras om pedagogiskt stöd: För att kunna delta i kursen krävs tillgång till egen dator tillsammans med datortillbehör för nätburen kommunikation, s…</t>
         </is>
       </c>
       <c r="E313" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG247</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=FPA222J</t>
         </is>
       </c>
     </row>
     <row r="314">
       <c r="A314" s="2" t="inlineStr">
         <is>
-          <t>APG24D</t>
+          <t>FPA222N</t>
         </is>
       </c>
       <c r="B314" t="inlineStr">
         <is>
-          <t>PGA</t>
+          <t>PEDAGARB</t>
         </is>
       </c>
       <c r="C314" t="inlineStr">
         <is>
-          <t>Saknar standardfras om pedagogiskt stöd</t>
+          <t>Sektion saknas</t>
         </is>
       </c>
       <c r="D314" t="inlineStr">
         <is>
-          <t>Saknar standardfras om pedagogiskt stöd: Kursen motsvarar PG3033 och PG3066.…</t>
+          <t>Ingen Övrigt-sektion i kursplanen</t>
         </is>
       </c>
       <c r="E314" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG24D</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=FPA222N</t>
         </is>
       </c>
     </row>
     <row r="315">
       <c r="A315" s="2" t="inlineStr">
         <is>
-          <t>APG24E</t>
+          <t>GPA2FL</t>
         </is>
       </c>
       <c r="B315" t="inlineStr">
         <is>
-          <t>PGA</t>
+          <t>PEE</t>
         </is>
       </c>
       <c r="C315" t="inlineStr">
@@ -8938,24 +8938,24 @@
       </c>
       <c r="D315" t="inlineStr">
         <is>
-          <t>Saknar standardfras om pedagogiskt stöd: Kursen motsvarar PG3036 och PG3060.…</t>
+          <t>Saknar standardfras om pedagogiskt stöd: Ersätter PA1044.…</t>
         </is>
       </c>
       <c r="E315" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG24E</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPA2FL</t>
         </is>
       </c>
     </row>
     <row r="316">
       <c r="A316" s="2" t="inlineStr">
         <is>
-          <t>APG24S</t>
+          <t>GPA2FW</t>
         </is>
       </c>
       <c r="B316" t="inlineStr">
         <is>
-          <t>PGA</t>
+          <t>PEE</t>
         </is>
       </c>
       <c r="C316" t="inlineStr">
@@ -8965,24 +8965,24 @@
       </c>
       <c r="D316" t="inlineStr">
         <is>
-          <t>Saknar standardfras om pedagogiskt stöd: I kursen ingår en obligatorisk träff motsvarande maximalt tre dagar på campus. Kursen motsvarar PG3045.…</t>
+          <t>Saknar standardfras om pedagogiskt stöd: Ersätter PA1046.…</t>
         </is>
       </c>
       <c r="E316" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG24S</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPA2FW</t>
         </is>
       </c>
     </row>
     <row r="317">
       <c r="A317" s="2" t="inlineStr">
         <is>
-          <t>APG25N</t>
+          <t>GPA2K3</t>
         </is>
       </c>
       <c r="B317" t="inlineStr">
         <is>
-          <t>PGA</t>
+          <t>PEE</t>
         </is>
       </c>
       <c r="C317" t="inlineStr">
@@ -8992,51 +8992,51 @@
       </c>
       <c r="D317" t="inlineStr">
         <is>
-          <t>Saknar standardfras om pedagogiskt stöd: Kursen kan ingå som valbar kurs i magisterprogrammet i pedagogiskt arbete vid Högskolan Dalarna.…</t>
+          <t>Saknar standardfras om pedagogiskt stöd: Ersätter PA1053.…</t>
         </is>
       </c>
       <c r="E317" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG25N</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPA2K3</t>
         </is>
       </c>
     </row>
     <row r="318">
       <c r="A318" s="2" t="inlineStr">
         <is>
-          <t>APG26D</t>
+          <t>GPA2KU</t>
         </is>
       </c>
       <c r="B318" t="inlineStr">
         <is>
-          <t>PGA</t>
+          <t>PEE</t>
         </is>
       </c>
       <c r="C318" t="inlineStr">
         <is>
-          <t>Sektion saknas</t>
+          <t>Saknar standardfras om pedagogiskt stöd</t>
         </is>
       </c>
       <c r="D318" t="inlineStr">
         <is>
-          <t>Ingen Övrigt-sektion i kursplanen</t>
+          <t>Saknar standardfras om pedagogiskt stöd: Kursen ges endast som uppdragsutbildning.…</t>
         </is>
       </c>
       <c r="E318" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG26D</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPA2KU</t>
         </is>
       </c>
     </row>
     <row r="319">
       <c r="A319" s="2" t="inlineStr">
         <is>
-          <t>APG275</t>
+          <t>GPA2LM</t>
         </is>
       </c>
       <c r="B319" t="inlineStr">
         <is>
-          <t>PGA</t>
+          <t>PEE</t>
         </is>
       </c>
       <c r="C319" t="inlineStr">
@@ -9046,24 +9046,24 @@
       </c>
       <c r="D319" t="inlineStr">
         <is>
-          <t>Saknar standardfras om pedagogiskt stöd: För nätbaserad kurs ingår en obligatorisk träff om maximalt tre dagar på campus. För nätbaserad kurs krävs att den stude…</t>
+          <t>Saknar standardfras om pedagogiskt stöd: Kursen ersätter GPA2F2.…</t>
         </is>
       </c>
       <c r="E319" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG275</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPA2LM</t>
         </is>
       </c>
     </row>
     <row r="320">
       <c r="A320" s="2" t="inlineStr">
         <is>
-          <t>APG276</t>
+          <t>GPA2LN</t>
         </is>
       </c>
       <c r="B320" t="inlineStr">
         <is>
-          <t>PGA</t>
+          <t>PEE</t>
         </is>
       </c>
       <c r="C320" t="inlineStr">
@@ -9073,24 +9073,24 @@
       </c>
       <c r="D320" t="inlineStr">
         <is>
-          <t>Saknar standardfras om pedagogiskt stöd: För nätbaserad kurs ingår en obligatorisk träff om maximalt tre dagar på campus. För nätbaserad kurs krävs att den stude…</t>
+          <t>Saknar standardfras om pedagogiskt stöd: Kursen ingår i Personal- och arbetslivsprogrammet. Kan ej tillgodoräknas i en examen samtidigt som kursen PA1024, Redovi…</t>
         </is>
       </c>
       <c r="E320" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG276</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPA2LN</t>
         </is>
       </c>
     </row>
     <row r="321">
       <c r="A321" s="2" t="inlineStr">
         <is>
-          <t>APG27T</t>
+          <t>GPA2NY</t>
         </is>
       </c>
       <c r="B321" t="inlineStr">
         <is>
-          <t>PGA</t>
+          <t>PEE</t>
         </is>
       </c>
       <c r="C321" t="inlineStr">
@@ -9100,24 +9100,24 @@
       </c>
       <c r="D321" t="inlineStr">
         <is>
-          <t>Saknar standardfras om pedagogiskt stöd: Kursen är en uppdragsutbildning från Skolverket och gäller rektorer som genomgått Rektorsprogrammet med godkänt resultat…</t>
+          <t>Saknar standardfras om pedagogiskt stöd: Ersätter GPA269.…</t>
         </is>
       </c>
       <c r="E321" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG27T</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPA2NY</t>
         </is>
       </c>
     </row>
     <row r="322">
       <c r="A322" s="2" t="inlineStr">
         <is>
-          <t>APG27U</t>
+          <t>GPA2P7</t>
         </is>
       </c>
       <c r="B322" t="inlineStr">
         <is>
-          <t>PGA</t>
+          <t>PEE</t>
         </is>
       </c>
       <c r="C322" t="inlineStr">
@@ -9127,24 +9127,24 @@
       </c>
       <c r="D322" t="inlineStr">
         <is>
-          <t>Saknar standardfras om pedagogiskt stöd: Kursen ingår i Förskollärarprogrammet. Student som underkänts i mål knutna till kursens verksamhetsförlagda utbildning h…</t>
+          <t>Saknar standardfras om pedagogiskt stöd: Ersätter GPA2FN.…</t>
         </is>
       </c>
       <c r="E322" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG27U</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPA2P7</t>
         </is>
       </c>
     </row>
     <row r="323">
       <c r="A323" s="2" t="inlineStr">
         <is>
-          <t>APG27Z</t>
+          <t>GPA2R6</t>
         </is>
       </c>
       <c r="B323" t="inlineStr">
         <is>
-          <t>PGA</t>
+          <t>PEE</t>
         </is>
       </c>
       <c r="C323" t="inlineStr">
@@ -9154,24 +9154,24 @@
       </c>
       <c r="D323" t="inlineStr">
         <is>
-          <t>Saknar standardfras om pedagogiskt stöd: Nätbaserad kurs, innehåller obligatoriska campusträffar. Student som underkänts i mål knutna till kursens verksamhetsför…</t>
+          <t>Saknar standardfras om pedagogiskt stöd: Ersätter GPA2JY.…</t>
         </is>
       </c>
       <c r="E323" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG27Z</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPA2R6</t>
         </is>
       </c>
     </row>
     <row r="324">
       <c r="A324" s="2" t="inlineStr">
         <is>
-          <t>APG282</t>
+          <t>PA2008</t>
         </is>
       </c>
       <c r="B324" t="inlineStr">
         <is>
-          <t>PGA</t>
+          <t>PEE</t>
         </is>
       </c>
       <c r="C324" t="inlineStr">
@@ -9181,24 +9181,24 @@
       </c>
       <c r="D324" t="inlineStr">
         <is>
-          <t>Saknar standardfras om pedagogiskt stöd: Nätbaserad kurs, innehåller en campusträff då ventilering av självständiga arbeten sker.…</t>
+          <t>Saknar standardfras om pedagogiskt stöd: Kursen ingår i Personal- och arbetslivsprogrammet.…</t>
         </is>
       </c>
       <c r="E324" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG282</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PA2008</t>
         </is>
       </c>
     </row>
     <row r="325">
       <c r="A325" s="2" t="inlineStr">
         <is>
-          <t>APG28B</t>
+          <t>PA2009</t>
         </is>
       </c>
       <c r="B325" t="inlineStr">
         <is>
-          <t>PGA</t>
+          <t>PEE</t>
         </is>
       </c>
       <c r="C325" t="inlineStr">
@@ -9208,24 +9208,24 @@
       </c>
       <c r="D325" t="inlineStr">
         <is>
-          <t>Saknar standardfras om pedagogiskt stöd: Nätbaserad kurs, innehåller obligatorisk campusträff. Student som underkänts i mål knutna till kursens verksamhetsförlag…</t>
+          <t>Saknar standardfras om pedagogiskt stöd: Kursen ingår i Personal- och arbetslivsprogrammet.…</t>
         </is>
       </c>
       <c r="E325" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG28B</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PA2009</t>
         </is>
       </c>
     </row>
     <row r="326">
       <c r="A326" s="2" t="inlineStr">
         <is>
-          <t>GPG22J</t>
+          <t>PA2010</t>
         </is>
       </c>
       <c r="B326" t="inlineStr">
         <is>
-          <t>PGA</t>
+          <t>PEE</t>
         </is>
       </c>
       <c r="C326" t="inlineStr">
@@ -9235,24 +9235,24 @@
       </c>
       <c r="D326" t="inlineStr">
         <is>
-          <t>Saknar standardfras om pedagogiskt stöd: Kursen erbjuds som campus/nät-kurs. För kursdeltagare som medverkar via nätet krävs tillgång till dator med internetuppk…</t>
+          <t>Saknar standardfras om pedagogiskt stöd: Kursen ingår i Personal- och arbetslivsprogrammet.…</t>
         </is>
       </c>
       <c r="E326" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG22J</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PA2010</t>
         </is>
       </c>
     </row>
     <row r="327">
       <c r="A327" s="2" t="inlineStr">
         <is>
-          <t>GPG22K</t>
+          <t>PA2011</t>
         </is>
       </c>
       <c r="B327" t="inlineStr">
         <is>
-          <t>PGA</t>
+          <t>PEE</t>
         </is>
       </c>
       <c r="C327" t="inlineStr">
@@ -9262,19 +9262,19 @@
       </c>
       <c r="D327" t="inlineStr">
         <is>
-          <t>Saknar standardfras om pedagogiskt stöd: Kursen ingår i programmet Kompletterande pedagogisk utbildning. Kursen motsvarar PG2066. Kursen avslutas med en obligato…</t>
+          <t>Saknar standardfras om pedagogiskt stöd: Ersätter PA2006…</t>
         </is>
       </c>
       <c r="E327" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG22K</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PA2011</t>
         </is>
       </c>
     </row>
     <row r="328">
       <c r="A328" s="2" t="inlineStr">
         <is>
-          <t>GPG27X</t>
+          <t>APG22X</t>
         </is>
       </c>
       <c r="B328" t="inlineStr">
@@ -9289,19 +9289,19 @@
       </c>
       <c r="D328" t="inlineStr">
         <is>
-          <t>Saknar standardfras om pedagogiskt stöd: Kursen vänder sig till personer med någon form av behörighetsgivande lärar- eller förskollärarexamen som valt att återvä…</t>
+          <t>Saknar standardfras om pedagogiskt stöd: Kursen ingår i Magisterprogram i pedagogiskt arbete. Kursen motsvarar PG3062.…</t>
         </is>
       </c>
       <c r="E328" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG27X</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG22X</t>
         </is>
       </c>
     </row>
     <row r="329">
       <c r="A329" s="2" t="inlineStr">
         <is>
-          <t>GPG2E6</t>
+          <t>APG244</t>
         </is>
       </c>
       <c r="B329" t="inlineStr">
@@ -9316,19 +9316,19 @@
       </c>
       <c r="D329" t="inlineStr">
         <is>
-          <t>Saknar standardfras om pedagogiskt stöd: Kursen ingår i Grundlärarprogrammet. Kursen motsvarar PG2069. Denna kurs utgör den första delen av två inom vilka den st…</t>
+          <t>Saknar standardfras om pedagogiskt stöd: Kursen ingår i Grundlärarprogrammet. Kursen motsvarar PG3026.…</t>
         </is>
       </c>
       <c r="E329" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG2E6</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG244</t>
         </is>
       </c>
     </row>
     <row r="330">
       <c r="A330" s="2" t="inlineStr">
         <is>
-          <t>GPG2E7</t>
+          <t>APG245</t>
         </is>
       </c>
       <c r="B330" t="inlineStr">
@@ -9343,19 +9343,19 @@
       </c>
       <c r="D330" t="inlineStr">
         <is>
-          <t>Saknar standardfras om pedagogiskt stöd: Kursen ingår i Grundlärarprogrammet. Kursen motsvarar PG2070. Denna kurs utgör den första delen av två inom vilka den st…</t>
+          <t>Saknar standardfras om pedagogiskt stöd: Kursen ingår i Grundlärarprogrammet. Kursen motsvarar PG3027.…</t>
         </is>
       </c>
       <c r="E330" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG2E7</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG245</t>
         </is>
       </c>
     </row>
     <row r="331">
       <c r="A331" s="2" t="inlineStr">
         <is>
-          <t>GPG2LZ</t>
+          <t>APG246</t>
         </is>
       </c>
       <c r="B331" t="inlineStr">
@@ -9370,19 +9370,19 @@
       </c>
       <c r="D331" t="inlineStr">
         <is>
-          <t>Saknar standardfras om pedagogiskt stöd: För nätbaserad kurs krävs att den studerande har möjlighet att kommunicera med ljud och bild via en dator eller motsvara…</t>
+          <t>Saknar standardfras om pedagogiskt stöd: Kursen ingår i Grundlärarprogrammet. Kursen motsvarar PG3063. Denna kurs utgör den andra delen av två inom vilka den stu…</t>
         </is>
       </c>
       <c r="E331" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG2LZ</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG246</t>
         </is>
       </c>
     </row>
     <row r="332">
       <c r="A332" s="2" t="inlineStr">
         <is>
-          <t>GPG2M9</t>
+          <t>APG247</t>
         </is>
       </c>
       <c r="B332" t="inlineStr">
@@ -9397,19 +9397,19 @@
       </c>
       <c r="D332" t="inlineStr">
         <is>
-          <t>Saknar standardfras om pedagogiskt stöd: För nätbaserad kurs krävs att den studerande har möjlighet att kommunicera med ljud och bild via en dator eller motsvara…</t>
+          <t>Saknar standardfras om pedagogiskt stöd: Kursen ingår i Grundlärarprogrammet. Kursen motsvarar PG3064. Denna kurs utgör den andra delen av två inom vilka den stu…</t>
         </is>
       </c>
       <c r="E332" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG2M9</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG247</t>
         </is>
       </c>
     </row>
     <row r="333">
       <c r="A333" s="2" t="inlineStr">
         <is>
-          <t>GPG2N7</t>
+          <t>APG24D</t>
         </is>
       </c>
       <c r="B333" t="inlineStr">
@@ -9424,19 +9424,19 @@
       </c>
       <c r="D333" t="inlineStr">
         <is>
-          <t>Saknar standardfras om pedagogiskt stöd: För kursen krävs att den studerande har möjlighet att kommunicera med ljud och bild via en dator eller motsvarande. Kurs…</t>
+          <t>Saknar standardfras om pedagogiskt stöd: Kursen motsvarar PG3033 och PG3066.…</t>
         </is>
       </c>
       <c r="E333" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG2N7</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG24D</t>
         </is>
       </c>
     </row>
     <row r="334">
       <c r="A334" s="2" t="inlineStr">
         <is>
-          <t>GPG2QP</t>
+          <t>APG24E</t>
         </is>
       </c>
       <c r="B334" t="inlineStr">
@@ -9451,19 +9451,19 @@
       </c>
       <c r="D334" t="inlineStr">
         <is>
-          <t>Saknar standardfras om pedagogiskt stöd: Nätbaserad kurs, innehåller obligatoriska campusträffar. Student som underkänts i mål knutna till kursens verksamhetsför…</t>
+          <t>Saknar standardfras om pedagogiskt stöd: Kursen motsvarar PG3036 och PG3060.…</t>
         </is>
       </c>
       <c r="E334" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG2QP</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG24E</t>
         </is>
       </c>
     </row>
     <row r="335">
       <c r="A335" s="2" t="inlineStr">
         <is>
-          <t>GPG2RH</t>
+          <t>APG24S</t>
         </is>
       </c>
       <c r="B335" t="inlineStr">
@@ -9478,19 +9478,19 @@
       </c>
       <c r="D335" t="inlineStr">
         <is>
-          <t>Saknar standardfras om pedagogiskt stöd: Nätbaserad kurs, innehåller obligatoriska campusträffar. Student som underkänts i mål knutna till kursens verksamhetsför…</t>
+          <t>Saknar standardfras om pedagogiskt stöd: I kursen ingår en obligatorisk träff motsvarande maximalt tre dagar på campus. Kursen motsvarar PG3045.…</t>
         </is>
       </c>
       <c r="E335" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG2RH</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG24S</t>
         </is>
       </c>
     </row>
     <row r="336">
       <c r="A336" s="2" t="inlineStr">
         <is>
-          <t>GPG2RR</t>
+          <t>APG25N</t>
         </is>
       </c>
       <c r="B336" t="inlineStr">
@@ -9505,19 +9505,19 @@
       </c>
       <c r="D336" t="inlineStr">
         <is>
-          <t>Saknar standardfras om pedagogiskt stöd: Nätbaserad kurs, innehåller obligatoriska campusträffar.…</t>
+          <t>Saknar standardfras om pedagogiskt stöd: Kursen kan ingå som valbar kurs i magisterprogrammet i pedagogiskt arbete vid Högskolan Dalarna.…</t>
         </is>
       </c>
       <c r="E336" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG2RR</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG25N</t>
         </is>
       </c>
     </row>
     <row r="337">
       <c r="A337" s="2" t="inlineStr">
         <is>
-          <t>GPG2RS</t>
+          <t>APG26D</t>
         </is>
       </c>
       <c r="B337" t="inlineStr">
@@ -9527,24 +9527,24 @@
       </c>
       <c r="C337" t="inlineStr">
         <is>
-          <t>Saknar standardfras om pedagogiskt stöd</t>
+          <t>Sektion saknas</t>
         </is>
       </c>
       <c r="D337" t="inlineStr">
         <is>
-          <t>Saknar standardfras om pedagogiskt stöd: Nätbaserad kurs, innehåller obligatoriska campusträffar. Student som underkänts i mål knutna till kursens verksamhetsför…</t>
+          <t>Ingen Övrigt-sektion i kursplanen</t>
         </is>
       </c>
       <c r="E337" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG2RS</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG26D</t>
         </is>
       </c>
     </row>
     <row r="338">
       <c r="A338" s="2" t="inlineStr">
         <is>
-          <t>GPG2S7</t>
+          <t>APG275</t>
         </is>
       </c>
       <c r="B338" t="inlineStr">
@@ -9559,19 +9559,19 @@
       </c>
       <c r="D338" t="inlineStr">
         <is>
-          <t>Saknar standardfras om pedagogiskt stöd: Nätbaserad kurs, innehåller obligatoriska campusträffar.…</t>
+          <t>Saknar standardfras om pedagogiskt stöd: För nätbaserad kurs ingår en obligatorisk träff om maximalt tre dagar på campus. För nätbaserad kurs krävs att den stude…</t>
         </is>
       </c>
       <c r="E338" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG2S7</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG275</t>
         </is>
       </c>
     </row>
     <row r="339">
       <c r="A339" s="2" t="inlineStr">
         <is>
-          <t>GPG2S8</t>
+          <t>APG276</t>
         </is>
       </c>
       <c r="B339" t="inlineStr">
@@ -9586,19 +9586,19 @@
       </c>
       <c r="D339" t="inlineStr">
         <is>
-          <t>Saknar standardfras om pedagogiskt stöd: Nätbaserad kurs, innehåller obligatoriska campusträffar. Student som underkänts i mål knutna till kursens verksamhetsför…</t>
+          <t>Saknar standardfras om pedagogiskt stöd: För nätbaserad kurs ingår en obligatorisk träff om maximalt tre dagar på campus. För nätbaserad kurs krävs att den stude…</t>
         </is>
       </c>
       <c r="E339" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG2S8</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG276</t>
         </is>
       </c>
     </row>
     <row r="340">
       <c r="A340" s="2" t="inlineStr">
         <is>
-          <t>GPG2S9</t>
+          <t>APG27T</t>
         </is>
       </c>
       <c r="B340" t="inlineStr">
@@ -9613,19 +9613,19 @@
       </c>
       <c r="D340" t="inlineStr">
         <is>
-          <t>Saknar standardfras om pedagogiskt stöd: I kursen ingår en träff på campus under maximalt tre dagar. Kursen motsvarar PG2057 och PG2068.…</t>
+          <t>Saknar standardfras om pedagogiskt stöd: Kursen är en uppdragsutbildning från Skolverket och gäller rektorer som genomgått Rektorsprogrammet med godkänt resultat…</t>
         </is>
       </c>
       <c r="E340" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG2S9</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG27T</t>
         </is>
       </c>
     </row>
     <row r="341">
       <c r="A341" s="2" t="inlineStr">
         <is>
-          <t>GPG2SC</t>
+          <t>APG27U</t>
         </is>
       </c>
       <c r="B341" t="inlineStr">
@@ -9640,19 +9640,19 @@
       </c>
       <c r="D341" t="inlineStr">
         <is>
-          <t>Saknar standardfras om pedagogiskt stöd: Nätbaserad kurs innehåller en obligatorisk campusträff om max tre dagar. I kursen ingår två-tre fältdagar vid en grundsk…</t>
+          <t>Saknar standardfras om pedagogiskt stöd: Kursen ingår i Förskollärarprogrammet. Student som underkänts i mål knutna till kursens verksamhetsförlagda utbildning h…</t>
         </is>
       </c>
       <c r="E341" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG2SC</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG27U</t>
         </is>
       </c>
     </row>
     <row r="342">
       <c r="A342" s="2" t="inlineStr">
         <is>
-          <t>GPG2SG</t>
+          <t>APG27Z</t>
         </is>
       </c>
       <c r="B342" t="inlineStr">
@@ -9662,24 +9662,24 @@
       </c>
       <c r="C342" t="inlineStr">
         <is>
-          <t>Sektion saknas</t>
+          <t>Saknar standardfras om pedagogiskt stöd</t>
         </is>
       </c>
       <c r="D342" t="inlineStr">
         <is>
-          <t>Ingen Övrigt-sektion i kursplanen</t>
+          <t>Saknar standardfras om pedagogiskt stöd: Nätbaserad kurs, innehåller obligatoriska campusträffar. Student som underkänts i mål knutna till kursens verksamhetsför…</t>
         </is>
       </c>
       <c r="E342" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG2SG</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG27Z</t>
         </is>
       </c>
     </row>
     <row r="343">
       <c r="A343" s="2" t="inlineStr">
         <is>
-          <t>GPG2SH</t>
+          <t>APG282</t>
         </is>
       </c>
       <c r="B343" t="inlineStr">
@@ -9689,24 +9689,24 @@
       </c>
       <c r="C343" t="inlineStr">
         <is>
-          <t>Sektion saknas</t>
+          <t>Saknar standardfras om pedagogiskt stöd</t>
         </is>
       </c>
       <c r="D343" t="inlineStr">
         <is>
-          <t>Ingen Övrigt-sektion i kursplanen</t>
+          <t>Saknar standardfras om pedagogiskt stöd: Nätbaserad kurs, innehåller en campusträff då ventilering av självständiga arbeten sker.…</t>
         </is>
       </c>
       <c r="E343" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG2SH</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG282</t>
         </is>
       </c>
     </row>
     <row r="344">
       <c r="A344" s="2" t="inlineStr">
         <is>
-          <t>GPG2TT</t>
+          <t>APG28B</t>
         </is>
       </c>
       <c r="B344" t="inlineStr">
@@ -9716,24 +9716,24 @@
       </c>
       <c r="C344" t="inlineStr">
         <is>
-          <t>Sektion saknas</t>
+          <t>Saknar standardfras om pedagogiskt stöd</t>
         </is>
       </c>
       <c r="D344" t="inlineStr">
         <is>
-          <t>Ingen Övrigt-sektion i kursplanen</t>
+          <t>Saknar standardfras om pedagogiskt stöd: Nätbaserad kurs, innehåller obligatorisk campusträff. Student som underkänts i mål knutna till kursens verksamhetsförlag…</t>
         </is>
       </c>
       <c r="E344" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG2TT</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG28B</t>
         </is>
       </c>
     </row>
     <row r="345">
       <c r="A345" s="2" t="inlineStr">
         <is>
-          <t>GPG2VW</t>
+          <t>GPG22J</t>
         </is>
       </c>
       <c r="B345" t="inlineStr">
@@ -9748,19 +9748,19 @@
       </c>
       <c r="D345" t="inlineStr">
         <is>
-          <t>Saknar standardfras om pedagogiskt stöd: Nätbaserad kurs, innehåller obligatoriska campusträffar.…</t>
+          <t>Saknar standardfras om pedagogiskt stöd: Kursen erbjuds som campus/nät-kurs. För kursdeltagare som medverkar via nätet krävs tillgång till dator med internetuppk…</t>
         </is>
       </c>
       <c r="E345" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG2VW</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG22J</t>
         </is>
       </c>
     </row>
     <row r="346">
       <c r="A346" s="2" t="inlineStr">
         <is>
-          <t>GPG2VX</t>
+          <t>GPG22K</t>
         </is>
       </c>
       <c r="B346" t="inlineStr">
@@ -9775,19 +9775,19 @@
       </c>
       <c r="D346" t="inlineStr">
         <is>
-          <t>Saknar standardfras om pedagogiskt stöd: Nätbaserad kurs, innehåller obligatoriska campusträffar.…</t>
+          <t>Saknar standardfras om pedagogiskt stöd: Kursen ingår i programmet Kompletterande pedagogisk utbildning. Kursen motsvarar PG2066. Kursen avslutas med en obligato…</t>
         </is>
       </c>
       <c r="E346" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG2VX</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG22K</t>
         </is>
       </c>
     </row>
     <row r="347">
       <c r="A347" s="2" t="inlineStr">
         <is>
-          <t>GPG2WR</t>
+          <t>GPG27X</t>
         </is>
       </c>
       <c r="B347" t="inlineStr">
@@ -9802,19 +9802,19 @@
       </c>
       <c r="D347" t="inlineStr">
         <is>
-          <t>Saknar standardfras om pedagogiskt stöd: Nätbaserad kurs, innehåller en campusträff då ventilering av självständiga arbeten sker.…</t>
+          <t>Saknar standardfras om pedagogiskt stöd: Kursen vänder sig till personer med någon form av behörighetsgivande lärar- eller förskollärarexamen som valt att återvä…</t>
         </is>
       </c>
       <c r="E347" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG2WR</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG27X</t>
         </is>
       </c>
     </row>
     <row r="348">
       <c r="A348" s="2" t="inlineStr">
         <is>
-          <t>GPG2YG</t>
+          <t>GPG2E6</t>
         </is>
       </c>
       <c r="B348" t="inlineStr">
@@ -9829,19 +9829,19 @@
       </c>
       <c r="D348" t="inlineStr">
         <is>
-          <t>Saknar standardfras om pedagogiskt stöd: Ersätter GSV22L. I kursen ingår en obligatorisk träff om max två dagar på campus. För nätbaserad kurs krävs att den stud…</t>
+          <t>Saknar standardfras om pedagogiskt stöd: Kursen ingår i Grundlärarprogrammet. Kursen motsvarar PG2069. Denna kurs utgör den första delen av två inom vilka den st…</t>
         </is>
       </c>
       <c r="E348" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG2YG</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG2E6</t>
         </is>
       </c>
     </row>
     <row r="349">
       <c r="A349" s="2" t="inlineStr">
         <is>
-          <t>GPG2YH</t>
+          <t>GPG2E7</t>
         </is>
       </c>
       <c r="B349" t="inlineStr">
@@ -9856,19 +9856,19 @@
       </c>
       <c r="D349" t="inlineStr">
         <is>
-          <t>Saknar standardfras om pedagogiskt stöd: Nätbaserad kurs, innehåller obligatorisk campusträff. Student som underkänts i mål knutna till kursens verksamhetsförlag…</t>
+          <t>Saknar standardfras om pedagogiskt stöd: Kursen ingår i Grundlärarprogrammet. Kursen motsvarar PG2070. Denna kurs utgör den första delen av två inom vilka den st…</t>
         </is>
       </c>
       <c r="E349" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG2YH</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG2E7</t>
         </is>
       </c>
     </row>
     <row r="350">
       <c r="A350" s="2" t="inlineStr">
         <is>
-          <t>PG2043</t>
+          <t>GPG2LZ</t>
         </is>
       </c>
       <c r="B350" t="inlineStr">
@@ -9883,19 +9883,19 @@
       </c>
       <c r="D350" t="inlineStr">
         <is>
-          <t>Saknar standardfras om pedagogiskt stöd: Kursen ingick i huvudområdet pedagogiskt arbete till och med 2015-01-19.…</t>
+          <t>Saknar standardfras om pedagogiskt stöd: För nätbaserad kurs krävs att den studerande har möjlighet att kommunicera med ljud och bild via en dator eller motsvara…</t>
         </is>
       </c>
       <c r="E350" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PG2043</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG2LZ</t>
         </is>
       </c>
     </row>
     <row r="351">
       <c r="A351" s="2" t="inlineStr">
         <is>
-          <t>PG2048</t>
+          <t>GPG2M9</t>
         </is>
       </c>
       <c r="B351" t="inlineStr">
@@ -9915,14 +9915,14 @@
       </c>
       <c r="E351" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PG2048</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG2M9</t>
         </is>
       </c>
     </row>
     <row r="352">
       <c r="A352" s="2" t="inlineStr">
         <is>
-          <t>PG3023</t>
+          <t>GPG2N7</t>
         </is>
       </c>
       <c r="B352" t="inlineStr">
@@ -9937,19 +9937,19 @@
       </c>
       <c r="D352" t="inlineStr">
         <is>
-          <t>Saknar standardfras om pedagogiskt stöd: För nätbaserad kurs krävs att den studerande har möjlighet att kommunicera med ljud och bild via en dator eller motsvara…</t>
+          <t>Saknar standardfras om pedagogiskt stöd: För kursen krävs att den studerande har möjlighet att kommunicera med ljud och bild via en dator eller motsvarande. Kurs…</t>
         </is>
       </c>
       <c r="E352" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PG3023</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG2N7</t>
         </is>
       </c>
     </row>
     <row r="353">
       <c r="A353" s="2" t="inlineStr">
         <is>
-          <t>PG3024</t>
+          <t>GPG2QP</t>
         </is>
       </c>
       <c r="B353" t="inlineStr">
@@ -9964,19 +9964,19 @@
       </c>
       <c r="D353" t="inlineStr">
         <is>
-          <t>Saknar standardfras om pedagogiskt stöd: För nätbaserad kurs krävs att den studerande har möjlighet att kommunicera med ljud och bild via en dator eller motsvara…</t>
+          <t>Saknar standardfras om pedagogiskt stöd: Nätbaserad kurs, innehåller obligatoriska campusträffar. Student som underkänts i mål knutna till kursens verksamhetsför…</t>
         </is>
       </c>
       <c r="E353" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PG3024</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG2QP</t>
         </is>
       </c>
     </row>
     <row r="354">
       <c r="A354" s="2" t="inlineStr">
         <is>
-          <t>PG3025</t>
+          <t>GPG2RH</t>
         </is>
       </c>
       <c r="B354" t="inlineStr">
@@ -9991,19 +9991,19 @@
       </c>
       <c r="D354" t="inlineStr">
         <is>
-          <t>Saknar standardfras om pedagogiskt stöd: För nätbaserad kurs krävs att den studerande har möjlighet att kommunicera med ljud och bild via en dator eller motsvara…</t>
+          <t>Saknar standardfras om pedagogiskt stöd: Nätbaserad kurs, innehåller obligatoriska campusträffar. Student som underkänts i mål knutna till kursens verksamhetsför…</t>
         </is>
       </c>
       <c r="E354" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PG3025</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG2RH</t>
         </is>
       </c>
     </row>
     <row r="355">
       <c r="A355" s="2" t="inlineStr">
         <is>
-          <t>PG3031</t>
+          <t>GPG2RR</t>
         </is>
       </c>
       <c r="B355" t="inlineStr">
@@ -10013,24 +10013,24 @@
       </c>
       <c r="C355" t="inlineStr">
         <is>
-          <t>Sektion saknas</t>
+          <t>Saknar standardfras om pedagogiskt stöd</t>
         </is>
       </c>
       <c r="D355" t="inlineStr">
         <is>
-          <t>Ingen Övrigt-sektion i kursplanen</t>
+          <t>Saknar standardfras om pedagogiskt stöd: Nätbaserad kurs, innehåller obligatoriska campusträffar.…</t>
         </is>
       </c>
       <c r="E355" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PG3031</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG2RR</t>
         </is>
       </c>
     </row>
     <row r="356">
       <c r="A356" s="2" t="inlineStr">
         <is>
-          <t>PG3041</t>
+          <t>GPG2RS</t>
         </is>
       </c>
       <c r="B356" t="inlineStr">
@@ -10045,19 +10045,19 @@
       </c>
       <c r="D356" t="inlineStr">
         <is>
-          <t>Saknar standardfras om pedagogiskt stöd: Kursen motsvarar PG3016.…</t>
+          <t>Saknar standardfras om pedagogiskt stöd: Nätbaserad kurs, innehåller obligatoriska campusträffar. Student som underkänts i mål knutna till kursens verksamhetsför…</t>
         </is>
       </c>
       <c r="E356" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PG3041</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG2RS</t>
         </is>
       </c>
     </row>
     <row r="357">
       <c r="A357" s="2" t="inlineStr">
         <is>
-          <t>PG3056</t>
+          <t>GPG2S7</t>
         </is>
       </c>
       <c r="B357" t="inlineStr">
@@ -10072,19 +10072,19 @@
       </c>
       <c r="D357" t="inlineStr">
         <is>
-          <t>Saknar standardfras om pedagogiskt stöd: För nätbaserad kurs krävs att den studerande har möjlighet att kommunicera med ljud och bild via en dator eller motsvara…</t>
+          <t>Saknar standardfras om pedagogiskt stöd: Nätbaserad kurs, innehåller obligatoriska campusträffar.…</t>
         </is>
       </c>
       <c r="E357" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PG3056</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG2S7</t>
         </is>
       </c>
     </row>
     <row r="358">
       <c r="A358" s="2" t="inlineStr">
         <is>
-          <t>PG3061</t>
+          <t>GPG2S8</t>
         </is>
       </c>
       <c r="B358" t="inlineStr">
@@ -10099,19 +10099,19 @@
       </c>
       <c r="D358" t="inlineStr">
         <is>
-          <t>Saknar standardfras om pedagogiskt stöd: Kursen ingår i Magisterprogram i pedagogiskt arbete.…</t>
+          <t>Saknar standardfras om pedagogiskt stöd: Nätbaserad kurs, innehåller obligatoriska campusträffar. Student som underkänts i mål knutna till kursens verksamhetsför…</t>
         </is>
       </c>
       <c r="E358" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PG3061</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG2S8</t>
         </is>
       </c>
     </row>
     <row r="359">
       <c r="A359" s="2" t="inlineStr">
         <is>
-          <t>PG3065</t>
+          <t>GPG2S9</t>
         </is>
       </c>
       <c r="B359" t="inlineStr">
@@ -10126,19 +10126,19 @@
       </c>
       <c r="D359" t="inlineStr">
         <is>
-          <t>Saknar standardfras om pedagogiskt stöd: För nätbaserad kurs krävs att den studerande har möjlighet att kommunicera med ljud och bild via en dator eller motsvara…</t>
+          <t>Saknar standardfras om pedagogiskt stöd: I kursen ingår en träff på campus under maximalt tre dagar. Kursen motsvarar PG2057 och PG2068.…</t>
         </is>
       </c>
       <c r="E359" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PG3065</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG2S9</t>
         </is>
       </c>
     </row>
     <row r="360">
       <c r="A360" s="2" t="inlineStr">
         <is>
-          <t>PG3069</t>
+          <t>GPG2SC</t>
         </is>
       </c>
       <c r="B360" t="inlineStr">
@@ -10153,105 +10153,105 @@
       </c>
       <c r="D360" t="inlineStr">
         <is>
-          <t>Saknar standardfras om pedagogiskt stöd: Kursen ingår i Magisterprogram i pedagogiskt arbete. Kursen motsvarar PG3059.…</t>
+          <t>Saknar standardfras om pedagogiskt stöd: Nätbaserad kurs innehåller en obligatorisk campusträff om max tre dagar. I kursen ingår två-tre fältdagar vid en grundsk…</t>
         </is>
       </c>
       <c r="E360" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PG3069</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG2SC</t>
         </is>
       </c>
     </row>
     <row r="361">
       <c r="A361" s="2" t="inlineStr">
         <is>
-          <t>ARK227</t>
+          <t>GPG2SG</t>
         </is>
       </c>
       <c r="B361" t="inlineStr">
         <is>
-          <t>RKA</t>
+          <t>PGA</t>
         </is>
       </c>
       <c r="C361" t="inlineStr">
         <is>
-          <t>Saknar standardfras om pedagogiskt stöd</t>
+          <t>Sektion saknas</t>
         </is>
       </c>
       <c r="D361" t="inlineStr">
         <is>
-          <t>Saknar standardfras om pedagogiskt stöd: Ersätter RK3015. Motsvarar RK3038, AS3007 och AS3015.…</t>
+          <t>Ingen Övrigt-sektion i kursplanen</t>
         </is>
       </c>
       <c r="E361" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ARK227</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG2SG</t>
         </is>
       </c>
     </row>
     <row r="362">
       <c r="A362" s="2" t="inlineStr">
         <is>
-          <t>ARK25B</t>
+          <t>GPG2SH</t>
         </is>
       </c>
       <c r="B362" t="inlineStr">
         <is>
-          <t>RKA</t>
+          <t>PGA</t>
         </is>
       </c>
       <c r="C362" t="inlineStr">
         <is>
-          <t>Saknar standardfras om pedagogiskt stöd</t>
+          <t>Sektion saknas</t>
         </is>
       </c>
       <c r="D362" t="inlineStr">
         <is>
-          <t>Saknar standardfras om pedagogiskt stöd: För nätbaserad kurs krävs tillgång till dator, headset, webbkamera och internetuppkoppling, eller motsvarande funktionse…</t>
+          <t>Ingen Övrigt-sektion i kursplanen</t>
         </is>
       </c>
       <c r="E362" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ARK25B</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG2SH</t>
         </is>
       </c>
     </row>
     <row r="363">
       <c r="A363" s="2" t="inlineStr">
         <is>
-          <t>ARK25C</t>
+          <t>GPG2TT</t>
         </is>
       </c>
       <c r="B363" t="inlineStr">
         <is>
-          <t>RKA</t>
+          <t>PGA</t>
         </is>
       </c>
       <c r="C363" t="inlineStr">
         <is>
-          <t>Saknar standardfras om pedagogiskt stöd</t>
+          <t>Sektion saknas</t>
         </is>
       </c>
       <c r="D363" t="inlineStr">
         <is>
-          <t>Saknar standardfras om pedagogiskt stöd: För nätbaserad kurs krävs tillgång till dator, headset, webbkamera och internetuppkoppling, eller motsvarande funktionse…</t>
+          <t>Ingen Övrigt-sektion i kursplanen</t>
         </is>
       </c>
       <c r="E363" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ARK25C</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG2TT</t>
         </is>
       </c>
     </row>
     <row r="364">
       <c r="A364" s="2" t="inlineStr">
         <is>
-          <t>ARK262</t>
+          <t>GPG2VW</t>
         </is>
       </c>
       <c r="B364" t="inlineStr">
         <is>
-          <t>RKA</t>
+          <t>PGA</t>
         </is>
       </c>
       <c r="C364" t="inlineStr">
@@ -10261,24 +10261,24 @@
       </c>
       <c r="D364" t="inlineStr">
         <is>
-          <t>Saknar standardfras om pedagogiskt stöd: För nätbaserad kurs krävs att den studerande kan kommunicera med ljud och bild via en dator eller motsvarande.…</t>
+          <t>Saknar standardfras om pedagogiskt stöd: Nätbaserad kurs, innehåller obligatoriska campusträffar.…</t>
         </is>
       </c>
       <c r="E364" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ARK262</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG2VW</t>
         </is>
       </c>
     </row>
     <row r="365">
       <c r="A365" s="2" t="inlineStr">
         <is>
-          <t>ARK26T</t>
+          <t>GPG2VX</t>
         </is>
       </c>
       <c r="B365" t="inlineStr">
         <is>
-          <t>RKA</t>
+          <t>PGA</t>
         </is>
       </c>
       <c r="C365" t="inlineStr">
@@ -10288,24 +10288,24 @@
       </c>
       <c r="D365" t="inlineStr">
         <is>
-          <t>Saknar standardfras om pedagogiskt stöd: För nätbaserad kurs krävs att den studerande kan kommunicera med ljud och bild via en dator eller motsvarande.…</t>
+          <t>Saknar standardfras om pedagogiskt stöd: Nätbaserad kurs, innehåller obligatoriska campusträffar.…</t>
         </is>
       </c>
       <c r="E365" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ARK26T</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG2VX</t>
         </is>
       </c>
     </row>
     <row r="366">
       <c r="A366" s="2" t="inlineStr">
         <is>
-          <t>ARK27Q</t>
+          <t>GPG2WR</t>
         </is>
       </c>
       <c r="B366" t="inlineStr">
         <is>
-          <t>RKA</t>
+          <t>PGA</t>
         </is>
       </c>
       <c r="C366" t="inlineStr">
@@ -10315,24 +10315,24 @@
       </c>
       <c r="D366" t="inlineStr">
         <is>
-          <t>Saknar standardfras om pedagogiskt stöd: För nätbaserad kurs krävs att studenten kan kommunicera med ljud och bild via en dator eller motsvarande utrustning.…</t>
+          <t>Saknar standardfras om pedagogiskt stöd: Nätbaserad kurs, innehåller en campusträff då ventilering av självständiga arbeten sker.…</t>
         </is>
       </c>
       <c r="E366" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ARK27Q</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG2WR</t>
         </is>
       </c>
     </row>
     <row r="367">
       <c r="A367" s="2" t="inlineStr">
         <is>
-          <t>GRK2EF</t>
+          <t>GPG2YG</t>
         </is>
       </c>
       <c r="B367" t="inlineStr">
         <is>
-          <t>RKA</t>
+          <t>PGA</t>
         </is>
       </c>
       <c r="C367" t="inlineStr">
@@ -10342,24 +10342,24 @@
       </c>
       <c r="D367" t="inlineStr">
         <is>
-          <t>Saknar standardfras om pedagogiskt stöd: Då kursen är nätbaserad krävs dator, headset, webbkamera och Internetuppkoppling. Kursen kan ej ingå i en examen samtidi…</t>
+          <t>Saknar standardfras om pedagogiskt stöd: Ersätter GSV22L. I kursen ingår en obligatorisk träff om max två dagar på campus. För nätbaserad kurs krävs att den stud…</t>
         </is>
       </c>
       <c r="E367" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRK2EF</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG2YG</t>
         </is>
       </c>
     </row>
     <row r="368">
       <c r="A368" s="2" t="inlineStr">
         <is>
-          <t>GRK2JJ</t>
+          <t>GPG2YH</t>
         </is>
       </c>
       <c r="B368" t="inlineStr">
         <is>
-          <t>RKA</t>
+          <t>PGA</t>
         </is>
       </c>
       <c r="C368" t="inlineStr">
@@ -10369,24 +10369,24 @@
       </c>
       <c r="D368" t="inlineStr">
         <is>
-          <t>Saknar standardfras om pedagogiskt stöd: För nätbaserad kurs krävs att den studerande kan kommunicera med ljud och bild via en dator eller motsvarande.…</t>
+          <t>Saknar standardfras om pedagogiskt stöd: Nätbaserad kurs, innehåller obligatorisk campusträff. Student som underkänts i mål knutna till kursens verksamhetsförlag…</t>
         </is>
       </c>
       <c r="E368" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRK2JJ</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG2YH</t>
         </is>
       </c>
     </row>
     <row r="369">
       <c r="A369" s="2" t="inlineStr">
         <is>
-          <t>GRK2JK</t>
+          <t>PG2043</t>
         </is>
       </c>
       <c r="B369" t="inlineStr">
         <is>
-          <t>RKA</t>
+          <t>PGA</t>
         </is>
       </c>
       <c r="C369" t="inlineStr">
@@ -10396,24 +10396,24 @@
       </c>
       <c r="D369" t="inlineStr">
         <is>
-          <t>Saknar standardfras om pedagogiskt stöd: För nätbaserad kurs krävs att den studerande kan kommunicera med ljud och bild via en dator eller motsvarande.…</t>
+          <t>Saknar standardfras om pedagogiskt stöd: Kursen ingick i huvudområdet pedagogiskt arbete till och med 2015-01-19.…</t>
         </is>
       </c>
       <c r="E369" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRK2JK</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PG2043</t>
         </is>
       </c>
     </row>
     <row r="370">
       <c r="A370" s="2" t="inlineStr">
         <is>
-          <t>GRK2KL</t>
+          <t>PG2048</t>
         </is>
       </c>
       <c r="B370" t="inlineStr">
         <is>
-          <t>RKA</t>
+          <t>PGA</t>
         </is>
       </c>
       <c r="C370" t="inlineStr">
@@ -10423,24 +10423,24 @@
       </c>
       <c r="D370" t="inlineStr">
         <is>
-          <t>Saknar standardfras om pedagogiskt stöd: All undervisning är nätbaserad. Seminarier och föreläsningar är schemalagda på bestämda tider och seminarierna förutsätt…</t>
+          <t>Saknar standardfras om pedagogiskt stöd: För nätbaserad kurs krävs att den studerande har möjlighet att kommunicera med ljud och bild via en dator eller motsvara…</t>
         </is>
       </c>
       <c r="E370" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRK2KL</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PG2048</t>
         </is>
       </c>
     </row>
     <row r="371">
       <c r="A371" s="2" t="inlineStr">
         <is>
-          <t>GRK2P3</t>
+          <t>PG3023</t>
         </is>
       </c>
       <c r="B371" t="inlineStr">
         <is>
-          <t>RKA</t>
+          <t>PGA</t>
         </is>
       </c>
       <c r="C371" t="inlineStr">
@@ -10450,24 +10450,24 @@
       </c>
       <c r="D371" t="inlineStr">
         <is>
-          <t>Saknar standardfras om pedagogiskt stöd: Kursen kan inte användas i en examen tillsammans med kurserna _Religionsvetenskap III_, 30 hp och _Religionsvetenskap II…</t>
+          <t>Saknar standardfras om pedagogiskt stöd: För nätbaserad kurs krävs att den studerande har möjlighet att kommunicera med ljud och bild via en dator eller motsvara…</t>
         </is>
       </c>
       <c r="E371" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRK2P3</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PG3023</t>
         </is>
       </c>
     </row>
     <row r="372">
       <c r="A372" s="2" t="inlineStr">
         <is>
-          <t>GRK2P4</t>
+          <t>PG3024</t>
         </is>
       </c>
       <c r="B372" t="inlineStr">
         <is>
-          <t>RKA</t>
+          <t>PGA</t>
         </is>
       </c>
       <c r="C372" t="inlineStr">
@@ -10477,24 +10477,24 @@
       </c>
       <c r="D372" t="inlineStr">
         <is>
-          <t>Saknar standardfras om pedagogiskt stöd: Ersätter GRK2CD.…</t>
+          <t>Saknar standardfras om pedagogiskt stöd: För nätbaserad kurs krävs att den studerande har möjlighet att kommunicera med ljud och bild via en dator eller motsvara…</t>
         </is>
       </c>
       <c r="E372" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRK2P4</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PG3024</t>
         </is>
       </c>
     </row>
     <row r="373">
       <c r="A373" s="2" t="inlineStr">
         <is>
-          <t>GRK2Q4</t>
+          <t>PG3025</t>
         </is>
       </c>
       <c r="B373" t="inlineStr">
         <is>
-          <t>RKA</t>
+          <t>PGA</t>
         </is>
       </c>
       <c r="C373" t="inlineStr">
@@ -10504,51 +10504,51 @@
       </c>
       <c r="D373" t="inlineStr">
         <is>
-          <t>Saknar standardfras om pedagogiskt stöd: För nätbaserad kurs krävs att den studerande kan kommunicera med ljud och bild via en dator eller motsvarande. Ersätter …</t>
+          <t>Saknar standardfras om pedagogiskt stöd: För nätbaserad kurs krävs att den studerande har möjlighet att kommunicera med ljud och bild via en dator eller motsvara…</t>
         </is>
       </c>
       <c r="E373" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRK2Q4</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PG3025</t>
         </is>
       </c>
     </row>
     <row r="374">
       <c r="A374" s="2" t="inlineStr">
         <is>
-          <t>GRK2Q5</t>
+          <t>PG3031</t>
         </is>
       </c>
       <c r="B374" t="inlineStr">
         <is>
-          <t>RKA</t>
+          <t>PGA</t>
         </is>
       </c>
       <c r="C374" t="inlineStr">
         <is>
-          <t>Saknar standardfras om pedagogiskt stöd</t>
+          <t>Sektion saknas</t>
         </is>
       </c>
       <c r="D374" t="inlineStr">
         <is>
-          <t>Saknar standardfras om pedagogiskt stöd: Om den nätbaserade kursen läses som första ämne inom ämneslärarprogrammet krävs närvaro i Falun vid terminsstart under m…</t>
+          <t>Ingen Övrigt-sektion i kursplanen</t>
         </is>
       </c>
       <c r="E374" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRK2Q5</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PG3031</t>
         </is>
       </c>
     </row>
     <row r="375">
       <c r="A375" s="2" t="inlineStr">
         <is>
-          <t>GRK2R7</t>
+          <t>PG3041</t>
         </is>
       </c>
       <c r="B375" t="inlineStr">
         <is>
-          <t>RKA</t>
+          <t>PGA</t>
         </is>
       </c>
       <c r="C375" t="inlineStr">
@@ -10558,24 +10558,24 @@
       </c>
       <c r="D375" t="inlineStr">
         <is>
-          <t>Saknar standardfras om pedagogiskt stöd: Motsvarar delkurs 5 _Uppsats_, 15 hp i kursen _Religionsvetenskap III_, 30 hp (GRK25S). Ersätter GRK2NZ.…</t>
+          <t>Saknar standardfras om pedagogiskt stöd: Kursen motsvarar PG3016.…</t>
         </is>
       </c>
       <c r="E375" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRK2R7</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PG3041</t>
         </is>
       </c>
     </row>
     <row r="376">
       <c r="A376" s="2" t="inlineStr">
         <is>
-          <t>GRK2R8</t>
+          <t>PG3056</t>
         </is>
       </c>
       <c r="B376" t="inlineStr">
         <is>
-          <t>RKA</t>
+          <t>PGA</t>
         </is>
       </c>
       <c r="C376" t="inlineStr">
@@ -10585,24 +10585,24 @@
       </c>
       <c r="D376" t="inlineStr">
         <is>
-          <t>Saknar standardfras om pedagogiskt stöd: Motsvarar delkurs 3 _Examensarbete_, 15 hp i kursen _Religionsvetenskap III med examensarbete för kandidatexamen_, 30 hp…</t>
+          <t>Saknar standardfras om pedagogiskt stöd: För nätbaserad kurs krävs att den studerande har möjlighet att kommunicera med ljud och bild via en dator eller motsvara…</t>
         </is>
       </c>
       <c r="E376" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRK2R8</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PG3056</t>
         </is>
       </c>
     </row>
     <row r="377">
       <c r="A377" s="2" t="inlineStr">
         <is>
-          <t>GRK2TW</t>
+          <t>PG3061</t>
         </is>
       </c>
       <c r="B377" t="inlineStr">
         <is>
-          <t>RKA</t>
+          <t>PGA</t>
         </is>
       </c>
       <c r="C377" t="inlineStr">
@@ -10612,24 +10612,24 @@
       </c>
       <c r="D377" t="inlineStr">
         <is>
-          <t>Saknar standardfras om pedagogiskt stöd: För nätbaserad kurs krävs tillgång till dator, headset eller bordsmikrofon, webkamera och internetuppkoppling.…</t>
+          <t>Saknar standardfras om pedagogiskt stöd: Kursen ingår i Magisterprogram i pedagogiskt arbete.…</t>
         </is>
       </c>
       <c r="E377" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRK2TW</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PG3061</t>
         </is>
       </c>
     </row>
     <row r="378">
       <c r="A378" s="2" t="inlineStr">
         <is>
-          <t>GRK2TY</t>
+          <t>PG3065</t>
         </is>
       </c>
       <c r="B378" t="inlineStr">
         <is>
-          <t>RKA</t>
+          <t>PGA</t>
         </is>
       </c>
       <c r="C378" t="inlineStr">
@@ -10639,24 +10639,24 @@
       </c>
       <c r="D378" t="inlineStr">
         <is>
-          <t>Saknar standardfras om pedagogiskt stöd: För nätbaserad kurs krävs tillgång till dator, headset, webbkamera och internetuppkoppling. Ersätter GRK2DM.…</t>
+          <t>Saknar standardfras om pedagogiskt stöd: För nätbaserad kurs krävs att den studerande har möjlighet att kommunicera med ljud och bild via en dator eller motsvara…</t>
         </is>
       </c>
       <c r="E378" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRK2TY</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PG3065</t>
         </is>
       </c>
     </row>
     <row r="379">
       <c r="A379" s="2" t="inlineStr">
         <is>
-          <t>GRK2TZ</t>
+          <t>PG3069</t>
         </is>
       </c>
       <c r="B379" t="inlineStr">
         <is>
-          <t>RKA</t>
+          <t>PGA</t>
         </is>
       </c>
       <c r="C379" t="inlineStr">
@@ -10666,19 +10666,19 @@
       </c>
       <c r="D379" t="inlineStr">
         <is>
-          <t>Saknar standardfras om pedagogiskt stöd: Kursen innehåller två till tre fältdagar vid en grund- eller gymnasieskola. Kursen innehåller två till tre obligatoriska…</t>
+          <t>Saknar standardfras om pedagogiskt stöd: Kursen ingår i Magisterprogram i pedagogiskt arbete. Kursen motsvarar PG3059.…</t>
         </is>
       </c>
       <c r="E379" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRK2TZ</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PG3069</t>
         </is>
       </c>
     </row>
     <row r="380">
       <c r="A380" s="2" t="inlineStr">
         <is>
-          <t>RK1068</t>
+          <t>ARK227</t>
         </is>
       </c>
       <c r="B380" t="inlineStr">
@@ -10688,24 +10688,24 @@
       </c>
       <c r="C380" t="inlineStr">
         <is>
-          <t>Sektion saknas</t>
+          <t>Saknar standardfras om pedagogiskt stöd</t>
         </is>
       </c>
       <c r="D380" t="inlineStr">
         <is>
-          <t>Ingen Övrigt-sektion i kursplanen</t>
+          <t>Saknar standardfras om pedagogiskt stöd: Ersätter RK3015. Motsvarar RK3038, AS3007 och AS3015.…</t>
         </is>
       </c>
       <c r="E380" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RK1068</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ARK227</t>
         </is>
       </c>
     </row>
     <row r="381">
       <c r="A381" s="2" t="inlineStr">
         <is>
-          <t>RK2034</t>
+          <t>ARK25B</t>
         </is>
       </c>
       <c r="B381" t="inlineStr">
@@ -10720,19 +10720,19 @@
       </c>
       <c r="D381" t="inlineStr">
         <is>
-          <t>Saknar standardfras om pedagogiskt stöd: All undervisning är nätbaserad. Seminarier och föreläsningar är schemalagda på bestämda tider och seminarierna förutsätt…</t>
+          <t>Saknar standardfras om pedagogiskt stöd: För nätbaserad kurs krävs tillgång till dator, headset, webbkamera och internetuppkoppling, eller motsvarande funktionse…</t>
         </is>
       </c>
       <c r="E381" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RK2034</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ARK25B</t>
         </is>
       </c>
     </row>
     <row r="382">
       <c r="A382" s="2" t="inlineStr">
         <is>
-          <t>RK2038</t>
+          <t>ARK25C</t>
         </is>
       </c>
       <c r="B382" t="inlineStr">
@@ -10747,19 +10747,19 @@
       </c>
       <c r="D382" t="inlineStr">
         <is>
-          <t>Saknar standardfras om pedagogiskt stöd: All undervisning är nätbaserad. Seminarier och föreläsningar är schemalagda på bestämda tider och seminarierna förutsätt…</t>
+          <t>Saknar standardfras om pedagogiskt stöd: För nätbaserad kurs krävs tillgång till dator, headset, webbkamera och internetuppkoppling, eller motsvarande funktionse…</t>
         </is>
       </c>
       <c r="E382" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RK2038</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ARK25C</t>
         </is>
       </c>
     </row>
     <row r="383">
       <c r="A383" s="2" t="inlineStr">
         <is>
-          <t>RK3043</t>
+          <t>ARK262</t>
         </is>
       </c>
       <c r="B383" t="inlineStr">
@@ -10774,51 +10774,51 @@
       </c>
       <c r="D383" t="inlineStr">
         <is>
-          <t>Saknar standardfras om pedagogiskt stöd: Eftersom kursen är nätbaserad krävs tillgång till dator, headset, webbkamera och internetuppkoppling.…</t>
+          <t>Saknar standardfras om pedagogiskt stöd: För nätbaserad kurs krävs att den studerande kan kommunicera med ljud och bild via en dator eller motsvarande.…</t>
         </is>
       </c>
       <c r="E383" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RK3043</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ARK262</t>
         </is>
       </c>
     </row>
     <row r="384">
       <c r="A384" s="2" t="inlineStr">
         <is>
-          <t>GRV22R</t>
+          <t>ARK26T</t>
         </is>
       </c>
       <c r="B384" t="inlineStr">
         <is>
-          <t>RVA</t>
+          <t>RKA</t>
         </is>
       </c>
       <c r="C384" t="inlineStr">
         <is>
-          <t>Sektion saknas</t>
+          <t>Saknar standardfras om pedagogiskt stöd</t>
         </is>
       </c>
       <c r="D384" t="inlineStr">
         <is>
-          <t>Ingen Övrigt-sektion i kursplanen</t>
+          <t>Saknar standardfras om pedagogiskt stöd: För nätbaserad kurs krävs att den studerande kan kommunicera med ljud och bild via en dator eller motsvarande.…</t>
         </is>
       </c>
       <c r="E384" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRV22R</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ARK26T</t>
         </is>
       </c>
     </row>
     <row r="385">
       <c r="A385" s="2" t="inlineStr">
         <is>
-          <t>GRV266</t>
+          <t>ARK27Q</t>
         </is>
       </c>
       <c r="B385" t="inlineStr">
         <is>
-          <t>RVA</t>
+          <t>RKA</t>
         </is>
       </c>
       <c r="C385" t="inlineStr">
@@ -10828,24 +10828,24 @@
       </c>
       <c r="D385" t="inlineStr">
         <is>
-          <t>Saknar standardfras om pedagogiskt stöd: Studenten har rätt till fyra omtentamenstillfällen. Kursen ersätter RV1003.…</t>
+          <t>Saknar standardfras om pedagogiskt stöd: För nätbaserad kurs krävs att studenten kan kommunicera med ljud och bild via en dator eller motsvarande utrustning.…</t>
         </is>
       </c>
       <c r="E385" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRV266</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ARK27Q</t>
         </is>
       </c>
     </row>
     <row r="386">
       <c r="A386" s="2" t="inlineStr">
         <is>
-          <t>GRV2CE</t>
+          <t>GRK2EF</t>
         </is>
       </c>
       <c r="B386" t="inlineStr">
         <is>
-          <t>RVA</t>
+          <t>RKA</t>
         </is>
       </c>
       <c r="C386" t="inlineStr">
@@ -10855,51 +10855,51 @@
       </c>
       <c r="D386" t="inlineStr">
         <is>
-          <t>Saknar standardfras om pedagogiskt stöd: Ersätter RV1055.…</t>
+          <t>Saknar standardfras om pedagogiskt stöd: Då kursen är nätbaserad krävs dator, headset, webbkamera och Internetuppkoppling. Kursen kan ej ingå i en examen samtidi…</t>
         </is>
       </c>
       <c r="E386" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRV2CE</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRK2EF</t>
         </is>
       </c>
     </row>
     <row r="387">
       <c r="A387" s="2" t="inlineStr">
         <is>
-          <t>GRV2FC</t>
+          <t>GRK2JJ</t>
         </is>
       </c>
       <c r="B387" t="inlineStr">
         <is>
-          <t>RVA</t>
+          <t>RKA</t>
         </is>
       </c>
       <c r="C387" t="inlineStr">
         <is>
-          <t>Sektion saknas</t>
+          <t>Saknar standardfras om pedagogiskt stöd</t>
         </is>
       </c>
       <c r="D387" t="inlineStr">
         <is>
-          <t>Ingen Övrigt-sektion i kursplanen</t>
+          <t>Saknar standardfras om pedagogiskt stöd: För nätbaserad kurs krävs att den studerande kan kommunicera med ljud och bild via en dator eller motsvarande.…</t>
         </is>
       </c>
       <c r="E387" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRV2FC</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRK2JJ</t>
         </is>
       </c>
     </row>
     <row r="388">
       <c r="A388" s="2" t="inlineStr">
         <is>
-          <t>GRV2MK</t>
+          <t>GRK2JK</t>
         </is>
       </c>
       <c r="B388" t="inlineStr">
         <is>
-          <t>RVA</t>
+          <t>RKA</t>
         </is>
       </c>
       <c r="C388" t="inlineStr">
@@ -10909,24 +10909,24 @@
       </c>
       <c r="D388" t="inlineStr">
         <is>
-          <t>Saknar standardfras om pedagogiskt stöd: Kursen ersätter GRV2CE.…</t>
+          <t>Saknar standardfras om pedagogiskt stöd: För nätbaserad kurs krävs att den studerande kan kommunicera med ljud och bild via en dator eller motsvarande.…</t>
         </is>
       </c>
       <c r="E388" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRV2MK</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRK2JK</t>
         </is>
       </c>
     </row>
     <row r="389">
       <c r="A389" s="2" t="inlineStr">
         <is>
-          <t>RV1001</t>
+          <t>GRK2KL</t>
         </is>
       </c>
       <c r="B389" t="inlineStr">
         <is>
-          <t>RVA</t>
+          <t>RKA</t>
         </is>
       </c>
       <c r="C389" t="inlineStr">
@@ -10936,24 +10936,24 @@
       </c>
       <c r="D389" t="inlineStr">
         <is>
-          <t>Saknar standardfras om pedagogiskt stöd: Studenten har rätt till fyra omtentamenstillfällen. Kursen ersätter RVA021.…</t>
+          <t>Saknar standardfras om pedagogiskt stöd: All undervisning är nätbaserad. Seminarier och föreläsningar är schemalagda på bestämda tider och seminarierna förutsätt…</t>
         </is>
       </c>
       <c r="E389" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1001</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRK2KL</t>
         </is>
       </c>
     </row>
     <row r="390">
       <c r="A390" s="2" t="inlineStr">
         <is>
-          <t>RV1002</t>
+          <t>GRK2P3</t>
         </is>
       </c>
       <c r="B390" t="inlineStr">
         <is>
-          <t>RVA</t>
+          <t>RKA</t>
         </is>
       </c>
       <c r="C390" t="inlineStr">
@@ -10963,24 +10963,24 @@
       </c>
       <c r="D390" t="inlineStr">
         <is>
-          <t>Saknar standardfras om pedagogiskt stöd: Studenten har rätt till fyra omtentamenstillfällen. Kursen ersätter RVA045…</t>
+          <t>Saknar standardfras om pedagogiskt stöd: Kursen kan inte användas i en examen tillsammans med kurserna _Religionsvetenskap III_, 30 hp och _Religionsvetenskap II…</t>
         </is>
       </c>
       <c r="E390" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1002</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRK2P3</t>
         </is>
       </c>
     </row>
     <row r="391">
       <c r="A391" s="2" t="inlineStr">
         <is>
-          <t>RV1003</t>
+          <t>GRK2P4</t>
         </is>
       </c>
       <c r="B391" t="inlineStr">
         <is>
-          <t>RVA</t>
+          <t>RKA</t>
         </is>
       </c>
       <c r="C391" t="inlineStr">
@@ -10990,24 +10990,24 @@
       </c>
       <c r="D391" t="inlineStr">
         <is>
-          <t>Saknar standardfras om pedagogiskt stöd: Studenten har rätt till fyra omtentamenstillfällen. Kursen ersätter RVA044…</t>
+          <t>Saknar standardfras om pedagogiskt stöd: Ersätter GRK2CD.…</t>
         </is>
       </c>
       <c r="E391" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1003</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRK2P4</t>
         </is>
       </c>
     </row>
     <row r="392">
       <c r="A392" s="2" t="inlineStr">
         <is>
-          <t>RV1004</t>
+          <t>GRK2Q4</t>
         </is>
       </c>
       <c r="B392" t="inlineStr">
         <is>
-          <t>RVA</t>
+          <t>RKA</t>
         </is>
       </c>
       <c r="C392" t="inlineStr">
@@ -11017,24 +11017,24 @@
       </c>
       <c r="D392" t="inlineStr">
         <is>
-          <t>Saknar standardfras om pedagogiskt stöd: Studenten har rätt till fyra omtentamenstillfällen. Kursen ersätter RVA008…</t>
+          <t>Saknar standardfras om pedagogiskt stöd: För nätbaserad kurs krävs att den studerande kan kommunicera med ljud och bild via en dator eller motsvarande. Ersätter …</t>
         </is>
       </c>
       <c r="E392" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1004</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRK2Q4</t>
         </is>
       </c>
     </row>
     <row r="393">
       <c r="A393" s="2" t="inlineStr">
         <is>
-          <t>RV1009</t>
+          <t>GRK2Q5</t>
         </is>
       </c>
       <c r="B393" t="inlineStr">
         <is>
-          <t>RVA</t>
+          <t>RKA</t>
         </is>
       </c>
       <c r="C393" t="inlineStr">
@@ -11044,24 +11044,24 @@
       </c>
       <c r="D393" t="inlineStr">
         <is>
-          <t>Saknar standardfras om pedagogiskt stöd: Studenten har rätt till fyra omtentamenstillfällen. Ersätter RVA 050…</t>
+          <t>Saknar standardfras om pedagogiskt stöd: Om den nätbaserade kursen läses som första ämne inom ämneslärarprogrammet krävs närvaro i Falun vid terminsstart under m…</t>
         </is>
       </c>
       <c r="E393" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1009</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRK2Q5</t>
         </is>
       </c>
     </row>
     <row r="394">
       <c r="A394" s="2" t="inlineStr">
         <is>
-          <t>RV1015</t>
+          <t>GRK2R7</t>
         </is>
       </c>
       <c r="B394" t="inlineStr">
         <is>
-          <t>RVA</t>
+          <t>RKA</t>
         </is>
       </c>
       <c r="C394" t="inlineStr">
@@ -11071,24 +11071,24 @@
       </c>
       <c r="D394" t="inlineStr">
         <is>
-          <t>Saknar standardfras om pedagogiskt stöd: Ersätter IEA023…</t>
+          <t>Saknar standardfras om pedagogiskt stöd: Motsvarar delkurs 5 _Uppsats_, 15 hp i kursen _Religionsvetenskap III_, 30 hp (GRK25S). Ersätter GRK2NZ.…</t>
         </is>
       </c>
       <c r="E394" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1015</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRK2R7</t>
         </is>
       </c>
     </row>
     <row r="395">
       <c r="A395" s="2" t="inlineStr">
         <is>
-          <t>RV1026</t>
+          <t>GRK2R8</t>
         </is>
       </c>
       <c r="B395" t="inlineStr">
         <is>
-          <t>RVA</t>
+          <t>RKA</t>
         </is>
       </c>
       <c r="C395" t="inlineStr">
@@ -11098,24 +11098,24 @@
       </c>
       <c r="D395" t="inlineStr">
         <is>
-          <t>Saknar standardfras om pedagogiskt stöd: Studenten har rätt till fyra omtentamenstillfällen. Kursen ersätter RVA002…</t>
+          <t>Saknar standardfras om pedagogiskt stöd: Motsvarar delkurs 3 _Examensarbete_, 15 hp i kursen _Religionsvetenskap III med examensarbete för kandidatexamen_, 30 hp…</t>
         </is>
       </c>
       <c r="E395" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1026</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRK2R8</t>
         </is>
       </c>
     </row>
     <row r="396">
       <c r="A396" s="2" t="inlineStr">
         <is>
-          <t>RV1034</t>
+          <t>GRK2TW</t>
         </is>
       </c>
       <c r="B396" t="inlineStr">
         <is>
-          <t>RVA</t>
+          <t>RKA</t>
         </is>
       </c>
       <c r="C396" t="inlineStr">
@@ -11125,24 +11125,24 @@
       </c>
       <c r="D396" t="inlineStr">
         <is>
-          <t>Saknar standardfras om pedagogiskt stöd: Studenten har rätt till fyra omtentamenstillfällen. Kursen ersätter RVA051…</t>
+          <t>Saknar standardfras om pedagogiskt stöd: För nätbaserad kurs krävs tillgång till dator, headset eller bordsmikrofon, webkamera och internetuppkoppling.…</t>
         </is>
       </c>
       <c r="E396" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1034</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRK2TW</t>
         </is>
       </c>
     </row>
     <row r="397">
       <c r="A397" s="2" t="inlineStr">
         <is>
-          <t>RV1037</t>
+          <t>GRK2TY</t>
         </is>
       </c>
       <c r="B397" t="inlineStr">
         <is>
-          <t>RVA</t>
+          <t>RKA</t>
         </is>
       </c>
       <c r="C397" t="inlineStr">
@@ -11152,105 +11152,105 @@
       </c>
       <c r="D397" t="inlineStr">
         <is>
-          <t>Saknar standardfras om pedagogiskt stöd: Ersätter IEA023 och RV1015…</t>
+          <t>Saknar standardfras om pedagogiskt stöd: För nätbaserad kurs krävs tillgång till dator, headset, webbkamera och internetuppkoppling. Ersätter GRK2DM.…</t>
         </is>
       </c>
       <c r="E397" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1037</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRK2TY</t>
         </is>
       </c>
     </row>
     <row r="398">
       <c r="A398" s="2" t="inlineStr">
         <is>
-          <t>RV1038</t>
+          <t>GRK2TZ</t>
         </is>
       </c>
       <c r="B398" t="inlineStr">
         <is>
-          <t>RVA</t>
+          <t>RKA</t>
         </is>
       </c>
       <c r="C398" t="inlineStr">
         <is>
-          <t>Sektion saknas</t>
+          <t>Saknar standardfras om pedagogiskt stöd</t>
         </is>
       </c>
       <c r="D398" t="inlineStr">
         <is>
-          <t>Ingen Övrigt-sektion i kursplanen</t>
+          <t>Saknar standardfras om pedagogiskt stöd: Kursen innehåller två till tre fältdagar vid en grund- eller gymnasieskola. Kursen innehåller två till tre obligatoriska…</t>
         </is>
       </c>
       <c r="E398" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1038</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRK2TZ</t>
         </is>
       </c>
     </row>
     <row r="399">
       <c r="A399" s="2" t="inlineStr">
         <is>
-          <t>RV1039</t>
+          <t>RK1068</t>
         </is>
       </c>
       <c r="B399" t="inlineStr">
         <is>
-          <t>RVA</t>
+          <t>RKA</t>
         </is>
       </c>
       <c r="C399" t="inlineStr">
         <is>
-          <t>Saknar standardfras om pedagogiskt stöd</t>
+          <t>Sektion saknas</t>
         </is>
       </c>
       <c r="D399" t="inlineStr">
         <is>
-          <t>Saknar standardfras om pedagogiskt stöd: Studenten har rätt till fyra omtentamenstillfällen. Ersätter RVA 043…</t>
+          <t>Ingen Övrigt-sektion i kursplanen</t>
         </is>
       </c>
       <c r="E399" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1039</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RK1068</t>
         </is>
       </c>
     </row>
     <row r="400">
       <c r="A400" s="2" t="inlineStr">
         <is>
-          <t>RV1043</t>
+          <t>RK2034</t>
         </is>
       </c>
       <c r="B400" t="inlineStr">
         <is>
-          <t>RVA</t>
+          <t>RKA</t>
         </is>
       </c>
       <c r="C400" t="inlineStr">
         <is>
-          <t>Sektion saknas</t>
+          <t>Saknar standardfras om pedagogiskt stöd</t>
         </is>
       </c>
       <c r="D400" t="inlineStr">
         <is>
-          <t>Ingen Övrigt-sektion i kursplanen</t>
+          <t>Saknar standardfras om pedagogiskt stöd: All undervisning är nätbaserad. Seminarier och föreläsningar är schemalagda på bestämda tider och seminarierna förutsätt…</t>
         </is>
       </c>
       <c r="E400" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1043</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RK2034</t>
         </is>
       </c>
     </row>
     <row r="401">
       <c r="A401" s="2" t="inlineStr">
         <is>
-          <t>RV1044</t>
+          <t>RK2038</t>
         </is>
       </c>
       <c r="B401" t="inlineStr">
         <is>
-          <t>RVA</t>
+          <t>RKA</t>
         </is>
       </c>
       <c r="C401" t="inlineStr">
@@ -11260,46 +11260,46 @@
       </c>
       <c r="D401" t="inlineStr">
         <is>
-          <t>Saknar standardfras om pedagogiskt stöd: Överlappar RV1038…</t>
+          <t>Saknar standardfras om pedagogiskt stöd: All undervisning är nätbaserad. Seminarier och föreläsningar är schemalagda på bestämda tider och seminarierna förutsätt…</t>
         </is>
       </c>
       <c r="E401" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1044</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RK2038</t>
         </is>
       </c>
     </row>
     <row r="402">
       <c r="A402" s="2" t="inlineStr">
         <is>
-          <t>RV1045</t>
+          <t>RK3043</t>
         </is>
       </c>
       <c r="B402" t="inlineStr">
         <is>
-          <t>RVA</t>
+          <t>RKA</t>
         </is>
       </c>
       <c r="C402" t="inlineStr">
         <is>
-          <t>Sektion saknas</t>
+          <t>Saknar standardfras om pedagogiskt stöd</t>
         </is>
       </c>
       <c r="D402" t="inlineStr">
         <is>
-          <t>Ingen Övrigt-sektion i kursplanen</t>
+          <t>Saknar standardfras om pedagogiskt stöd: Eftersom kursen är nätbaserad krävs tillgång till dator, headset, webbkamera och internetuppkoppling.…</t>
         </is>
       </c>
       <c r="E402" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1045</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RK3043</t>
         </is>
       </c>
     </row>
     <row r="403">
       <c r="A403" s="2" t="inlineStr">
         <is>
-          <t>RV1046</t>
+          <t>GRV22R</t>
         </is>
       </c>
       <c r="B403" t="inlineStr">
@@ -11309,24 +11309,24 @@
       </c>
       <c r="C403" t="inlineStr">
         <is>
-          <t>Saknar standardfras om pedagogiskt stöd</t>
+          <t>Sektion saknas</t>
         </is>
       </c>
       <c r="D403" t="inlineStr">
         <is>
-          <t>Saknar standardfras om pedagogiskt stöd: Ersätter RV1028.…</t>
+          <t>Ingen Övrigt-sektion i kursplanen</t>
         </is>
       </c>
       <c r="E403" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1046</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRV22R</t>
         </is>
       </c>
     </row>
     <row r="404">
       <c r="A404" s="2" t="inlineStr">
         <is>
-          <t>RV1047</t>
+          <t>GRV266</t>
         </is>
       </c>
       <c r="B404" t="inlineStr">
@@ -11341,19 +11341,19 @@
       </c>
       <c r="D404" t="inlineStr">
         <is>
-          <t>Saknar standardfras om pedagogiskt stöd: Ersätter RV1011.…</t>
+          <t>Saknar standardfras om pedagogiskt stöd: Studenten har rätt till fyra omtentamenstillfällen. Kursen ersätter RV1003.…</t>
         </is>
       </c>
       <c r="E404" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1047</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRV266</t>
         </is>
       </c>
     </row>
     <row r="405">
       <c r="A405" s="2" t="inlineStr">
         <is>
-          <t>RV1048</t>
+          <t>GRV2CE</t>
         </is>
       </c>
       <c r="B405" t="inlineStr">
@@ -11368,19 +11368,19 @@
       </c>
       <c r="D405" t="inlineStr">
         <is>
-          <t>Saknar standardfras om pedagogiskt stöd: En betydande del av kursmaterialet (först och främst rättsfall) är på engelska. Maximalt fem provtillfällen. Ersätter RV…</t>
+          <t>Saknar standardfras om pedagogiskt stöd: Ersätter RV1055.…</t>
         </is>
       </c>
       <c r="E405" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1048</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRV2CE</t>
         </is>
       </c>
     </row>
     <row r="406">
       <c r="A406" s="2" t="inlineStr">
         <is>
-          <t>RV1049</t>
+          <t>GRV2FC</t>
         </is>
       </c>
       <c r="B406" t="inlineStr">
@@ -11390,24 +11390,24 @@
       </c>
       <c r="C406" t="inlineStr">
         <is>
-          <t>Saknar standardfras om pedagogiskt stöd</t>
+          <t>Sektion saknas</t>
         </is>
       </c>
       <c r="D406" t="inlineStr">
         <is>
-          <t>Saknar standardfras om pedagogiskt stöd: Ersätter RV1030. Maximalt fem provtillfällen.…</t>
+          <t>Ingen Övrigt-sektion i kursplanen</t>
         </is>
       </c>
       <c r="E406" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1049</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRV2FC</t>
         </is>
       </c>
     </row>
     <row r="407">
       <c r="A407" s="2" t="inlineStr">
         <is>
-          <t>RV1050</t>
+          <t>GRV2MK</t>
         </is>
       </c>
       <c r="B407" t="inlineStr">
@@ -11422,19 +11422,19 @@
       </c>
       <c r="D407" t="inlineStr">
         <is>
-          <t>Saknar standardfras om pedagogiskt stöd: Maximalt fem provtillfällen. Ersätter RV1014.…</t>
+          <t>Saknar standardfras om pedagogiskt stöd: Kursen ersätter GRV2CE.…</t>
         </is>
       </c>
       <c r="E407" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1050</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRV2MK</t>
         </is>
       </c>
     </row>
     <row r="408">
       <c r="A408" s="2" t="inlineStr">
         <is>
-          <t>RV1051</t>
+          <t>RV1001</t>
         </is>
       </c>
       <c r="B408" t="inlineStr">
@@ -11449,19 +11449,19 @@
       </c>
       <c r="D408" t="inlineStr">
         <is>
-          <t>Saknar standardfras om pedagogiskt stöd: Ersätter RV1041. Allmän straffrätt och straffprocessrätt förekommer inte på denna kurs.…</t>
+          <t>Saknar standardfras om pedagogiskt stöd: Studenten har rätt till fyra omtentamenstillfällen. Kursen ersätter RVA021.…</t>
         </is>
       </c>
       <c r="E408" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1051</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1001</t>
         </is>
       </c>
     </row>
     <row r="409">
       <c r="A409" s="2" t="inlineStr">
         <is>
-          <t>RV1052</t>
+          <t>RV1002</t>
         </is>
       </c>
       <c r="B409" t="inlineStr">
@@ -11476,19 +11476,19 @@
       </c>
       <c r="D409" t="inlineStr">
         <is>
-          <t>Saknar standardfras om pedagogiskt stöd: Ersätter RV1035.…</t>
+          <t>Saknar standardfras om pedagogiskt stöd: Studenten har rätt till fyra omtentamenstillfällen. Kursen ersätter RVA045…</t>
         </is>
       </c>
       <c r="E409" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1052</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1002</t>
         </is>
       </c>
     </row>
     <row r="410">
       <c r="A410" s="2" t="inlineStr">
         <is>
-          <t>RV1053</t>
+          <t>RV1003</t>
         </is>
       </c>
       <c r="B410" t="inlineStr">
@@ -11498,24 +11498,24 @@
       </c>
       <c r="C410" t="inlineStr">
         <is>
-          <t>Sektion saknas</t>
+          <t>Saknar standardfras om pedagogiskt stöd</t>
         </is>
       </c>
       <c r="D410" t="inlineStr">
         <is>
-          <t>Ingen Övrigt-sektion i kursplanen</t>
+          <t>Saknar standardfras om pedagogiskt stöd: Studenten har rätt till fyra omtentamenstillfällen. Kursen ersätter RVA044…</t>
         </is>
       </c>
       <c r="E410" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1053</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1003</t>
         </is>
       </c>
     </row>
     <row r="411">
       <c r="A411" s="2" t="inlineStr">
         <is>
-          <t>RV1054</t>
+          <t>RV1004</t>
         </is>
       </c>
       <c r="B411" t="inlineStr">
@@ -11530,19 +11530,19 @@
       </c>
       <c r="D411" t="inlineStr">
         <is>
-          <t>Saknar standardfras om pedagogiskt stöd: Ersätter RV1010.…</t>
+          <t>Saknar standardfras om pedagogiskt stöd: Studenten har rätt till fyra omtentamenstillfällen. Kursen ersätter RVA008…</t>
         </is>
       </c>
       <c r="E411" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1054</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1004</t>
         </is>
       </c>
     </row>
     <row r="412">
       <c r="A412" s="2" t="inlineStr">
         <is>
-          <t>RV1055</t>
+          <t>RV1009</t>
         </is>
       </c>
       <c r="B412" t="inlineStr">
@@ -11557,19 +11557,19 @@
       </c>
       <c r="D412" t="inlineStr">
         <is>
-          <t>Saknar standardfras om pedagogiskt stöd: Ersätter EU1024.…</t>
+          <t>Saknar standardfras om pedagogiskt stöd: Studenten har rätt till fyra omtentamenstillfällen. Ersätter RVA 050…</t>
         </is>
       </c>
       <c r="E412" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1055</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1009</t>
         </is>
       </c>
     </row>
     <row r="413">
       <c r="A413" s="2" t="inlineStr">
         <is>
-          <t>RV1056</t>
+          <t>RV1015</t>
         </is>
       </c>
       <c r="B413" t="inlineStr">
@@ -11584,19 +11584,19 @@
       </c>
       <c r="D413" t="inlineStr">
         <is>
-          <t>Saknar standardfras om pedagogiskt stöd: Kursen ersätter RV1018.…</t>
+          <t>Saknar standardfras om pedagogiskt stöd: Ersätter IEA023…</t>
         </is>
       </c>
       <c r="E413" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1056</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1015</t>
         </is>
       </c>
     </row>
     <row r="414">
       <c r="A414" s="2" t="inlineStr">
         <is>
-          <t>RV1057</t>
+          <t>RV1026</t>
         </is>
       </c>
       <c r="B414" t="inlineStr">
@@ -11611,19 +11611,19 @@
       </c>
       <c r="D414" t="inlineStr">
         <is>
-          <t>Saknar standardfras om pedagogiskt stöd: Kursen ersätter RV1036. Kursen överlappar delvis Handelsrättslig översiktskurs.…</t>
+          <t>Saknar standardfras om pedagogiskt stöd: Studenten har rätt till fyra omtentamenstillfällen. Kursen ersätter RVA002…</t>
         </is>
       </c>
       <c r="E414" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1057</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1026</t>
         </is>
       </c>
     </row>
     <row r="415">
       <c r="A415" s="2" t="inlineStr">
         <is>
-          <t>RV1058</t>
+          <t>RV1034</t>
         </is>
       </c>
       <c r="B415" t="inlineStr">
@@ -11638,24 +11638,24 @@
       </c>
       <c r="D415" t="inlineStr">
         <is>
-          <t>Saknar standardfras om pedagogiskt stöd: Kursen ersätter RV1006 och RV1017 och överlappar delvis kursen Juridik för detaljhandel, 7,5 hp.…</t>
+          <t>Saknar standardfras om pedagogiskt stöd: Studenten har rätt till fyra omtentamenstillfällen. Kursen ersätter RVA051…</t>
         </is>
       </c>
       <c r="E415" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1058</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1034</t>
         </is>
       </c>
     </row>
     <row r="416">
       <c r="A416" s="2" t="inlineStr">
         <is>
-          <t>ASK22G</t>
+          <t>RV1037</t>
         </is>
       </c>
       <c r="B416" t="inlineStr">
         <is>
-          <t>SKA</t>
+          <t>RVA</t>
         </is>
       </c>
       <c r="C416" t="inlineStr">
@@ -11665,51 +11665,51 @@
       </c>
       <c r="D416" t="inlineStr">
         <is>
-          <t>Saknar standardfras om pedagogiskt stöd: Kursen ingår i Magisterprogram: Demokrati, medborgarskap och förändring.…</t>
+          <t>Saknar standardfras om pedagogiskt stöd: Ersätter IEA023 och RV1015…</t>
         </is>
       </c>
       <c r="E416" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASK22G</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1037</t>
         </is>
       </c>
     </row>
     <row r="417">
       <c r="A417" s="2" t="inlineStr">
         <is>
-          <t>ASK22H</t>
+          <t>RV1038</t>
         </is>
       </c>
       <c r="B417" t="inlineStr">
         <is>
-          <t>SKA</t>
+          <t>RVA</t>
         </is>
       </c>
       <c r="C417" t="inlineStr">
         <is>
-          <t>Saknar standardfras om pedagogiskt stöd</t>
+          <t>Sektion saknas</t>
         </is>
       </c>
       <c r="D417" t="inlineStr">
         <is>
-          <t>Saknar standardfras om pedagogiskt stöd: Kursen ingår i Magisterprogram: Demokrati, medborgarskap och förändring.…</t>
+          <t>Ingen Övrigt-sektion i kursplanen</t>
         </is>
       </c>
       <c r="E417" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASK22H</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1038</t>
         </is>
       </c>
     </row>
     <row r="418">
       <c r="A418" s="2" t="inlineStr">
         <is>
-          <t>ASK22J</t>
+          <t>RV1039</t>
         </is>
       </c>
       <c r="B418" t="inlineStr">
         <is>
-          <t>SKA</t>
+          <t>RVA</t>
         </is>
       </c>
       <c r="C418" t="inlineStr">
@@ -11719,51 +11719,51 @@
       </c>
       <c r="D418" t="inlineStr">
         <is>
-          <t>Saknar standardfras om pedagogiskt stöd: Kursen ingår i Magisterprogram: Demokrati, medborgarskap och förändring.…</t>
+          <t>Saknar standardfras om pedagogiskt stöd: Studenten har rätt till fyra omtentamenstillfällen. Ersätter RVA 043…</t>
         </is>
       </c>
       <c r="E418" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASK22J</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1039</t>
         </is>
       </c>
     </row>
     <row r="419">
       <c r="A419" s="2" t="inlineStr">
         <is>
-          <t>ASK22K</t>
+          <t>RV1043</t>
         </is>
       </c>
       <c r="B419" t="inlineStr">
         <is>
-          <t>SKA</t>
+          <t>RVA</t>
         </is>
       </c>
       <c r="C419" t="inlineStr">
         <is>
-          <t>Saknar standardfras om pedagogiskt stöd</t>
+          <t>Sektion saknas</t>
         </is>
       </c>
       <c r="D419" t="inlineStr">
         <is>
-          <t>Saknar standardfras om pedagogiskt stöd: Kursen ingår i Magisterprogram: Demokrati, medborgarskap och förändring.…</t>
+          <t>Ingen Övrigt-sektion i kursplanen</t>
         </is>
       </c>
       <c r="E419" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASK22K</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1043</t>
         </is>
       </c>
     </row>
     <row r="420">
       <c r="A420" s="2" t="inlineStr">
         <is>
-          <t>ASK22L</t>
+          <t>RV1044</t>
         </is>
       </c>
       <c r="B420" t="inlineStr">
         <is>
-          <t>SKA</t>
+          <t>RVA</t>
         </is>
       </c>
       <c r="C420" t="inlineStr">
@@ -11773,51 +11773,51 @@
       </c>
       <c r="D420" t="inlineStr">
         <is>
-          <t>Saknar standardfras om pedagogiskt stöd: Kursen ingår i Magisterprogram: Demokrati, medborgarskap och förändring.…</t>
+          <t>Saknar standardfras om pedagogiskt stöd: Överlappar RV1038…</t>
         </is>
       </c>
       <c r="E420" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASK22L</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1044</t>
         </is>
       </c>
     </row>
     <row r="421">
       <c r="A421" s="2" t="inlineStr">
         <is>
-          <t>ASK22M</t>
+          <t>RV1045</t>
         </is>
       </c>
       <c r="B421" t="inlineStr">
         <is>
-          <t>SKA</t>
+          <t>RVA</t>
         </is>
       </c>
       <c r="C421" t="inlineStr">
         <is>
-          <t>Saknar standardfras om pedagogiskt stöd</t>
+          <t>Sektion saknas</t>
         </is>
       </c>
       <c r="D421" t="inlineStr">
         <is>
-          <t>Saknar standardfras om pedagogiskt stöd: Kursen ingår i Magisterprogram: Demokrati, medborgarskap och förändring. Handledning ges endast under angiven kursperiod…</t>
+          <t>Ingen Övrigt-sektion i kursplanen</t>
         </is>
       </c>
       <c r="E421" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASK22M</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1045</t>
         </is>
       </c>
     </row>
     <row r="422">
       <c r="A422" s="2" t="inlineStr">
         <is>
-          <t>ASK289</t>
+          <t>RV1046</t>
         </is>
       </c>
       <c r="B422" t="inlineStr">
         <is>
-          <t>SKA</t>
+          <t>RVA</t>
         </is>
       </c>
       <c r="C422" t="inlineStr">
@@ -11827,78 +11827,78 @@
       </c>
       <c r="D422" t="inlineStr">
         <is>
-          <t>Saknar standardfras om pedagogiskt stöd: Kursen ingår i Magisterprogram: Demokrati, medborgarskap och förändring. Kursen motsvarar ASK22L.…</t>
+          <t>Saknar standardfras om pedagogiskt stöd: Ersätter RV1028.…</t>
         </is>
       </c>
       <c r="E422" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASK289</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1046</t>
         </is>
       </c>
     </row>
     <row r="423">
       <c r="A423" s="2" t="inlineStr">
         <is>
-          <t>GSK2C9</t>
+          <t>RV1047</t>
         </is>
       </c>
       <c r="B423" t="inlineStr">
         <is>
-          <t>SKA</t>
+          <t>RVA</t>
         </is>
       </c>
       <c r="C423" t="inlineStr">
         <is>
-          <t>Sektion saknas</t>
+          <t>Saknar standardfras om pedagogiskt stöd</t>
         </is>
       </c>
       <c r="D423" t="inlineStr">
         <is>
-          <t>Ingen Övrigt-sektion i kursplanen</t>
+          <t>Saknar standardfras om pedagogiskt stöd: Ersätter RV1011.…</t>
         </is>
       </c>
       <c r="E423" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSK2C9</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1047</t>
         </is>
       </c>
     </row>
     <row r="424">
       <c r="A424" s="2" t="inlineStr">
         <is>
-          <t>GSK2K2</t>
+          <t>RV1048</t>
         </is>
       </c>
       <c r="B424" t="inlineStr">
         <is>
-          <t>SKA</t>
+          <t>RVA</t>
         </is>
       </c>
       <c r="C424" t="inlineStr">
         <is>
-          <t>Sektion saknas</t>
+          <t>Saknar standardfras om pedagogiskt stöd</t>
         </is>
       </c>
       <c r="D424" t="inlineStr">
         <is>
-          <t>Ingen Övrigt-sektion i kursplanen</t>
+          <t>Saknar standardfras om pedagogiskt stöd: En betydande del av kursmaterialet (först och främst rättsfall) är på engelska. Maximalt fem provtillfällen. Ersätter RV…</t>
         </is>
       </c>
       <c r="E424" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSK2K2</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1048</t>
         </is>
       </c>
     </row>
     <row r="425">
       <c r="A425" s="2" t="inlineStr">
         <is>
-          <t>GSK2PM</t>
+          <t>RV1049</t>
         </is>
       </c>
       <c r="B425" t="inlineStr">
         <is>
-          <t>SKA</t>
+          <t>RVA</t>
         </is>
       </c>
       <c r="C425" t="inlineStr">
@@ -11908,51 +11908,51 @@
       </c>
       <c r="D425" t="inlineStr">
         <is>
-          <t>Saknar standardfras om pedagogiskt stöd: Kursen motsvarar SK1059.…</t>
+          <t>Saknar standardfras om pedagogiskt stöd: Ersätter RV1030. Maximalt fem provtillfällen.…</t>
         </is>
       </c>
       <c r="E425" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSK2PM</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1049</t>
         </is>
       </c>
     </row>
     <row r="426">
       <c r="A426" s="2" t="inlineStr">
         <is>
-          <t>GSK2PN</t>
+          <t>RV1050</t>
         </is>
       </c>
       <c r="B426" t="inlineStr">
         <is>
-          <t>SKA</t>
+          <t>RVA</t>
         </is>
       </c>
       <c r="C426" t="inlineStr">
         <is>
-          <t>Sektion saknas</t>
+          <t>Saknar standardfras om pedagogiskt stöd</t>
         </is>
       </c>
       <c r="D426" t="inlineStr">
         <is>
-          <t>Ingen Övrigt-sektion i kursplanen</t>
+          <t>Saknar standardfras om pedagogiskt stöd: Maximalt fem provtillfällen. Ersätter RV1014.…</t>
         </is>
       </c>
       <c r="E426" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSK2PN</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1050</t>
         </is>
       </c>
     </row>
     <row r="427">
       <c r="A427" s="2" t="inlineStr">
         <is>
-          <t>GSK2PP</t>
+          <t>RV1051</t>
         </is>
       </c>
       <c r="B427" t="inlineStr">
         <is>
-          <t>SKA</t>
+          <t>RVA</t>
         </is>
       </c>
       <c r="C427" t="inlineStr">
@@ -11962,24 +11962,24 @@
       </c>
       <c r="D427" t="inlineStr">
         <is>
-          <t>Saknar standardfras om pedagogiskt stöd: Kursen motsvarar SK1056.…</t>
+          <t>Saknar standardfras om pedagogiskt stöd: Ersätter RV1041. Allmän straffrätt och straffprocessrätt förekommer inte på denna kurs.…</t>
         </is>
       </c>
       <c r="E427" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSK2PP</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1051</t>
         </is>
       </c>
     </row>
     <row r="428">
       <c r="A428" s="2" t="inlineStr">
         <is>
-          <t>GSK2PQ</t>
+          <t>RV1052</t>
         </is>
       </c>
       <c r="B428" t="inlineStr">
         <is>
-          <t>SKA</t>
+          <t>RVA</t>
         </is>
       </c>
       <c r="C428" t="inlineStr">
@@ -11989,51 +11989,51 @@
       </c>
       <c r="D428" t="inlineStr">
         <is>
-          <t>Saknar standardfras om pedagogiskt stöd: Kursen motsvarar SK1055.…</t>
+          <t>Saknar standardfras om pedagogiskt stöd: Ersätter RV1035.…</t>
         </is>
       </c>
       <c r="E428" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSK2PQ</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1052</t>
         </is>
       </c>
     </row>
     <row r="429">
       <c r="A429" s="2" t="inlineStr">
         <is>
-          <t>GSK2PR</t>
+          <t>RV1053</t>
         </is>
       </c>
       <c r="B429" t="inlineStr">
         <is>
-          <t>SKA</t>
+          <t>RVA</t>
         </is>
       </c>
       <c r="C429" t="inlineStr">
         <is>
-          <t>Saknar standardfras om pedagogiskt stöd</t>
+          <t>Sektion saknas</t>
         </is>
       </c>
       <c r="D429" t="inlineStr">
         <is>
-          <t>Saknar standardfras om pedagogiskt stöd: Kursen motsvarar SK1062.…</t>
+          <t>Ingen Övrigt-sektion i kursplanen</t>
         </is>
       </c>
       <c r="E429" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSK2PR</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1053</t>
         </is>
       </c>
     </row>
     <row r="430">
       <c r="A430" s="2" t="inlineStr">
         <is>
-          <t>GSK2PS</t>
+          <t>RV1054</t>
         </is>
       </c>
       <c r="B430" t="inlineStr">
         <is>
-          <t>SKA</t>
+          <t>RVA</t>
         </is>
       </c>
       <c r="C430" t="inlineStr">
@@ -12043,24 +12043,24 @@
       </c>
       <c r="D430" t="inlineStr">
         <is>
-          <t>Saknar standardfras om pedagogiskt stöd: Kursen motsvarar SK1054 och SK1057.…</t>
+          <t>Saknar standardfras om pedagogiskt stöd: Ersätter RV1010.…</t>
         </is>
       </c>
       <c r="E430" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSK2PS</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1054</t>
         </is>
       </c>
     </row>
     <row r="431">
       <c r="A431" s="2" t="inlineStr">
         <is>
-          <t>GSK2PT</t>
+          <t>RV1055</t>
         </is>
       </c>
       <c r="B431" t="inlineStr">
         <is>
-          <t>SKA</t>
+          <t>RVA</t>
         </is>
       </c>
       <c r="C431" t="inlineStr">
@@ -12070,24 +12070,24 @@
       </c>
       <c r="D431" t="inlineStr">
         <is>
-          <t>Saknar standardfras om pedagogiskt stöd: Kursen motsvarar SK1061.…</t>
+          <t>Saknar standardfras om pedagogiskt stöd: Ersätter EU1024.…</t>
         </is>
       </c>
       <c r="E431" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSK2PT</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1055</t>
         </is>
       </c>
     </row>
     <row r="432">
       <c r="A432" s="2" t="inlineStr">
         <is>
-          <t>GSK2PU</t>
+          <t>RV1056</t>
         </is>
       </c>
       <c r="B432" t="inlineStr">
         <is>
-          <t>SKA</t>
+          <t>RVA</t>
         </is>
       </c>
       <c r="C432" t="inlineStr">
@@ -12097,24 +12097,24 @@
       </c>
       <c r="D432" t="inlineStr">
         <is>
-          <t>Saknar standardfras om pedagogiskt stöd: Kursen motsvarar SK1063.…</t>
+          <t>Saknar standardfras om pedagogiskt stöd: Kursen ersätter RV1018.…</t>
         </is>
       </c>
       <c r="E432" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSK2PU</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1056</t>
         </is>
       </c>
     </row>
     <row r="433">
       <c r="A433" s="2" t="inlineStr">
         <is>
-          <t>GSK2PV</t>
+          <t>RV1057</t>
         </is>
       </c>
       <c r="B433" t="inlineStr">
         <is>
-          <t>SKA</t>
+          <t>RVA</t>
         </is>
       </c>
       <c r="C433" t="inlineStr">
@@ -12124,24 +12124,24 @@
       </c>
       <c r="D433" t="inlineStr">
         <is>
-          <t>Saknar standardfras om pedagogiskt stöd: Kursen motsvarar SK2015.…</t>
+          <t>Saknar standardfras om pedagogiskt stöd: Kursen ersätter RV1036. Kursen överlappar delvis Handelsrättslig översiktskurs.…</t>
         </is>
       </c>
       <c r="E433" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSK2PV</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1057</t>
         </is>
       </c>
     </row>
     <row r="434">
       <c r="A434" s="2" t="inlineStr">
         <is>
-          <t>GSK2PW</t>
+          <t>RV1058</t>
         </is>
       </c>
       <c r="B434" t="inlineStr">
         <is>
-          <t>SKA</t>
+          <t>RVA</t>
         </is>
       </c>
       <c r="C434" t="inlineStr">
@@ -12151,19 +12151,19 @@
       </c>
       <c r="D434" t="inlineStr">
         <is>
-          <t>Saknar standardfras om pedagogiskt stöd: Kursen motsvarar SK2016.…</t>
+          <t>Saknar standardfras om pedagogiskt stöd: Kursen ersätter RV1006 och RV1017 och överlappar delvis kursen Juridik för detaljhandel, 7,5 hp.…</t>
         </is>
       </c>
       <c r="E434" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSK2PW</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1058</t>
         </is>
       </c>
     </row>
     <row r="435">
       <c r="A435" s="2" t="inlineStr">
         <is>
-          <t>GSK2QE</t>
+          <t>ASK22G</t>
         </is>
       </c>
       <c r="B435" t="inlineStr">
@@ -12173,24 +12173,24 @@
       </c>
       <c r="C435" t="inlineStr">
         <is>
-          <t>Sektion saknas</t>
+          <t>Saknar standardfras om pedagogiskt stöd</t>
         </is>
       </c>
       <c r="D435" t="inlineStr">
         <is>
-          <t>Ingen Övrigt-sektion i kursplanen</t>
+          <t>Saknar standardfras om pedagogiskt stöd: Kursen ingår i Magisterprogram: Demokrati, medborgarskap och förändring.…</t>
         </is>
       </c>
       <c r="E435" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSK2QE</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASK22G</t>
         </is>
       </c>
     </row>
     <row r="436">
       <c r="A436" s="2" t="inlineStr">
         <is>
-          <t>GSK2UH</t>
+          <t>ASK22H</t>
         </is>
       </c>
       <c r="B436" t="inlineStr">
@@ -12205,19 +12205,19 @@
       </c>
       <c r="D436" t="inlineStr">
         <is>
-          <t>Saknar standardfras om pedagogiskt stöd: Kursen motsvarar SK1063 och GSK2PU.…</t>
+          <t>Saknar standardfras om pedagogiskt stöd: Kursen ingår i Magisterprogram: Demokrati, medborgarskap och förändring.…</t>
         </is>
       </c>
       <c r="E436" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSK2UH</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASK22H</t>
         </is>
       </c>
     </row>
     <row r="437">
       <c r="A437" s="2" t="inlineStr">
         <is>
-          <t>GSK2UJ</t>
+          <t>ASK22J</t>
         </is>
       </c>
       <c r="B437" t="inlineStr">
@@ -12232,19 +12232,19 @@
       </c>
       <c r="D437" t="inlineStr">
         <is>
-          <t>Saknar standardfras om pedagogiskt stöd: Kursen motsvarar SK2016 och GSK2PW…</t>
+          <t>Saknar standardfras om pedagogiskt stöd: Kursen ingår i Magisterprogram: Demokrati, medborgarskap och förändring.…</t>
         </is>
       </c>
       <c r="E437" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSK2UJ</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASK22J</t>
         </is>
       </c>
     </row>
     <row r="438">
       <c r="A438" s="2" t="inlineStr">
         <is>
-          <t>SK1018</t>
+          <t>ASK22K</t>
         </is>
       </c>
       <c r="B438" t="inlineStr">
@@ -12259,19 +12259,19 @@
       </c>
       <c r="D438" t="inlineStr">
         <is>
-          <t>Saknar standardfras om pedagogiskt stöd: Fem tentamenstillfällen. Kursen ersätter SKA022. Kursen ingick i huvudområdet statsvetenskap till och med 2015-08-24.…</t>
+          <t>Saknar standardfras om pedagogiskt stöd: Kursen ingår i Magisterprogram: Demokrati, medborgarskap och förändring.…</t>
         </is>
       </c>
       <c r="E438" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SK1018</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASK22K</t>
         </is>
       </c>
     </row>
     <row r="439">
       <c r="A439" s="2" t="inlineStr">
         <is>
-          <t>SK1050</t>
+          <t>ASK22L</t>
         </is>
       </c>
       <c r="B439" t="inlineStr">
@@ -12286,19 +12286,19 @@
       </c>
       <c r="D439" t="inlineStr">
         <is>
-          <t>Saknar standardfras om pedagogiskt stöd: Antal provtillfällen begränsas till fem. Kursen ingår i Samhällsvetarprogrammet och kurspaketet Statsvetenskap II.…</t>
+          <t>Saknar standardfras om pedagogiskt stöd: Kursen ingår i Magisterprogram: Demokrati, medborgarskap och förändring.…</t>
         </is>
       </c>
       <c r="E439" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SK1050</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASK22L</t>
         </is>
       </c>
     </row>
     <row r="440">
       <c r="A440" s="2" t="inlineStr">
         <is>
-          <t>SK1054</t>
+          <t>ASK22M</t>
         </is>
       </c>
       <c r="B440" t="inlineStr">
@@ -12313,19 +12313,19 @@
       </c>
       <c r="D440" t="inlineStr">
         <is>
-          <t>Saknar standardfras om pedagogiskt stöd: Kursen ingår i kurspaketet Internationella relationer I. Kursen motsvarar SK1024.…</t>
+          <t>Saknar standardfras om pedagogiskt stöd: Kursen ingår i Magisterprogram: Demokrati, medborgarskap och förändring. Handledning ges endast under angiven kursperiod…</t>
         </is>
       </c>
       <c r="E440" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SK1054</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASK22M</t>
         </is>
       </c>
     </row>
     <row r="441">
       <c r="A441" s="2" t="inlineStr">
         <is>
-          <t>SK1055</t>
+          <t>ASK289</t>
         </is>
       </c>
       <c r="B441" t="inlineStr">
@@ -12340,19 +12340,19 @@
       </c>
       <c r="D441" t="inlineStr">
         <is>
-          <t>Saknar standardfras om pedagogiskt stöd: Kursen ingår i Samhällsvetarprogrammet och kurspaketet Statsvetenskap I. Kursen motsvarar SK1046.…</t>
+          <t>Saknar standardfras om pedagogiskt stöd: Kursen ingår i Magisterprogram: Demokrati, medborgarskap och förändring. Kursen motsvarar ASK22L.…</t>
         </is>
       </c>
       <c r="E441" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SK1055</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASK289</t>
         </is>
       </c>
     </row>
     <row r="442">
       <c r="A442" s="2" t="inlineStr">
         <is>
-          <t>SK1058</t>
+          <t>GSK2C9</t>
         </is>
       </c>
       <c r="B442" t="inlineStr">
@@ -12362,24 +12362,24 @@
       </c>
       <c r="C442" t="inlineStr">
         <is>
-          <t>Saknar standardfras om pedagogiskt stöd</t>
+          <t>Sektion saknas</t>
         </is>
       </c>
       <c r="D442" t="inlineStr">
         <is>
-          <t>Saknar standardfras om pedagogiskt stöd: Kursen ingår i kurspaketet Internationella relationer I. Kursen motsvarar SK1044.…</t>
+          <t>Ingen Övrigt-sektion i kursplanen</t>
         </is>
       </c>
       <c r="E442" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SK1058</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSK2C9</t>
         </is>
       </c>
     </row>
     <row r="443">
       <c r="A443" s="2" t="inlineStr">
         <is>
-          <t>SK1060</t>
+          <t>GSK2K2</t>
         </is>
       </c>
       <c r="B443" t="inlineStr">
@@ -12389,24 +12389,24 @@
       </c>
       <c r="C443" t="inlineStr">
         <is>
-          <t>Saknar standardfras om pedagogiskt stöd</t>
+          <t>Sektion saknas</t>
         </is>
       </c>
       <c r="D443" t="inlineStr">
         <is>
-          <t>Saknar standardfras om pedagogiskt stöd: Kursen ingår i kurspaketet Internationella relationer I. Kursen motsvarar SK1037.…</t>
+          <t>Ingen Övrigt-sektion i kursplanen</t>
         </is>
       </c>
       <c r="E443" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SK1060</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSK2K2</t>
         </is>
       </c>
     </row>
     <row r="444">
       <c r="A444" s="2" t="inlineStr">
         <is>
-          <t>SK1062</t>
+          <t>GSK2PM</t>
         </is>
       </c>
       <c r="B444" t="inlineStr">
@@ -12421,19 +12421,19 @@
       </c>
       <c r="D444" t="inlineStr">
         <is>
-          <t>Saknar standardfras om pedagogiskt stöd: Kursen ingår i Samhällsvetarprogrammet och kurspaketet Statsvetenskap II. Kursen motsvarar SK1052.…</t>
+          <t>Saknar standardfras om pedagogiskt stöd: Kursen motsvarar SK1059.…</t>
         </is>
       </c>
       <c r="E444" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SK1062</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSK2PM</t>
         </is>
       </c>
     </row>
     <row r="445">
       <c r="A445" s="2" t="inlineStr">
         <is>
-          <t>SK1064</t>
+          <t>GSK2PN</t>
         </is>
       </c>
       <c r="B445" t="inlineStr">
@@ -12443,24 +12443,24 @@
       </c>
       <c r="C445" t="inlineStr">
         <is>
-          <t>Saknar standardfras om pedagogiskt stöd</t>
+          <t>Sektion saknas</t>
         </is>
       </c>
       <c r="D445" t="inlineStr">
         <is>
-          <t>Saknar standardfras om pedagogiskt stöd: Kursen ingår i kurspaketet Internationella relationer II.…</t>
+          <t>Ingen Övrigt-sektion i kursplanen</t>
         </is>
       </c>
       <c r="E445" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SK1064</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSK2PN</t>
         </is>
       </c>
     </row>
     <row r="446">
       <c r="A446" s="2" t="inlineStr">
         <is>
-          <t>SK1065</t>
+          <t>GSK2PP</t>
         </is>
       </c>
       <c r="B446" t="inlineStr">
@@ -12475,19 +12475,19 @@
       </c>
       <c r="D446" t="inlineStr">
         <is>
-          <t>Saknar standardfras om pedagogiskt stöd: Kursen ingår i kurspaketet Internationella relationer II.…</t>
+          <t>Saknar standardfras om pedagogiskt stöd: Kursen motsvarar SK1056.…</t>
         </is>
       </c>
       <c r="E446" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SK1065</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSK2PP</t>
         </is>
       </c>
     </row>
     <row r="447">
       <c r="A447" s="2" t="inlineStr">
         <is>
-          <t>SK2009</t>
+          <t>GSK2PQ</t>
         </is>
       </c>
       <c r="B447" t="inlineStr">
@@ -12502,19 +12502,19 @@
       </c>
       <c r="D447" t="inlineStr">
         <is>
-          <t>Saknar standardfras om pedagogiskt stöd: Kursen ingår i kurspaketet Internationella relationer III.…</t>
+          <t>Saknar standardfras om pedagogiskt stöd: Kursen motsvarar SK1055.…</t>
         </is>
       </c>
       <c r="E447" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SK2009</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSK2PQ</t>
         </is>
       </c>
     </row>
     <row r="448">
       <c r="A448" s="2" t="inlineStr">
         <is>
-          <t>SK2011</t>
+          <t>GSK2PR</t>
         </is>
       </c>
       <c r="B448" t="inlineStr">
@@ -12529,19 +12529,19 @@
       </c>
       <c r="D448" t="inlineStr">
         <is>
-          <t>Saknar standardfras om pedagogiskt stöd: Kursen ingår som valbar kurs i kurspaketet Internationella relationer III.…</t>
+          <t>Saknar standardfras om pedagogiskt stöd: Kursen motsvarar SK1062.…</t>
         </is>
       </c>
       <c r="E448" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SK2011</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSK2PR</t>
         </is>
       </c>
     </row>
     <row r="449">
       <c r="A449" s="2" t="inlineStr">
         <is>
-          <t>SK2013</t>
+          <t>GSK2PS</t>
         </is>
       </c>
       <c r="B449" t="inlineStr">
@@ -12556,19 +12556,19 @@
       </c>
       <c r="D449" t="inlineStr">
         <is>
-          <t>Saknar standardfras om pedagogiskt stöd: Kursen ingår i Samhällsvetarprogrammet. Kursen ingår i kurspaketet Statsvetenskap III. Kursen motsvarar SK2001.…</t>
+          <t>Saknar standardfras om pedagogiskt stöd: Kursen motsvarar SK1054 och SK1057.…</t>
         </is>
       </c>
       <c r="E449" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SK2013</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSK2PS</t>
         </is>
       </c>
     </row>
     <row r="450">
       <c r="A450" s="2" t="inlineStr">
         <is>
-          <t>SK2015</t>
+          <t>GSK2PT</t>
         </is>
       </c>
       <c r="B450" t="inlineStr">
@@ -12583,19 +12583,19 @@
       </c>
       <c r="D450" t="inlineStr">
         <is>
-          <t>Saknar standardfras om pedagogiskt stöd: Kursen kan inte tillgodoräknas i examen parallellt med Samhällsvetenskapliga metoder II - inriktning sociologi på grund …</t>
+          <t>Saknar standardfras om pedagogiskt stöd: Kursen motsvarar SK1061.…</t>
         </is>
       </c>
       <c r="E450" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SK2015</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSK2PT</t>
         </is>
       </c>
     </row>
     <row r="451">
       <c r="A451" s="2" t="inlineStr">
         <is>
-          <t>SK2016</t>
+          <t>GSK2PU</t>
         </is>
       </c>
       <c r="B451" t="inlineStr">
@@ -12610,24 +12610,24 @@
       </c>
       <c r="D451" t="inlineStr">
         <is>
-          <t>Saknar standardfras om pedagogiskt stöd: Kursen ingår i Samhällsvetarprogrammet. Kursen ingår i kurspaketet Statsvetenskap III. Kursen motsvarar SK2007.…</t>
+          <t>Saknar standardfras om pedagogiskt stöd: Kursen motsvarar SK1063.…</t>
         </is>
       </c>
       <c r="E451" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SK2016</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSK2PU</t>
         </is>
       </c>
     </row>
     <row r="452">
       <c r="A452" s="2" t="inlineStr">
         <is>
-          <t>GSO2PL</t>
+          <t>GSK2PV</t>
         </is>
       </c>
       <c r="B452" t="inlineStr">
         <is>
-          <t>SOA</t>
+          <t>SKA</t>
         </is>
       </c>
       <c r="C452" t="inlineStr">
@@ -12637,24 +12637,24 @@
       </c>
       <c r="D452" t="inlineStr">
         <is>
-          <t>Saknar standardfras om pedagogiskt stöd: Kursen ingår i Socionomprogrammet. Kursen motsvarar GSO26K.…</t>
+          <t>Saknar standardfras om pedagogiskt stöd: Kursen motsvarar SK2015.…</t>
         </is>
       </c>
       <c r="E452" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSO2PL</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSK2PV</t>
         </is>
       </c>
     </row>
     <row r="453">
       <c r="A453" s="2" t="inlineStr">
         <is>
-          <t>GSO2UA</t>
+          <t>GSK2PW</t>
         </is>
       </c>
       <c r="B453" t="inlineStr">
         <is>
-          <t>SOA</t>
+          <t>SKA</t>
         </is>
       </c>
       <c r="C453" t="inlineStr">
@@ -12664,51 +12664,51 @@
       </c>
       <c r="D453" t="inlineStr">
         <is>
-          <t>Saknar standardfras om pedagogiskt stöd: Kursen motsvarar SO1023 samt SO1028…</t>
+          <t>Saknar standardfras om pedagogiskt stöd: Kursen motsvarar SK2016.…</t>
         </is>
       </c>
       <c r="E453" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSO2UA</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSK2PW</t>
         </is>
       </c>
     </row>
     <row r="454">
       <c r="A454" s="2" t="inlineStr">
         <is>
-          <t>GSO2UC</t>
+          <t>GSK2QE</t>
         </is>
       </c>
       <c r="B454" t="inlineStr">
         <is>
-          <t>SOA</t>
+          <t>SKA</t>
         </is>
       </c>
       <c r="C454" t="inlineStr">
         <is>
-          <t>Saknar standardfras om pedagogiskt stöd</t>
+          <t>Sektion saknas</t>
         </is>
       </c>
       <c r="D454" t="inlineStr">
         <is>
-          <t>Saknar standardfras om pedagogiskt stöd: Det krävs att den studerande kan kommunicera med både ljud och bild via en dator Ersätter kursen GSO29C.…</t>
+          <t>Ingen Övrigt-sektion i kursplanen</t>
         </is>
       </c>
       <c r="E454" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSO2UC</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSK2QE</t>
         </is>
       </c>
     </row>
     <row r="455">
       <c r="A455" s="2" t="inlineStr">
         <is>
-          <t>GSO2XU</t>
+          <t>GSK2UH</t>
         </is>
       </c>
       <c r="B455" t="inlineStr">
         <is>
-          <t>SOA</t>
+          <t>SKA</t>
         </is>
       </c>
       <c r="C455" t="inlineStr">
@@ -12718,24 +12718,24 @@
       </c>
       <c r="D455" t="inlineStr">
         <is>
-          <t>Saknar standardfras om pedagogiskt stöd: Kursen motsvarar SO1038 samt SO1041.…</t>
+          <t>Saknar standardfras om pedagogiskt stöd: Kursen motsvarar SK1063 och GSK2PU.…</t>
         </is>
       </c>
       <c r="E455" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSO2XU</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSK2UH</t>
         </is>
       </c>
     </row>
     <row r="456">
       <c r="A456" s="2" t="inlineStr">
         <is>
-          <t>GSO2XV</t>
+          <t>GSK2UJ</t>
         </is>
       </c>
       <c r="B456" t="inlineStr">
         <is>
-          <t>SOA</t>
+          <t>SKA</t>
         </is>
       </c>
       <c r="C456" t="inlineStr">
@@ -12745,24 +12745,24 @@
       </c>
       <c r="D456" t="inlineStr">
         <is>
-          <t>Saknar standardfras om pedagogiskt stöd: Kursen motsvarar SO2007 samt SO2009.…</t>
+          <t>Saknar standardfras om pedagogiskt stöd: Kursen motsvarar SK2016 och GSK2PW…</t>
         </is>
       </c>
       <c r="E456" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSO2XV</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSK2UJ</t>
         </is>
       </c>
     </row>
     <row r="457">
       <c r="A457" s="2" t="inlineStr">
         <is>
-          <t>GSO33U</t>
+          <t>SK1018</t>
         </is>
       </c>
       <c r="B457" t="inlineStr">
         <is>
-          <t>SOA</t>
+          <t>SKA</t>
         </is>
       </c>
       <c r="C457" t="inlineStr">
@@ -12772,24 +12772,24 @@
       </c>
       <c r="D457" t="inlineStr">
         <is>
-          <t>Saknar standardfras om pedagogiskt stöd: Kursen överlappar SO2007, SO2009 samt GSO2XV.…</t>
+          <t>Saknar standardfras om pedagogiskt stöd: Fem tentamenstillfällen. Kursen ersätter SKA022. Kursen ingick i huvudområdet statsvetenskap till och med 2015-08-24.…</t>
         </is>
       </c>
       <c r="E457" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSO33U</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SK1018</t>
         </is>
       </c>
     </row>
     <row r="458">
       <c r="A458" s="2" t="inlineStr">
         <is>
-          <t>SO1006</t>
+          <t>SK1050</t>
         </is>
       </c>
       <c r="B458" t="inlineStr">
         <is>
-          <t>SOA</t>
+          <t>SKA</t>
         </is>
       </c>
       <c r="C458" t="inlineStr">
@@ -12799,24 +12799,24 @@
       </c>
       <c r="D458" t="inlineStr">
         <is>
-          <t>Saknar standardfras om pedagogiskt stöd: Kursen kan tillgodoräknas i Sociologi I 30 högskolepoäng. Kursen motsvarar SOA023 Avvikande beteende A, 5 poäng.…</t>
+          <t>Saknar standardfras om pedagogiskt stöd: Antal provtillfällen begränsas till fem. Kursen ingår i Samhällsvetarprogrammet och kurspaketet Statsvetenskap II.…</t>
         </is>
       </c>
       <c r="E458" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SO1006</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SK1050</t>
         </is>
       </c>
     </row>
     <row r="459">
       <c r="A459" s="2" t="inlineStr">
         <is>
-          <t>SO1019</t>
+          <t>SK1054</t>
         </is>
       </c>
       <c r="B459" t="inlineStr">
         <is>
-          <t>SOA</t>
+          <t>SKA</t>
         </is>
       </c>
       <c r="C459" t="inlineStr">
@@ -12826,24 +12826,24 @@
       </c>
       <c r="D459" t="inlineStr">
         <is>
-          <t>Saknar standardfras om pedagogiskt stöd: Antal provtillfällen begränsas till fem.…</t>
+          <t>Saknar standardfras om pedagogiskt stöd: Kursen ingår i kurspaketet Internationella relationer I. Kursen motsvarar SK1024.…</t>
         </is>
       </c>
       <c r="E459" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SO1019</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SK1054</t>
         </is>
       </c>
     </row>
     <row r="460">
       <c r="A460" s="2" t="inlineStr">
         <is>
-          <t>SO1027</t>
+          <t>SK1055</t>
         </is>
       </c>
       <c r="B460" t="inlineStr">
         <is>
-          <t>SOA</t>
+          <t>SKA</t>
         </is>
       </c>
       <c r="C460" t="inlineStr">
@@ -12853,24 +12853,24 @@
       </c>
       <c r="D460" t="inlineStr">
         <is>
-          <t>Saknar standardfras om pedagogiskt stöd: Kursen ges på engelska.…</t>
+          <t>Saknar standardfras om pedagogiskt stöd: Kursen ingår i Samhällsvetarprogrammet och kurspaketet Statsvetenskap I. Kursen motsvarar SK1046.…</t>
         </is>
       </c>
       <c r="E460" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SO1027</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SK1055</t>
         </is>
       </c>
     </row>
     <row r="461">
       <c r="A461" s="2" t="inlineStr">
         <is>
-          <t>SO1030</t>
+          <t>SK1058</t>
         </is>
       </c>
       <c r="B461" t="inlineStr">
         <is>
-          <t>SOA</t>
+          <t>SKA</t>
         </is>
       </c>
       <c r="C461" t="inlineStr">
@@ -12880,24 +12880,24 @@
       </c>
       <c r="D461" t="inlineStr">
         <is>
-          <t>Saknar standardfras om pedagogiskt stöd: För varje kurstillfälle ges maximalt 5 examenstillfällen. Kursen ingår i samhällsvetarprogrammet. Kursen motsvarar SO101…</t>
+          <t>Saknar standardfras om pedagogiskt stöd: Kursen ingår i kurspaketet Internationella relationer I. Kursen motsvarar SK1044.…</t>
         </is>
       </c>
       <c r="E461" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SO1030</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SK1058</t>
         </is>
       </c>
     </row>
     <row r="462">
       <c r="A462" s="2" t="inlineStr">
         <is>
-          <t>SO1033</t>
+          <t>SK1060</t>
         </is>
       </c>
       <c r="B462" t="inlineStr">
         <is>
-          <t>SOA</t>
+          <t>SKA</t>
         </is>
       </c>
       <c r="C462" t="inlineStr">
@@ -12907,24 +12907,24 @@
       </c>
       <c r="D462" t="inlineStr">
         <is>
-          <t>Saknar standardfras om pedagogiskt stöd: Antal provtillfällen begränsas till fem. Kursen ges på engelska.…</t>
+          <t>Saknar standardfras om pedagogiskt stöd: Kursen ingår i kurspaketet Internationella relationer I. Kursen motsvarar SK1037.…</t>
         </is>
       </c>
       <c r="E462" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SO1033</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SK1060</t>
         </is>
       </c>
     </row>
     <row r="463">
       <c r="A463" s="2" t="inlineStr">
         <is>
-          <t>SO1034</t>
+          <t>SK1062</t>
         </is>
       </c>
       <c r="B463" t="inlineStr">
         <is>
-          <t>SOA</t>
+          <t>SKA</t>
         </is>
       </c>
       <c r="C463" t="inlineStr">
@@ -12934,24 +12934,24 @@
       </c>
       <c r="D463" t="inlineStr">
         <is>
-          <t>Saknar standardfras om pedagogiskt stöd: Denna kurs ingår i Samhällsvetarprogrammet. Kursen motsvarar SO1020.…</t>
+          <t>Saknar standardfras om pedagogiskt stöd: Kursen ingår i Samhällsvetarprogrammet och kurspaketet Statsvetenskap II. Kursen motsvarar SK1052.…</t>
         </is>
       </c>
       <c r="E463" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SO1034</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SK1062</t>
         </is>
       </c>
     </row>
     <row r="464">
       <c r="A464" s="2" t="inlineStr">
         <is>
-          <t>SO1037</t>
+          <t>SK1064</t>
         </is>
       </c>
       <c r="B464" t="inlineStr">
         <is>
-          <t>SOA</t>
+          <t>SKA</t>
         </is>
       </c>
       <c r="C464" t="inlineStr">
@@ -12961,24 +12961,24 @@
       </c>
       <c r="D464" t="inlineStr">
         <is>
-          <t>Saknar standardfras om pedagogiskt stöd: Kursen motsvarar SO1033.…</t>
+          <t>Saknar standardfras om pedagogiskt stöd: Kursen ingår i kurspaketet Internationella relationer II.…</t>
         </is>
       </c>
       <c r="E464" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SO1037</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SK1064</t>
         </is>
       </c>
     </row>
     <row r="465">
       <c r="A465" s="2" t="inlineStr">
         <is>
-          <t>SO1044</t>
+          <t>SK1065</t>
         </is>
       </c>
       <c r="B465" t="inlineStr">
         <is>
-          <t>SOA</t>
+          <t>SKA</t>
         </is>
       </c>
       <c r="C465" t="inlineStr">
@@ -12988,24 +12988,24 @@
       </c>
       <c r="D465" t="inlineStr">
         <is>
-          <t>Saknar standardfras om pedagogiskt stöd: Kursen ingår i Socionomprogrammet. Kursen motsvarar delkurs 1 i SO1021.…</t>
+          <t>Saknar standardfras om pedagogiskt stöd: Kursen ingår i kurspaketet Internationella relationer II.…</t>
         </is>
       </c>
       <c r="E465" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SO1044</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SK1065</t>
         </is>
       </c>
     </row>
     <row r="466">
       <c r="A466" s="2" t="inlineStr">
         <is>
-          <t>SO1047</t>
+          <t>SK2009</t>
         </is>
       </c>
       <c r="B466" t="inlineStr">
         <is>
-          <t>SOA</t>
+          <t>SKA</t>
         </is>
       </c>
       <c r="C466" t="inlineStr">
@@ -13015,78 +13015,78 @@
       </c>
       <c r="D466" t="inlineStr">
         <is>
-          <t>Saknar standardfras om pedagogiskt stöd: Kursen ingår i Sport Managementprogrammet och som valbar kurs i Samhällsvetarprogrammet. Kursen motsvarar delar av SO100…</t>
+          <t>Saknar standardfras om pedagogiskt stöd: Kursen ingår i kurspaketet Internationella relationer III.…</t>
         </is>
       </c>
       <c r="E466" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SO1047</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SK2009</t>
         </is>
       </c>
     </row>
     <row r="467">
       <c r="A467" s="2" t="inlineStr">
         <is>
-          <t>ATR25Z</t>
+          <t>SK2011</t>
         </is>
       </c>
       <c r="B467" t="inlineStr">
         <is>
-          <t>TRU</t>
+          <t>SKA</t>
         </is>
       </c>
       <c r="C467" t="inlineStr">
         <is>
-          <t>Sektion saknas</t>
+          <t>Saknar standardfras om pedagogiskt stöd</t>
         </is>
       </c>
       <c r="D467" t="inlineStr">
         <is>
-          <t>Ingen Övrigt-sektion i kursplanen</t>
+          <t>Saknar standardfras om pedagogiskt stöd: Kursen ingår som valbar kurs i kurspaketet Internationella relationer III.…</t>
         </is>
       </c>
       <c r="E467" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ATR25Z</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SK2011</t>
         </is>
       </c>
     </row>
     <row r="468">
       <c r="A468" s="2" t="inlineStr">
         <is>
-          <t>ATR26B</t>
+          <t>SK2013</t>
         </is>
       </c>
       <c r="B468" t="inlineStr">
         <is>
-          <t>TRU</t>
+          <t>SKA</t>
         </is>
       </c>
       <c r="C468" t="inlineStr">
         <is>
-          <t>Sektion saknas</t>
+          <t>Saknar standardfras om pedagogiskt stöd</t>
         </is>
       </c>
       <c r="D468" t="inlineStr">
         <is>
-          <t>Ingen Övrigt-sektion i kursplanen</t>
+          <t>Saknar standardfras om pedagogiskt stöd: Kursen ingår i Samhällsvetarprogrammet. Kursen ingår i kurspaketet Statsvetenskap III. Kursen motsvarar SK2001.…</t>
         </is>
       </c>
       <c r="E468" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ATR26B</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SK2013</t>
         </is>
       </c>
     </row>
     <row r="469">
       <c r="A469" s="2" t="inlineStr">
         <is>
-          <t>GTR22D</t>
+          <t>SK2015</t>
         </is>
       </c>
       <c r="B469" t="inlineStr">
         <is>
-          <t>TRU</t>
+          <t>SKA</t>
         </is>
       </c>
       <c r="C469" t="inlineStr">
@@ -13096,24 +13096,24 @@
       </c>
       <c r="D469" t="inlineStr">
         <is>
-          <t>Saknar standardfras om pedagogiskt stöd: Antalet examinationstillfällen är högst 5 av varje modul.…</t>
+          <t>Saknar standardfras om pedagogiskt stöd: Kursen kan inte tillgodoräknas i examen parallellt med Samhällsvetenskapliga metoder II - inriktning sociologi på grund …</t>
         </is>
       </c>
       <c r="E469" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTR22D</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SK2015</t>
         </is>
       </c>
     </row>
     <row r="470">
       <c r="A470" s="2" t="inlineStr">
         <is>
-          <t>GTR265</t>
+          <t>SK2016</t>
         </is>
       </c>
       <c r="B470" t="inlineStr">
         <is>
-          <t>TRU</t>
+          <t>SKA</t>
         </is>
       </c>
       <c r="C470" t="inlineStr">
@@ -13123,24 +13123,24 @@
       </c>
       <c r="D470" t="inlineStr">
         <is>
-          <t>Saknar standardfras om pedagogiskt stöd: Ersätter TR1027.…</t>
+          <t>Saknar standardfras om pedagogiskt stöd: Kursen ingår i Samhällsvetarprogrammet. Kursen ingår i kurspaketet Statsvetenskap III. Kursen motsvarar SK2007.…</t>
         </is>
       </c>
       <c r="E470" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTR265</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SK2016</t>
         </is>
       </c>
     </row>
     <row r="471">
       <c r="A471" s="2" t="inlineStr">
         <is>
-          <t>GTR26E</t>
+          <t>GSO2PL</t>
         </is>
       </c>
       <c r="B471" t="inlineStr">
         <is>
-          <t>TRU</t>
+          <t>SOA</t>
         </is>
       </c>
       <c r="C471" t="inlineStr">
@@ -13150,51 +13150,51 @@
       </c>
       <c r="D471" t="inlineStr">
         <is>
-          <t>Saknar standardfras om pedagogiskt stöd: Erätter TR1035.…</t>
+          <t>Saknar standardfras om pedagogiskt stöd: Kursen ingår i Socionomprogrammet. Kursen motsvarar GSO26K.…</t>
         </is>
       </c>
       <c r="E471" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTR26E</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSO2PL</t>
         </is>
       </c>
     </row>
     <row r="472">
       <c r="A472" s="2" t="inlineStr">
         <is>
-          <t>GTR296</t>
+          <t>GSO2UA</t>
         </is>
       </c>
       <c r="B472" t="inlineStr">
         <is>
-          <t>TRU</t>
+          <t>SOA</t>
         </is>
       </c>
       <c r="C472" t="inlineStr">
         <is>
-          <t>Sektion saknas</t>
+          <t>Saknar standardfras om pedagogiskt stöd</t>
         </is>
       </c>
       <c r="D472" t="inlineStr">
         <is>
-          <t>Ingen Övrigt-sektion i kursplanen</t>
+          <t>Saknar standardfras om pedagogiskt stöd: Kursen motsvarar SO1023 samt SO1028…</t>
         </is>
       </c>
       <c r="E472" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTR296</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSO2UA</t>
         </is>
       </c>
     </row>
     <row r="473">
       <c r="A473" s="2" t="inlineStr">
         <is>
-          <t>GTR29Q</t>
+          <t>GSO2UC</t>
         </is>
       </c>
       <c r="B473" t="inlineStr">
         <is>
-          <t>TRU</t>
+          <t>SOA</t>
         </is>
       </c>
       <c r="C473" t="inlineStr">
@@ -13204,51 +13204,51 @@
       </c>
       <c r="D473" t="inlineStr">
         <is>
-          <t>Saknar standardfras om pedagogiskt stöd: Ersätter TR1028.…</t>
+          <t>Saknar standardfras om pedagogiskt stöd: Det krävs att den studerande kan kommunicera med både ljud och bild via en dator Ersätter kursen GSO29C.…</t>
         </is>
       </c>
       <c r="E473" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTR29Q</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSO2UC</t>
         </is>
       </c>
     </row>
     <row r="474">
       <c r="A474" s="2" t="inlineStr">
         <is>
-          <t>GTR2CT</t>
+          <t>GSO2XU</t>
         </is>
       </c>
       <c r="B474" t="inlineStr">
         <is>
-          <t>TRU</t>
+          <t>SOA</t>
         </is>
       </c>
       <c r="C474" t="inlineStr">
         <is>
-          <t>Sektion saknas</t>
+          <t>Saknar standardfras om pedagogiskt stöd</t>
         </is>
       </c>
       <c r="D474" t="inlineStr">
         <is>
-          <t>Ingen Övrigt-sektion i kursplanen</t>
+          <t>Saknar standardfras om pedagogiskt stöd: Kursen motsvarar SO1038 samt SO1041.…</t>
         </is>
       </c>
       <c r="E474" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTR2CT</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSO2XU</t>
         </is>
       </c>
     </row>
     <row r="475">
       <c r="A475" s="2" t="inlineStr">
         <is>
-          <t>GTR2DG</t>
+          <t>GSO2XV</t>
         </is>
       </c>
       <c r="B475" t="inlineStr">
         <is>
-          <t>TRU</t>
+          <t>SOA</t>
         </is>
       </c>
       <c r="C475" t="inlineStr">
@@ -13258,78 +13258,78 @@
       </c>
       <c r="D475" t="inlineStr">
         <is>
-          <t>Saknar standardfras om pedagogiskt stöd: Ersätter TR2004.…</t>
+          <t>Saknar standardfras om pedagogiskt stöd: Kursen motsvarar SO2007 samt SO2009.…</t>
         </is>
       </c>
       <c r="E475" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTR2DG</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSO2XV</t>
         </is>
       </c>
     </row>
     <row r="476">
       <c r="A476" s="2" t="inlineStr">
         <is>
-          <t>GTR2DP</t>
+          <t>GSO33U</t>
         </is>
       </c>
       <c r="B476" t="inlineStr">
         <is>
-          <t>TRU</t>
+          <t>SOA</t>
         </is>
       </c>
       <c r="C476" t="inlineStr">
         <is>
-          <t>Sektion saknas</t>
+          <t>Saknar standardfras om pedagogiskt stöd</t>
         </is>
       </c>
       <c r="D476" t="inlineStr">
         <is>
-          <t>Ingen Övrigt-sektion i kursplanen</t>
+          <t>Saknar standardfras om pedagogiskt stöd: Kursen överlappar SO2007, SO2009 samt GSO2XV.…</t>
         </is>
       </c>
       <c r="E476" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTR2DP</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSO33U</t>
         </is>
       </c>
     </row>
     <row r="477">
       <c r="A477" s="2" t="inlineStr">
         <is>
-          <t>GTR2G6</t>
+          <t>SO1006</t>
         </is>
       </c>
       <c r="B477" t="inlineStr">
         <is>
-          <t>TRU</t>
+          <t>SOA</t>
         </is>
       </c>
       <c r="C477" t="inlineStr">
         <is>
-          <t>Sektion saknas</t>
+          <t>Saknar standardfras om pedagogiskt stöd</t>
         </is>
       </c>
       <c r="D477" t="inlineStr">
         <is>
-          <t>Ingen Övrigt-sektion i kursplanen</t>
+          <t>Saknar standardfras om pedagogiskt stöd: Kursen kan tillgodoräknas i Sociologi I 30 högskolepoäng. Kursen motsvarar SOA023 Avvikande beteende A, 5 poäng.…</t>
         </is>
       </c>
       <c r="E477" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTR2G6</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SO1006</t>
         </is>
       </c>
     </row>
     <row r="478">
       <c r="A478" s="2" t="inlineStr">
         <is>
-          <t>GTR2HA</t>
+          <t>SO1019</t>
         </is>
       </c>
       <c r="B478" t="inlineStr">
         <is>
-          <t>TRU</t>
+          <t>SOA</t>
         </is>
       </c>
       <c r="C478" t="inlineStr">
@@ -13339,78 +13339,78 @@
       </c>
       <c r="D478" t="inlineStr">
         <is>
-          <t>Saknar standardfras om pedagogiskt stöd: Studenten ansvarar för val och anskaffning av praktikplats. Dock måste praktikplatsen godkännas av kursansvarig innan på…</t>
+          <t>Saknar standardfras om pedagogiskt stöd: Antal provtillfällen begränsas till fem.…</t>
         </is>
       </c>
       <c r="E478" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTR2HA</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SO1019</t>
         </is>
       </c>
     </row>
     <row r="479">
       <c r="A479" s="2" t="inlineStr">
         <is>
-          <t>GTR2K8</t>
+          <t>SO1027</t>
         </is>
       </c>
       <c r="B479" t="inlineStr">
         <is>
-          <t>TRU</t>
+          <t>SOA</t>
         </is>
       </c>
       <c r="C479" t="inlineStr">
         <is>
-          <t>Sektion saknas</t>
+          <t>Saknar standardfras om pedagogiskt stöd</t>
         </is>
       </c>
       <c r="D479" t="inlineStr">
         <is>
-          <t>Ingen Övrigt-sektion i kursplanen</t>
+          <t>Saknar standardfras om pedagogiskt stöd: Kursen ges på engelska.…</t>
         </is>
       </c>
       <c r="E479" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTR2K8</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SO1027</t>
         </is>
       </c>
     </row>
     <row r="480">
       <c r="A480" s="2" t="inlineStr">
         <is>
-          <t>GTR2UM</t>
+          <t>SO1030</t>
         </is>
       </c>
       <c r="B480" t="inlineStr">
         <is>
-          <t>TRU</t>
+          <t>SOA</t>
         </is>
       </c>
       <c r="C480" t="inlineStr">
         <is>
-          <t>Sektion saknas</t>
+          <t>Saknar standardfras om pedagogiskt stöd</t>
         </is>
       </c>
       <c r="D480" t="inlineStr">
         <is>
-          <t>Ingen Övrigt-sektion i kursplanen</t>
+          <t>Saknar standardfras om pedagogiskt stöd: För varje kurstillfälle ges maximalt 5 examenstillfällen. Kursen ingår i samhällsvetarprogrammet. Kursen motsvarar SO101…</t>
         </is>
       </c>
       <c r="E480" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTR2UM</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SO1030</t>
         </is>
       </c>
     </row>
     <row r="481">
       <c r="A481" s="2" t="inlineStr">
         <is>
-          <t>GTR2UP</t>
+          <t>SO1033</t>
         </is>
       </c>
       <c r="B481" t="inlineStr">
         <is>
-          <t>TRU</t>
+          <t>SOA</t>
         </is>
       </c>
       <c r="C481" t="inlineStr">
@@ -13420,105 +13420,105 @@
       </c>
       <c r="D481" t="inlineStr">
         <is>
-          <t>Saknar standardfras om pedagogiskt stöd: Ersätter TR1036…</t>
+          <t>Saknar standardfras om pedagogiskt stöd: Antal provtillfällen begränsas till fem. Kursen ges på engelska.…</t>
         </is>
       </c>
       <c r="E481" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTR2UP</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SO1033</t>
         </is>
       </c>
     </row>
     <row r="482">
       <c r="A482" s="2" t="inlineStr">
         <is>
-          <t>TR1007</t>
+          <t>SO1034</t>
         </is>
       </c>
       <c r="B482" t="inlineStr">
         <is>
-          <t>TRU</t>
+          <t>SOA</t>
         </is>
       </c>
       <c r="C482" t="inlineStr">
         <is>
-          <t>Sektion saknas</t>
+          <t>Saknar standardfras om pedagogiskt stöd</t>
         </is>
       </c>
       <c r="D482" t="inlineStr">
         <is>
-          <t>Ingen Övrigt-sektion i kursplanen</t>
+          <t>Saknar standardfras om pedagogiskt stöd: Denna kurs ingår i Samhällsvetarprogrammet. Kursen motsvarar SO1020.…</t>
         </is>
       </c>
       <c r="E482" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TR1007</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SO1034</t>
         </is>
       </c>
     </row>
     <row r="483">
       <c r="A483" s="2" t="inlineStr">
         <is>
-          <t>TR1011</t>
+          <t>SO1037</t>
         </is>
       </c>
       <c r="B483" t="inlineStr">
         <is>
-          <t>TRU</t>
+          <t>SOA</t>
         </is>
       </c>
       <c r="C483" t="inlineStr">
         <is>
-          <t>Sektion saknas</t>
+          <t>Saknar standardfras om pedagogiskt stöd</t>
         </is>
       </c>
       <c r="D483" t="inlineStr">
         <is>
-          <t>Ingen Övrigt-sektion i kursplanen</t>
+          <t>Saknar standardfras om pedagogiskt stöd: Kursen motsvarar SO1033.…</t>
         </is>
       </c>
       <c r="E483" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TR1011</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SO1037</t>
         </is>
       </c>
     </row>
     <row r="484">
       <c r="A484" s="2" t="inlineStr">
         <is>
-          <t>TR1013</t>
+          <t>SO1044</t>
         </is>
       </c>
       <c r="B484" t="inlineStr">
         <is>
-          <t>TRU</t>
+          <t>SOA</t>
         </is>
       </c>
       <c r="C484" t="inlineStr">
         <is>
-          <t>Sektion saknas</t>
+          <t>Saknar standardfras om pedagogiskt stöd</t>
         </is>
       </c>
       <c r="D484" t="inlineStr">
         <is>
-          <t>Ingen Övrigt-sektion i kursplanen</t>
+          <t>Saknar standardfras om pedagogiskt stöd: Kursen ingår i Socionomprogrammet. Kursen motsvarar delkurs 1 i SO1021.…</t>
         </is>
       </c>
       <c r="E484" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TR1013</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SO1044</t>
         </is>
       </c>
     </row>
     <row r="485">
       <c r="A485" s="2" t="inlineStr">
         <is>
-          <t>TR1016</t>
+          <t>SO1047</t>
         </is>
       </c>
       <c r="B485" t="inlineStr">
         <is>
-          <t>TRU</t>
+          <t>SOA</t>
         </is>
       </c>
       <c r="C485" t="inlineStr">
@@ -13528,19 +13528,19 @@
       </c>
       <c r="D485" t="inlineStr">
         <is>
-          <t>Saknar standardfras om pedagogiskt stöd: Max fem examinationstillfällen erbjuds.…</t>
+          <t>Saknar standardfras om pedagogiskt stöd: Kursen ingår i Sport Managementprogrammet och som valbar kurs i Samhällsvetarprogrammet. Kursen motsvarar delar av SO100…</t>
         </is>
       </c>
       <c r="E485" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TR1016</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SO1047</t>
         </is>
       </c>
     </row>
     <row r="486">
       <c r="A486" s="2" t="inlineStr">
         <is>
-          <t>TR1018</t>
+          <t>ATR25Z</t>
         </is>
       </c>
       <c r="B486" t="inlineStr">
@@ -13550,24 +13550,24 @@
       </c>
       <c r="C486" t="inlineStr">
         <is>
-          <t>Saknar standardfras om pedagogiskt stöd</t>
+          <t>Sektion saknas</t>
         </is>
       </c>
       <c r="D486" t="inlineStr">
         <is>
-          <t>Saknar standardfras om pedagogiskt stöd: Max 5 examinationstillfällen.…</t>
+          <t>Ingen Övrigt-sektion i kursplanen</t>
         </is>
       </c>
       <c r="E486" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TR1018</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ATR25Z</t>
         </is>
       </c>
     </row>
     <row r="487">
       <c r="A487" s="2" t="inlineStr">
         <is>
-          <t>TR1019</t>
+          <t>ATR26B</t>
         </is>
       </c>
       <c r="B487" t="inlineStr">
@@ -13577,24 +13577,24 @@
       </c>
       <c r="C487" t="inlineStr">
         <is>
-          <t>Saknar standardfras om pedagogiskt stöd</t>
+          <t>Sektion saknas</t>
         </is>
       </c>
       <c r="D487" t="inlineStr">
         <is>
-          <t>Saknar standardfras om pedagogiskt stöd: Max fem tentamenstillfällen Vid sent inlämnade arbeten kan högst betyget C erhållas. Kan ej ingå i en examen samtidigt s…</t>
+          <t>Ingen Övrigt-sektion i kursplanen</t>
         </is>
       </c>
       <c r="E487" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TR1019</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ATR26B</t>
         </is>
       </c>
     </row>
     <row r="488">
       <c r="A488" s="2" t="inlineStr">
         <is>
-          <t>TR1024</t>
+          <t>GTR22D</t>
         </is>
       </c>
       <c r="B488" t="inlineStr">
@@ -13604,24 +13604,24 @@
       </c>
       <c r="C488" t="inlineStr">
         <is>
-          <t>Sektion saknas</t>
+          <t>Saknar standardfras om pedagogiskt stöd</t>
         </is>
       </c>
       <c r="D488" t="inlineStr">
         <is>
-          <t>Ingen Övrigt-sektion i kursplanen</t>
+          <t>Saknar standardfras om pedagogiskt stöd: Antalet examinationstillfällen är högst 5 av varje modul.…</t>
         </is>
       </c>
       <c r="E488" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TR1024</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTR22D</t>
         </is>
       </c>
     </row>
     <row r="489">
       <c r="A489" s="2" t="inlineStr">
         <is>
-          <t>TR1025</t>
+          <t>GTR265</t>
         </is>
       </c>
       <c r="B489" t="inlineStr">
@@ -13636,19 +13636,19 @@
       </c>
       <c r="D489" t="inlineStr">
         <is>
-          <t>Saknar standardfras om pedagogiskt stöd: Maximalt fem examinationer Kursen ersätter FEC041, FEC061…</t>
+          <t>Saknar standardfras om pedagogiskt stöd: Ersätter TR1027.…</t>
         </is>
       </c>
       <c r="E489" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TR1025</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTR265</t>
         </is>
       </c>
     </row>
     <row r="490">
       <c r="A490" s="2" t="inlineStr">
         <is>
-          <t>TR1027</t>
+          <t>GTR26E</t>
         </is>
       </c>
       <c r="B490" t="inlineStr">
@@ -13663,19 +13663,19 @@
       </c>
       <c r="D490" t="inlineStr">
         <is>
-          <t>Saknar standardfras om pedagogiskt stöd: Ersätter TR1024.…</t>
+          <t>Saknar standardfras om pedagogiskt stöd: Erätter TR1035.…</t>
         </is>
       </c>
       <c r="E490" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TR1027</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTR26E</t>
         </is>
       </c>
     </row>
     <row r="491">
       <c r="A491" s="2" t="inlineStr">
         <is>
-          <t>TR1028</t>
+          <t>GTR296</t>
         </is>
       </c>
       <c r="B491" t="inlineStr">
@@ -13685,24 +13685,24 @@
       </c>
       <c r="C491" t="inlineStr">
         <is>
-          <t>Saknar standardfras om pedagogiskt stöd</t>
+          <t>Sektion saknas</t>
         </is>
       </c>
       <c r="D491" t="inlineStr">
         <is>
-          <t>Saknar standardfras om pedagogiskt stöd: Ersätter TR1023…</t>
+          <t>Ingen Övrigt-sektion i kursplanen</t>
         </is>
       </c>
       <c r="E491" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TR1028</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTR296</t>
         </is>
       </c>
     </row>
     <row r="492">
       <c r="A492" s="2" t="inlineStr">
         <is>
-          <t>TR1029</t>
+          <t>GTR29Q</t>
         </is>
       </c>
       <c r="B492" t="inlineStr">
@@ -13717,19 +13717,19 @@
       </c>
       <c r="D492" t="inlineStr">
         <is>
-          <t>Saknar standardfras om pedagogiskt stöd: Maximalt fem examinationer Kursen ersätter TR1025.…</t>
+          <t>Saknar standardfras om pedagogiskt stöd: Ersätter TR1028.…</t>
         </is>
       </c>
       <c r="E492" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TR1029</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTR29Q</t>
         </is>
       </c>
     </row>
     <row r="493">
       <c r="A493" s="2" t="inlineStr">
         <is>
-          <t>TR1030</t>
+          <t>GTR2CT</t>
         </is>
       </c>
       <c r="B493" t="inlineStr">
@@ -13739,24 +13739,24 @@
       </c>
       <c r="C493" t="inlineStr">
         <is>
-          <t>Saknar standardfras om pedagogiskt stöd</t>
+          <t>Sektion saknas</t>
         </is>
       </c>
       <c r="D493" t="inlineStr">
         <is>
-          <t>Saknar standardfras om pedagogiskt stöd: Max fem examinationstillfällen. Ersätter TR1015.…</t>
+          <t>Ingen Övrigt-sektion i kursplanen</t>
         </is>
       </c>
       <c r="E493" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TR1030</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTR2CT</t>
         </is>
       </c>
     </row>
     <row r="494">
       <c r="A494" s="2" t="inlineStr">
         <is>
-          <t>TR1031</t>
+          <t>GTR2DG</t>
         </is>
       </c>
       <c r="B494" t="inlineStr">
@@ -13771,19 +13771,19 @@
       </c>
       <c r="D494" t="inlineStr">
         <is>
-          <t>Saknar standardfras om pedagogiskt stöd: Ersätter TR1011.…</t>
+          <t>Saknar standardfras om pedagogiskt stöd: Ersätter TR2004.…</t>
         </is>
       </c>
       <c r="E494" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TR1031</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTR2DG</t>
         </is>
       </c>
     </row>
     <row r="495">
       <c r="A495" s="2" t="inlineStr">
         <is>
-          <t>TR1033</t>
+          <t>GTR2DP</t>
         </is>
       </c>
       <c r="B495" t="inlineStr">
@@ -13793,24 +13793,24 @@
       </c>
       <c r="C495" t="inlineStr">
         <is>
-          <t>Saknar standardfras om pedagogiskt stöd</t>
+          <t>Sektion saknas</t>
         </is>
       </c>
       <c r="D495" t="inlineStr">
         <is>
-          <t>Saknar standardfras om pedagogiskt stöd: Kursen ersätter TR1014. Kursen kan inte tillgodoräknas i en examen samtidigt som kursen Turismen i den globala ekonomin,…</t>
+          <t>Ingen Övrigt-sektion i kursplanen</t>
         </is>
       </c>
       <c r="E495" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TR1033</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTR2DP</t>
         </is>
       </c>
     </row>
     <row r="496">
       <c r="A496" s="2" t="inlineStr">
         <is>
-          <t>TR1034</t>
+          <t>GTR2G6</t>
         </is>
       </c>
       <c r="B496" t="inlineStr">
@@ -13820,24 +13820,24 @@
       </c>
       <c r="C496" t="inlineStr">
         <is>
-          <t>Saknar standardfras om pedagogiskt stöd</t>
+          <t>Sektion saknas</t>
         </is>
       </c>
       <c r="D496" t="inlineStr">
         <is>
-          <t>Saknar standardfras om pedagogiskt stöd: Studenten ansvarar för val och anskaffning av praktikplats. Dock måste praktikplatsen godkännas av kursansvarig innan på…</t>
+          <t>Ingen Övrigt-sektion i kursplanen</t>
         </is>
       </c>
       <c r="E496" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TR1034</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTR2G6</t>
         </is>
       </c>
     </row>
     <row r="497">
       <c r="A497" s="2" t="inlineStr">
         <is>
-          <t>TR1035</t>
+          <t>GTR2HA</t>
         </is>
       </c>
       <c r="B497" t="inlineStr">
@@ -13847,24 +13847,24 @@
       </c>
       <c r="C497" t="inlineStr">
         <is>
-          <t>Sektion saknas</t>
+          <t>Saknar standardfras om pedagogiskt stöd</t>
         </is>
       </c>
       <c r="D497" t="inlineStr">
         <is>
-          <t>Ingen Övrigt-sektion i kursplanen</t>
+          <t>Saknar standardfras om pedagogiskt stöd: Studenten ansvarar för val och anskaffning av praktikplats. Dock måste praktikplatsen godkännas av kursansvarig innan på…</t>
         </is>
       </c>
       <c r="E497" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TR1035</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTR2HA</t>
         </is>
       </c>
     </row>
     <row r="498">
       <c r="A498" s="2" t="inlineStr">
         <is>
-          <t>TR1036</t>
+          <t>GTR2K8</t>
         </is>
       </c>
       <c r="B498" t="inlineStr">
@@ -13874,24 +13874,24 @@
       </c>
       <c r="C498" t="inlineStr">
         <is>
-          <t>Saknar standardfras om pedagogiskt stöd</t>
+          <t>Sektion saknas</t>
         </is>
       </c>
       <c r="D498" t="inlineStr">
         <is>
-          <t>Saknar standardfras om pedagogiskt stöd: Antalet examinationstillfällen är högst 5 av varje modul.…</t>
+          <t>Ingen Övrigt-sektion i kursplanen</t>
         </is>
       </c>
       <c r="E498" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TR1036</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTR2K8</t>
         </is>
       </c>
     </row>
     <row r="499">
       <c r="A499" s="2" t="inlineStr">
         <is>
-          <t>TR2004</t>
+          <t>GTR2UM</t>
         </is>
       </c>
       <c r="B499" t="inlineStr">
@@ -13901,24 +13901,24 @@
       </c>
       <c r="C499" t="inlineStr">
         <is>
-          <t>Saknar standardfras om pedagogiskt stöd</t>
+          <t>Sektion saknas</t>
         </is>
       </c>
       <c r="D499" t="inlineStr">
         <is>
-          <t>Saknar standardfras om pedagogiskt stöd: Max 5 examinationstillfällen per delkurs. Ersätter TR2001.…</t>
+          <t>Ingen Övrigt-sektion i kursplanen</t>
         </is>
       </c>
       <c r="E499" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TR2004</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTR2UM</t>
         </is>
       </c>
     </row>
     <row r="500">
       <c r="A500" s="2" t="inlineStr">
         <is>
-          <t>TR2005</t>
+          <t>GTR2UP</t>
         </is>
       </c>
       <c r="B500" t="inlineStr">
@@ -13933,19 +13933,19 @@
       </c>
       <c r="D500" t="inlineStr">
         <is>
-          <t>Saknar standardfras om pedagogiskt stöd: Max 5 examinationstillfällen Varje uppsats förfogar över 20 timmar handledning. Betyg A eller B kan endast erhållas om u…</t>
+          <t>Saknar standardfras om pedagogiskt stöd: Ersätter TR1036…</t>
         </is>
       </c>
       <c r="E500" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TR2005</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTR2UP</t>
         </is>
       </c>
     </row>
     <row r="501">
       <c r="A501" s="2" t="inlineStr">
         <is>
-          <t>TR3006</t>
+          <t>TR1007</t>
         </is>
       </c>
       <c r="B501" t="inlineStr">
@@ -13965,14 +13965,14 @@
       </c>
       <c r="E501" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TR3006</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TR1007</t>
         </is>
       </c>
     </row>
     <row r="502">
       <c r="A502" s="2" t="inlineStr">
         <is>
-          <t>TR3008</t>
+          <t>TR1011</t>
         </is>
       </c>
       <c r="B502" t="inlineStr">
@@ -13982,24 +13982,24 @@
       </c>
       <c r="C502" t="inlineStr">
         <is>
-          <t>Saknar standardfras om pedagogiskt stöd</t>
+          <t>Sektion saknas</t>
         </is>
       </c>
       <c r="D502" t="inlineStr">
         <is>
-          <t>Saknar standardfras om pedagogiskt stöd: Max 5 examinationstillfällen Varje uppsats förfogar över 20 timmar handledning. Examinator bestämmer sista dag för inläm…</t>
+          <t>Ingen Övrigt-sektion i kursplanen</t>
         </is>
       </c>
       <c r="E502" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TR3008</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TR1011</t>
         </is>
       </c>
     </row>
     <row r="503">
       <c r="A503" s="2" t="inlineStr">
         <is>
-          <t>TR3009</t>
+          <t>TR1013</t>
         </is>
       </c>
       <c r="B503" t="inlineStr">
@@ -14009,24 +14009,24 @@
       </c>
       <c r="C503" t="inlineStr">
         <is>
-          <t>Saknar standardfras om pedagogiskt stöd</t>
+          <t>Sektion saknas</t>
         </is>
       </c>
       <c r="D503" t="inlineStr">
         <is>
-          <t>Saknar standardfras om pedagogiskt stöd: Ersätter TR3006.…</t>
+          <t>Ingen Övrigt-sektion i kursplanen</t>
         </is>
       </c>
       <c r="E503" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TR3009</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TR1013</t>
         </is>
       </c>
     </row>
     <row r="504">
       <c r="A504" s="2" t="inlineStr">
         <is>
-          <t>TR3010</t>
+          <t>TR1016</t>
         </is>
       </c>
       <c r="B504" t="inlineStr">
@@ -14041,51 +14041,51 @@
       </c>
       <c r="D504" t="inlineStr">
         <is>
-          <t>Saknar standardfras om pedagogiskt stöd: Antal examinationstillfällen är begränsade till fem för varje examinationsmoment. Kursen ersätter KG3016.…</t>
+          <t>Saknar standardfras om pedagogiskt stöd: Max fem examinationstillfällen erbjuds.…</t>
         </is>
       </c>
       <c r="E504" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TR3010</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TR1016</t>
         </is>
       </c>
     </row>
     <row r="505">
       <c r="A505" s="2" t="inlineStr">
         <is>
-          <t>AS2001</t>
+          <t>TR1018</t>
         </is>
       </c>
       <c r="B505" t="inlineStr">
         <is>
-          <t>UVX</t>
+          <t>TRU</t>
         </is>
       </c>
       <c r="C505" t="inlineStr">
         <is>
-          <t>Sektion saknas</t>
+          <t>Saknar standardfras om pedagogiskt stöd</t>
         </is>
       </c>
       <c r="D505" t="inlineStr">
         <is>
-          <t>Ingen Övrigt-sektion i kursplanen</t>
+          <t>Saknar standardfras om pedagogiskt stöd: Max 5 examinationstillfällen.…</t>
         </is>
       </c>
       <c r="E505" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AS2001</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TR1018</t>
         </is>
       </c>
     </row>
     <row r="506">
       <c r="A506" s="2" t="inlineStr">
         <is>
-          <t>AS2002</t>
+          <t>TR1019</t>
         </is>
       </c>
       <c r="B506" t="inlineStr">
         <is>
-          <t>UVX</t>
+          <t>TRU</t>
         </is>
       </c>
       <c r="C506" t="inlineStr">
@@ -14095,51 +14095,51 @@
       </c>
       <c r="D506" t="inlineStr">
         <is>
-          <t>Saknar standardfras om pedagogiskt stöd: Ersätter HI2002.…</t>
+          <t>Saknar standardfras om pedagogiskt stöd: Max fem tentamenstillfällen Vid sent inlämnade arbeten kan högst betyget C erhållas. Kan ej ingå i en examen samtidigt s…</t>
         </is>
       </c>
       <c r="E506" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AS2002</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TR1019</t>
         </is>
       </c>
     </row>
     <row r="507">
       <c r="A507" s="2" t="inlineStr">
         <is>
-          <t>AS2003</t>
+          <t>TR1024</t>
         </is>
       </c>
       <c r="B507" t="inlineStr">
         <is>
-          <t>UVX</t>
+          <t>TRU</t>
         </is>
       </c>
       <c r="C507" t="inlineStr">
         <is>
-          <t>Saknar standardfras om pedagogiskt stöd</t>
+          <t>Sektion saknas</t>
         </is>
       </c>
       <c r="D507" t="inlineStr">
         <is>
-          <t>Saknar standardfras om pedagogiskt stöd: Ersätter HI2003.…</t>
+          <t>Ingen Övrigt-sektion i kursplanen</t>
         </is>
       </c>
       <c r="E507" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AS2003</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TR1024</t>
         </is>
       </c>
     </row>
     <row r="508">
       <c r="A508" s="2" t="inlineStr">
         <is>
-          <t>AS3001</t>
+          <t>TR1025</t>
         </is>
       </c>
       <c r="B508" t="inlineStr">
         <is>
-          <t>UVX</t>
+          <t>TRU</t>
         </is>
       </c>
       <c r="C508" t="inlineStr">
@@ -14149,24 +14149,24 @@
       </c>
       <c r="D508" t="inlineStr">
         <is>
-          <t>Saknar standardfras om pedagogiskt stöd: Ersätter HI3003.…</t>
+          <t>Saknar standardfras om pedagogiskt stöd: Maximalt fem examinationer Kursen ersätter FEC041, FEC061…</t>
         </is>
       </c>
       <c r="E508" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AS3001</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TR1025</t>
         </is>
       </c>
     </row>
     <row r="509">
       <c r="A509" s="2" t="inlineStr">
         <is>
-          <t>AS3002</t>
+          <t>TR1027</t>
         </is>
       </c>
       <c r="B509" t="inlineStr">
         <is>
-          <t>UVX</t>
+          <t>TRU</t>
         </is>
       </c>
       <c r="C509" t="inlineStr">
@@ -14176,24 +14176,24 @@
       </c>
       <c r="D509" t="inlineStr">
         <is>
-          <t>Saknar standardfras om pedagogiskt stöd: Ersätter HI3001.…</t>
+          <t>Saknar standardfras om pedagogiskt stöd: Ersätter TR1024.…</t>
         </is>
       </c>
       <c r="E509" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AS3002</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TR1027</t>
         </is>
       </c>
     </row>
     <row r="510">
       <c r="A510" s="2" t="inlineStr">
         <is>
-          <t>AS3003</t>
+          <t>TR1028</t>
         </is>
       </c>
       <c r="B510" t="inlineStr">
         <is>
-          <t>UVX</t>
+          <t>TRU</t>
         </is>
       </c>
       <c r="C510" t="inlineStr">
@@ -14203,24 +14203,24 @@
       </c>
       <c r="D510" t="inlineStr">
         <is>
-          <t>Saknar standardfras om pedagogiskt stöd: Ersätter HI3002.…</t>
+          <t>Saknar standardfras om pedagogiskt stöd: Ersätter TR1023…</t>
         </is>
       </c>
       <c r="E510" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AS3003</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TR1028</t>
         </is>
       </c>
     </row>
     <row r="511">
       <c r="A511" s="2" t="inlineStr">
         <is>
-          <t>AS3004</t>
+          <t>TR1029</t>
         </is>
       </c>
       <c r="B511" t="inlineStr">
         <is>
-          <t>UVX</t>
+          <t>TRU</t>
         </is>
       </c>
       <c r="C511" t="inlineStr">
@@ -14230,24 +14230,24 @@
       </c>
       <c r="D511" t="inlineStr">
         <is>
-          <t>Saknar standardfras om pedagogiskt stöd: Ersätter HI3015.…</t>
+          <t>Saknar standardfras om pedagogiskt stöd: Maximalt fem examinationer Kursen ersätter TR1025.…</t>
         </is>
       </c>
       <c r="E511" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AS3004</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TR1029</t>
         </is>
       </c>
     </row>
     <row r="512">
       <c r="A512" s="2" t="inlineStr">
         <is>
-          <t>AS3005</t>
+          <t>TR1030</t>
         </is>
       </c>
       <c r="B512" t="inlineStr">
         <is>
-          <t>UVX</t>
+          <t>TRU</t>
         </is>
       </c>
       <c r="C512" t="inlineStr">
@@ -14257,24 +14257,24 @@
       </c>
       <c r="D512" t="inlineStr">
         <is>
-          <t>Saknar standardfras om pedagogiskt stöd: Ersätter HI3010.…</t>
+          <t>Saknar standardfras om pedagogiskt stöd: Max fem examinationstillfällen. Ersätter TR1015.…</t>
         </is>
       </c>
       <c r="E512" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AS3005</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TR1030</t>
         </is>
       </c>
     </row>
     <row r="513">
       <c r="A513" s="2" t="inlineStr">
         <is>
-          <t>AS3006</t>
+          <t>TR1031</t>
         </is>
       </c>
       <c r="B513" t="inlineStr">
         <is>
-          <t>UVX</t>
+          <t>TRU</t>
         </is>
       </c>
       <c r="C513" t="inlineStr">
@@ -14284,24 +14284,24 @@
       </c>
       <c r="D513" t="inlineStr">
         <is>
-          <t>Saknar standardfras om pedagogiskt stöd: Ersätter VÅ3090.…</t>
+          <t>Saknar standardfras om pedagogiskt stöd: Ersätter TR1011.…</t>
         </is>
       </c>
       <c r="E513" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AS3006</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TR1031</t>
         </is>
       </c>
     </row>
     <row r="514">
       <c r="A514" s="2" t="inlineStr">
         <is>
-          <t>AS3007</t>
+          <t>TR1033</t>
         </is>
       </c>
       <c r="B514" t="inlineStr">
         <is>
-          <t>UVX</t>
+          <t>TRU</t>
         </is>
       </c>
       <c r="C514" t="inlineStr">
@@ -14311,24 +14311,24 @@
       </c>
       <c r="D514" t="inlineStr">
         <is>
-          <t>Saknar standardfras om pedagogiskt stöd: Ersätter RK3038.…</t>
+          <t>Saknar standardfras om pedagogiskt stöd: Kursen ersätter TR1014. Kursen kan inte tillgodoräknas i en examen samtidigt som kursen Turismen i den globala ekonomin,…</t>
         </is>
       </c>
       <c r="E514" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AS3007</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TR1033</t>
         </is>
       </c>
     </row>
     <row r="515">
       <c r="A515" s="2" t="inlineStr">
         <is>
-          <t>AS3008</t>
+          <t>TR1034</t>
         </is>
       </c>
       <c r="B515" t="inlineStr">
         <is>
-          <t>UVX</t>
+          <t>TRU</t>
         </is>
       </c>
       <c r="C515" t="inlineStr">
@@ -14338,51 +14338,51 @@
       </c>
       <c r="D515" t="inlineStr">
         <is>
-          <t>Saknar standardfras om pedagogiskt stöd: Ersätter RK3037.…</t>
+          <t>Saknar standardfras om pedagogiskt stöd: Studenten ansvarar för val och anskaffning av praktikplats. Dock måste praktikplatsen godkännas av kursansvarig innan på…</t>
         </is>
       </c>
       <c r="E515" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AS3008</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TR1034</t>
         </is>
       </c>
     </row>
     <row r="516">
       <c r="A516" s="2" t="inlineStr">
         <is>
-          <t>AS3009</t>
+          <t>TR1035</t>
         </is>
       </c>
       <c r="B516" t="inlineStr">
         <is>
-          <t>UVX</t>
+          <t>TRU</t>
         </is>
       </c>
       <c r="C516" t="inlineStr">
         <is>
-          <t>Saknar standardfras om pedagogiskt stöd</t>
+          <t>Sektion saknas</t>
         </is>
       </c>
       <c r="D516" t="inlineStr">
         <is>
-          <t>Saknar standardfras om pedagogiskt stöd: Ersätter HI3018.…</t>
+          <t>Ingen Övrigt-sektion i kursplanen</t>
         </is>
       </c>
       <c r="E516" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AS3009</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TR1035</t>
         </is>
       </c>
     </row>
     <row r="517">
       <c r="A517" s="2" t="inlineStr">
         <is>
-          <t>AS3010</t>
+          <t>TR1036</t>
         </is>
       </c>
       <c r="B517" t="inlineStr">
         <is>
-          <t>UVX</t>
+          <t>TRU</t>
         </is>
       </c>
       <c r="C517" t="inlineStr">
@@ -14392,24 +14392,24 @@
       </c>
       <c r="D517" t="inlineStr">
         <is>
-          <t>Saknar standardfras om pedagogiskt stöd: Ersätter HI3017.…</t>
+          <t>Saknar standardfras om pedagogiskt stöd: Antalet examinationstillfällen är högst 5 av varje modul.…</t>
         </is>
       </c>
       <c r="E517" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AS3010</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TR1036</t>
         </is>
       </c>
     </row>
     <row r="518">
       <c r="A518" s="2" t="inlineStr">
         <is>
-          <t>AS3011</t>
+          <t>TR2004</t>
         </is>
       </c>
       <c r="B518" t="inlineStr">
         <is>
-          <t>UVX</t>
+          <t>TRU</t>
         </is>
       </c>
       <c r="C518" t="inlineStr">
@@ -14419,24 +14419,24 @@
       </c>
       <c r="D518" t="inlineStr">
         <is>
-          <t>Saknar standardfras om pedagogiskt stöd: Ersätter HI3016.…</t>
+          <t>Saknar standardfras om pedagogiskt stöd: Max 5 examinationstillfällen per delkurs. Ersätter TR2001.…</t>
         </is>
       </c>
       <c r="E518" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AS3011</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TR2004</t>
         </is>
       </c>
     </row>
     <row r="519">
       <c r="A519" s="2" t="inlineStr">
         <is>
-          <t>AS3012</t>
+          <t>TR2005</t>
         </is>
       </c>
       <c r="B519" t="inlineStr">
         <is>
-          <t>UVX</t>
+          <t>TRU</t>
         </is>
       </c>
       <c r="C519" t="inlineStr">
@@ -14446,24 +14446,24 @@
       </c>
       <c r="D519" t="inlineStr">
         <is>
-          <t>Saknar standardfras om pedagogiskt stöd: Ersätter HI3014.…</t>
+          <t>Saknar standardfras om pedagogiskt stöd: Max 5 examinationstillfällen Varje uppsats förfogar över 20 timmar handledning. Betyg A eller B kan endast erhållas om u…</t>
         </is>
       </c>
       <c r="E519" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AS3012</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TR2005</t>
         </is>
       </c>
     </row>
     <row r="520">
       <c r="A520" s="2" t="inlineStr">
         <is>
-          <t>AS4001</t>
+          <t>TR3006</t>
         </is>
       </c>
       <c r="B520" t="inlineStr">
         <is>
-          <t>UVX</t>
+          <t>TRU</t>
         </is>
       </c>
       <c r="C520" t="inlineStr">
@@ -14478,93 +14478,606 @@
       </c>
       <c r="E520" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AS4001</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TR3006</t>
         </is>
       </c>
     </row>
     <row r="521">
       <c r="A521" s="2" t="inlineStr">
         <is>
-          <t>AS4002</t>
+          <t>TR3008</t>
         </is>
       </c>
       <c r="B521" t="inlineStr">
         <is>
-          <t>UVX</t>
+          <t>TRU</t>
         </is>
       </c>
       <c r="C521" t="inlineStr">
         <is>
-          <t>Sektion saknas</t>
+          <t>Saknar standardfras om pedagogiskt stöd</t>
         </is>
       </c>
       <c r="D521" t="inlineStr">
         <is>
-          <t>Ingen Övrigt-sektion i kursplanen</t>
+          <t>Saknar standardfras om pedagogiskt stöd: Max 5 examinationstillfällen Varje uppsats förfogar över 20 timmar handledning. Examinator bestämmer sista dag för inläm…</t>
         </is>
       </c>
       <c r="E521" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AS4002</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TR3008</t>
         </is>
       </c>
     </row>
     <row r="522">
       <c r="A522" s="2" t="inlineStr">
         <is>
-          <t>AS4003</t>
+          <t>TR3009</t>
         </is>
       </c>
       <c r="B522" t="inlineStr">
         <is>
-          <t>UVX</t>
+          <t>TRU</t>
         </is>
       </c>
       <c r="C522" t="inlineStr">
         <is>
-          <t>Sektion saknas</t>
+          <t>Saknar standardfras om pedagogiskt stöd</t>
         </is>
       </c>
       <c r="D522" t="inlineStr">
         <is>
-          <t>Ingen Övrigt-sektion i kursplanen</t>
+          <t>Saknar standardfras om pedagogiskt stöd: Ersätter TR3006.…</t>
         </is>
       </c>
       <c r="E522" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AS4003</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TR3009</t>
         </is>
       </c>
     </row>
     <row r="523">
       <c r="A523" s="2" t="inlineStr">
         <is>
+          <t>TR3010</t>
+        </is>
+      </c>
+      <c r="B523" t="inlineStr">
+        <is>
+          <t>TRU</t>
+        </is>
+      </c>
+      <c r="C523" t="inlineStr">
+        <is>
+          <t>Saknar standardfras om pedagogiskt stöd</t>
+        </is>
+      </c>
+      <c r="D523" t="inlineStr">
+        <is>
+          <t>Saknar standardfras om pedagogiskt stöd: Antal examinationstillfällen är begränsade till fem för varje examinationsmoment. Kursen ersätter KG3016.…</t>
+        </is>
+      </c>
+      <c r="E523" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TR3010</t>
+        </is>
+      </c>
+    </row>
+    <row r="524">
+      <c r="A524" s="2" t="inlineStr">
+        <is>
+          <t>AS2001</t>
+        </is>
+      </c>
+      <c r="B524" t="inlineStr">
+        <is>
+          <t>UVX</t>
+        </is>
+      </c>
+      <c r="C524" t="inlineStr">
+        <is>
+          <t>Sektion saknas</t>
+        </is>
+      </c>
+      <c r="D524" t="inlineStr">
+        <is>
+          <t>Ingen Övrigt-sektion i kursplanen</t>
+        </is>
+      </c>
+      <c r="E524" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AS2001</t>
+        </is>
+      </c>
+    </row>
+    <row r="525">
+      <c r="A525" s="2" t="inlineStr">
+        <is>
+          <t>AS2002</t>
+        </is>
+      </c>
+      <c r="B525" t="inlineStr">
+        <is>
+          <t>UVX</t>
+        </is>
+      </c>
+      <c r="C525" t="inlineStr">
+        <is>
+          <t>Saknar standardfras om pedagogiskt stöd</t>
+        </is>
+      </c>
+      <c r="D525" t="inlineStr">
+        <is>
+          <t>Saknar standardfras om pedagogiskt stöd: Ersätter HI2002.…</t>
+        </is>
+      </c>
+      <c r="E525" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AS2002</t>
+        </is>
+      </c>
+    </row>
+    <row r="526">
+      <c r="A526" s="2" t="inlineStr">
+        <is>
+          <t>AS2003</t>
+        </is>
+      </c>
+      <c r="B526" t="inlineStr">
+        <is>
+          <t>UVX</t>
+        </is>
+      </c>
+      <c r="C526" t="inlineStr">
+        <is>
+          <t>Saknar standardfras om pedagogiskt stöd</t>
+        </is>
+      </c>
+      <c r="D526" t="inlineStr">
+        <is>
+          <t>Saknar standardfras om pedagogiskt stöd: Ersätter HI2003.…</t>
+        </is>
+      </c>
+      <c r="E526" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AS2003</t>
+        </is>
+      </c>
+    </row>
+    <row r="527">
+      <c r="A527" s="2" t="inlineStr">
+        <is>
+          <t>AS3001</t>
+        </is>
+      </c>
+      <c r="B527" t="inlineStr">
+        <is>
+          <t>UVX</t>
+        </is>
+      </c>
+      <c r="C527" t="inlineStr">
+        <is>
+          <t>Saknar standardfras om pedagogiskt stöd</t>
+        </is>
+      </c>
+      <c r="D527" t="inlineStr">
+        <is>
+          <t>Saknar standardfras om pedagogiskt stöd: Ersätter HI3003.…</t>
+        </is>
+      </c>
+      <c r="E527" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AS3001</t>
+        </is>
+      </c>
+    </row>
+    <row r="528">
+      <c r="A528" s="2" t="inlineStr">
+        <is>
+          <t>AS3002</t>
+        </is>
+      </c>
+      <c r="B528" t="inlineStr">
+        <is>
+          <t>UVX</t>
+        </is>
+      </c>
+      <c r="C528" t="inlineStr">
+        <is>
+          <t>Saknar standardfras om pedagogiskt stöd</t>
+        </is>
+      </c>
+      <c r="D528" t="inlineStr">
+        <is>
+          <t>Saknar standardfras om pedagogiskt stöd: Ersätter HI3001.…</t>
+        </is>
+      </c>
+      <c r="E528" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AS3002</t>
+        </is>
+      </c>
+    </row>
+    <row r="529">
+      <c r="A529" s="2" t="inlineStr">
+        <is>
+          <t>AS3003</t>
+        </is>
+      </c>
+      <c r="B529" t="inlineStr">
+        <is>
+          <t>UVX</t>
+        </is>
+      </c>
+      <c r="C529" t="inlineStr">
+        <is>
+          <t>Saknar standardfras om pedagogiskt stöd</t>
+        </is>
+      </c>
+      <c r="D529" t="inlineStr">
+        <is>
+          <t>Saknar standardfras om pedagogiskt stöd: Ersätter HI3002.…</t>
+        </is>
+      </c>
+      <c r="E529" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AS3003</t>
+        </is>
+      </c>
+    </row>
+    <row r="530">
+      <c r="A530" s="2" t="inlineStr">
+        <is>
+          <t>AS3004</t>
+        </is>
+      </c>
+      <c r="B530" t="inlineStr">
+        <is>
+          <t>UVX</t>
+        </is>
+      </c>
+      <c r="C530" t="inlineStr">
+        <is>
+          <t>Saknar standardfras om pedagogiskt stöd</t>
+        </is>
+      </c>
+      <c r="D530" t="inlineStr">
+        <is>
+          <t>Saknar standardfras om pedagogiskt stöd: Ersätter HI3015.…</t>
+        </is>
+      </c>
+      <c r="E530" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AS3004</t>
+        </is>
+      </c>
+    </row>
+    <row r="531">
+      <c r="A531" s="2" t="inlineStr">
+        <is>
+          <t>AS3005</t>
+        </is>
+      </c>
+      <c r="B531" t="inlineStr">
+        <is>
+          <t>UVX</t>
+        </is>
+      </c>
+      <c r="C531" t="inlineStr">
+        <is>
+          <t>Saknar standardfras om pedagogiskt stöd</t>
+        </is>
+      </c>
+      <c r="D531" t="inlineStr">
+        <is>
+          <t>Saknar standardfras om pedagogiskt stöd: Ersätter HI3010.…</t>
+        </is>
+      </c>
+      <c r="E531" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AS3005</t>
+        </is>
+      </c>
+    </row>
+    <row r="532">
+      <c r="A532" s="2" t="inlineStr">
+        <is>
+          <t>AS3006</t>
+        </is>
+      </c>
+      <c r="B532" t="inlineStr">
+        <is>
+          <t>UVX</t>
+        </is>
+      </c>
+      <c r="C532" t="inlineStr">
+        <is>
+          <t>Saknar standardfras om pedagogiskt stöd</t>
+        </is>
+      </c>
+      <c r="D532" t="inlineStr">
+        <is>
+          <t>Saknar standardfras om pedagogiskt stöd: Ersätter VÅ3090.…</t>
+        </is>
+      </c>
+      <c r="E532" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AS3006</t>
+        </is>
+      </c>
+    </row>
+    <row r="533">
+      <c r="A533" s="2" t="inlineStr">
+        <is>
+          <t>AS3007</t>
+        </is>
+      </c>
+      <c r="B533" t="inlineStr">
+        <is>
+          <t>UVX</t>
+        </is>
+      </c>
+      <c r="C533" t="inlineStr">
+        <is>
+          <t>Saknar standardfras om pedagogiskt stöd</t>
+        </is>
+      </c>
+      <c r="D533" t="inlineStr">
+        <is>
+          <t>Saknar standardfras om pedagogiskt stöd: Ersätter RK3038.…</t>
+        </is>
+      </c>
+      <c r="E533" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AS3007</t>
+        </is>
+      </c>
+    </row>
+    <row r="534">
+      <c r="A534" s="2" t="inlineStr">
+        <is>
+          <t>AS3008</t>
+        </is>
+      </c>
+      <c r="B534" t="inlineStr">
+        <is>
+          <t>UVX</t>
+        </is>
+      </c>
+      <c r="C534" t="inlineStr">
+        <is>
+          <t>Saknar standardfras om pedagogiskt stöd</t>
+        </is>
+      </c>
+      <c r="D534" t="inlineStr">
+        <is>
+          <t>Saknar standardfras om pedagogiskt stöd: Ersätter RK3037.…</t>
+        </is>
+      </c>
+      <c r="E534" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AS3008</t>
+        </is>
+      </c>
+    </row>
+    <row r="535">
+      <c r="A535" s="2" t="inlineStr">
+        <is>
+          <t>AS3009</t>
+        </is>
+      </c>
+      <c r="B535" t="inlineStr">
+        <is>
+          <t>UVX</t>
+        </is>
+      </c>
+      <c r="C535" t="inlineStr">
+        <is>
+          <t>Saknar standardfras om pedagogiskt stöd</t>
+        </is>
+      </c>
+      <c r="D535" t="inlineStr">
+        <is>
+          <t>Saknar standardfras om pedagogiskt stöd: Ersätter HI3018.…</t>
+        </is>
+      </c>
+      <c r="E535" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AS3009</t>
+        </is>
+      </c>
+    </row>
+    <row r="536">
+      <c r="A536" s="2" t="inlineStr">
+        <is>
+          <t>AS3010</t>
+        </is>
+      </c>
+      <c r="B536" t="inlineStr">
+        <is>
+          <t>UVX</t>
+        </is>
+      </c>
+      <c r="C536" t="inlineStr">
+        <is>
+          <t>Saknar standardfras om pedagogiskt stöd</t>
+        </is>
+      </c>
+      <c r="D536" t="inlineStr">
+        <is>
+          <t>Saknar standardfras om pedagogiskt stöd: Ersätter HI3017.…</t>
+        </is>
+      </c>
+      <c r="E536" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AS3010</t>
+        </is>
+      </c>
+    </row>
+    <row r="537">
+      <c r="A537" s="2" t="inlineStr">
+        <is>
+          <t>AS3011</t>
+        </is>
+      </c>
+      <c r="B537" t="inlineStr">
+        <is>
+          <t>UVX</t>
+        </is>
+      </c>
+      <c r="C537" t="inlineStr">
+        <is>
+          <t>Saknar standardfras om pedagogiskt stöd</t>
+        </is>
+      </c>
+      <c r="D537" t="inlineStr">
+        <is>
+          <t>Saknar standardfras om pedagogiskt stöd: Ersätter HI3016.…</t>
+        </is>
+      </c>
+      <c r="E537" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AS3011</t>
+        </is>
+      </c>
+    </row>
+    <row r="538">
+      <c r="A538" s="2" t="inlineStr">
+        <is>
+          <t>AS3012</t>
+        </is>
+      </c>
+      <c r="B538" t="inlineStr">
+        <is>
+          <t>UVX</t>
+        </is>
+      </c>
+      <c r="C538" t="inlineStr">
+        <is>
+          <t>Saknar standardfras om pedagogiskt stöd</t>
+        </is>
+      </c>
+      <c r="D538" t="inlineStr">
+        <is>
+          <t>Saknar standardfras om pedagogiskt stöd: Ersätter HI3014.…</t>
+        </is>
+      </c>
+      <c r="E538" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AS3012</t>
+        </is>
+      </c>
+    </row>
+    <row r="539">
+      <c r="A539" s="2" t="inlineStr">
+        <is>
+          <t>AS4001</t>
+        </is>
+      </c>
+      <c r="B539" t="inlineStr">
+        <is>
+          <t>UVX</t>
+        </is>
+      </c>
+      <c r="C539" t="inlineStr">
+        <is>
+          <t>Sektion saknas</t>
+        </is>
+      </c>
+      <c r="D539" t="inlineStr">
+        <is>
+          <t>Ingen Övrigt-sektion i kursplanen</t>
+        </is>
+      </c>
+      <c r="E539" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AS4001</t>
+        </is>
+      </c>
+    </row>
+    <row r="540">
+      <c r="A540" s="2" t="inlineStr">
+        <is>
+          <t>AS4002</t>
+        </is>
+      </c>
+      <c r="B540" t="inlineStr">
+        <is>
+          <t>UVX</t>
+        </is>
+      </c>
+      <c r="C540" t="inlineStr">
+        <is>
+          <t>Sektion saknas</t>
+        </is>
+      </c>
+      <c r="D540" t="inlineStr">
+        <is>
+          <t>Ingen Övrigt-sektion i kursplanen</t>
+        </is>
+      </c>
+      <c r="E540" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AS4002</t>
+        </is>
+      </c>
+    </row>
+    <row r="541">
+      <c r="A541" s="2" t="inlineStr">
+        <is>
+          <t>AS4003</t>
+        </is>
+      </c>
+      <c r="B541" t="inlineStr">
+        <is>
+          <t>UVX</t>
+        </is>
+      </c>
+      <c r="C541" t="inlineStr">
+        <is>
+          <t>Sektion saknas</t>
+        </is>
+      </c>
+      <c r="D541" t="inlineStr">
+        <is>
+          <t>Ingen Övrigt-sektion i kursplanen</t>
+        </is>
+      </c>
+      <c r="E541" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AS4003</t>
+        </is>
+      </c>
+    </row>
+    <row r="542">
+      <c r="A542" s="2" t="inlineStr">
+        <is>
           <t>AS4004</t>
         </is>
       </c>
-      <c r="B523" t="inlineStr">
+      <c r="B542" t="inlineStr">
         <is>
           <t>UVX</t>
         </is>
       </c>
-      <c r="C523" t="inlineStr">
+      <c r="C542" t="inlineStr">
         <is>
           <t>Sektion saknas</t>
         </is>
       </c>
-      <c r="D523" t="inlineStr">
+      <c r="D542" t="inlineStr">
         <is>
           <t>Ingen Övrigt-sektion i kursplanen</t>
         </is>
       </c>
-      <c r="E523" s="2" t="inlineStr">
+      <c r="E542" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AS4004</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:E523"/>
+  <autoFilter ref="A1:E542"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E2" r:id="rId2"/>
@@ -15610,6 +16123,44 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E522" r:id="rId1042"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A523" r:id="rId1043"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E523" r:id="rId1044"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A524" r:id="rId1045"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E524" r:id="rId1046"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A525" r:id="rId1047"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E525" r:id="rId1048"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A526" r:id="rId1049"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E526" r:id="rId1050"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A527" r:id="rId1051"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E527" r:id="rId1052"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A528" r:id="rId1053"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E528" r:id="rId1054"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A529" r:id="rId1055"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E529" r:id="rId1056"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A530" r:id="rId1057"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E530" r:id="rId1058"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A531" r:id="rId1059"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E531" r:id="rId1060"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A532" r:id="rId1061"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E532" r:id="rId1062"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A533" r:id="rId1063"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E533" r:id="rId1064"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A534" r:id="rId1065"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E534" r:id="rId1066"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A535" r:id="rId1067"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E535" r:id="rId1068"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A536" r:id="rId1069"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E536" r:id="rId1070"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A537" r:id="rId1071"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E537" r:id="rId1072"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A538" r:id="rId1073"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E538" r:id="rId1074"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A539" r:id="rId1075"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E539" r:id="rId1076"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A540" r:id="rId1077"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E540" r:id="rId1078"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A541" r:id="rId1079"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E541" r:id="rId1080"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A542" r:id="rId1081"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E542" r:id="rId1082"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/vault-dalarna-university/03 IKS/Analys/Övrigt.xlsx
+++ b/vault-dalarna-university/03 IKS/Analys/Övrigt.xlsx
@@ -2860,7 +2860,7 @@
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Saknar standardfras om pedagogiskt stöd: Antal examinationsförsök är begränsat till fem. Den som antagits till och registrerats på kursen har rätt att erhålla un…</t>
+          <t>Saknar standardfras om pedagogiskt stöd: Antal examinationsförsök är begränsat till fem.…</t>
         </is>
       </c>
       <c r="G73" s="2" t="inlineStr">
@@ -2926,7 +2926,7 @@
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Saknar standardfras om pedagogiskt stöd: Antal examinationsförsök är begränsat till fem. Den som antagits till och registrerats på kursen har rätt att erhålla un…</t>
+          <t>Saknar standardfras om pedagogiskt stöd: Antal examinationsförsök är begränsat till fem.…</t>
         </is>
       </c>
       <c r="G75" s="2" t="inlineStr">

--- a/vault-dalarna-university/03 IKS/Analys/Övrigt.xlsx
+++ b/vault-dalarna-university/03 IKS/Analys/Övrigt.xlsx
@@ -7727,7 +7727,7 @@
       </c>
       <c r="F216" t="inlineStr">
         <is>
-          <t>Saknar standardfras om pedagogiskt stöd: Erätter LP1030.…</t>
+          <t>Saknar standardfras om pedagogiskt stöd: Ersätter LP1030.…</t>
         </is>
       </c>
       <c r="G216" s="2" t="inlineStr">
@@ -17065,7 +17065,7 @@
       </c>
       <c r="F490" t="inlineStr">
         <is>
-          <t>Saknar standardfras om pedagogiskt stöd: Erätter TR1035.…</t>
+          <t>Saknar standardfras om pedagogiskt stöd: Ersätter TR1035.…</t>
         </is>
       </c>
       <c r="G490" s="2" t="inlineStr">

--- a/vault-dalarna-university/03 IKS/Analys/Övrigt.xlsx
+++ b/vault-dalarna-university/03 IKS/Analys/Övrigt.xlsx
@@ -8943,7 +8943,7 @@
       </c>
       <c r="F252" t="inlineStr">
         <is>
-          <t>Saknar standardfras om pedagogiskt stöd: Maximalt fem tentamenstillfällen. Ersätter NA3002.…</t>
+          <t>Saknar standardfras om pedagogiskt stöd: Maximalt fem tentamenstillfällen.…</t>
         </is>
       </c>
       <c r="G252" s="2" t="inlineStr">
